--- a/Cultural-y-patrimonial/Actividades_Cadiz_AgendaCultural.xlsx
+++ b/Cultural-y-patrimonial/Actividades_Cadiz_AgendaCultural.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://riamlab-my.sharepoint.com/personal/estebansota_gnoss_com/Documents/Documentos/GitHub/pidcad-jsons-powerbi/Cultural-y-patrimonial/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9E87AD27F026AF58A2463823DD7C17804F5B0E1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="1596" yWindow="1656" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Actividades" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Actividades" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,28 +27,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="533">
   <si>
-    <t xml:space="preserve">Nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descripción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lugar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enlace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Éxito Asegurado"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Los Síndrome DURACIÓN: 80 Minutos. ¿Recuerdas cuál fue tu último fracaso?
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Fecha(s)</t>
+  </si>
+  <si>
+    <t>Lugar</t>
+  </si>
+  <si>
+    <t>Temática</t>
+  </si>
+  <si>
+    <t>Enlace</t>
+  </si>
+  <si>
+    <t>"Éxito Asegurado"</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Los Síndrome DURACIÓN: 80 Minutos. ¿Recuerdas cuál fue tu último fracaso?
 Probablemente sí. Y sentimos decirte que de momento ha
 sido el último, pero en breve no lo será. Porque en la vida se
 pierde muchas más veces de las que se gana. Y sólo de vez
@@ -61,134 +66,134 @@
 ser todo un fracaso. ¿O era al revés?</t>
   </si>
   <si>
-    <t xml:space="preserve">23 de Octubre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle San Francisco, 11, Villamartín. Cádiz - Teatro Municipal Manuel Fraile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espectáculos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exito-asegurado-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Y tú ¿de qué te ries?', Alex O'dogherty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El evento conmemora el 25 aniversario de su debut en solitario con este espectáculo. La función tendrá lugar el 29 de agosto a las 21:30h en el Auditorio Alcalde Felipe Benítez en Rota, Cádiz. El show tiene una duración aproximada de 1 hora y 40 minutos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 de Agosto del 2026 | 21:30 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avenida San Fernando, 79, Rota. Cádiz - Teatro Auditorio Alcalde Felipe Benítez. Rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/y-tu-de-que-te-ries-alex-odogherty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aires, Hojas al viento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Cía. Piero Partigianoni - Clown Poético DURACIÓN: 60 min. Splinky es un hombrecito preso del demonio de su soledad, que atenúa su tristeza aferrándose a los recuerdos de su pasado que colecciona dentro de un enorme baúl.
+    <t>23 de Octubre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>Calle San Francisco, 11, Villamartín. Cádiz - Teatro Municipal Manuel Fraile</t>
+  </si>
+  <si>
+    <t>Espectáculos</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exito-asegurado-12</t>
+  </si>
+  <si>
+    <t>'Y tú ¿de qué te ries?', Alex O'dogherty</t>
+  </si>
+  <si>
+    <t>El evento conmemora el 25 aniversario de su debut en solitario con este espectáculo. La función tendrá lugar el 29 de agosto a las 21:30h en el Auditorio Alcalde Felipe Benítez en Rota, Cádiz. El show tiene una duración aproximada de 1 hora y 40 minutos.</t>
+  </si>
+  <si>
+    <t>29 de Agosto del 2026 | 21:30 h.</t>
+  </si>
+  <si>
+    <t>Avenida San Fernando, 79, Rota. Cádiz - Teatro Auditorio Alcalde Felipe Benítez. Rota</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/y-tu-de-que-te-ries-alex-odogherty</t>
+  </si>
+  <si>
+    <t>Aires, Hojas al viento</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Cía. Piero Partigianoni - Clown Poético DURACIÓN: 60 min. Splinky es un hombrecito preso del demonio de su soledad, que atenúa su tristeza aferrándose a los recuerdos de su pasado que colecciona dentro de un enorme baúl.
 Vive en el auto engaño de que su antiguo amor sigue existiendo y cada día está más enamorado de un cúmulo de viejos trastos sin vida. Sirio es su Ángel de la Guarda especializado en la escucha. Pronto conseguirá que nuestro clown se conecte con el presente y desde una profunda toma de conciencia pueda despedirse de su pasado, transformarse y emprender una nueva vida.</t>
   </si>
   <si>
-    <t xml:space="preserve">30 de Octubre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Teatro, s/n, Línea de la Concepción (La). Cádiz - Teatro Paseo de  La Velada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aires-hojas-al-viento-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aromas del Sur Cuarteto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Diego Valdivia DURACIÓN: 80 Minutos Se trata de un concierto de Piano de Cola (se incluye en caché si fuese necesario), acompañado de set completo de percusión, guitarra acústica-española y bailarín de danza española. En dichos conciertos interpretamos composiciones propias de temátic social y familiar diversa así como versiones muy personales como Llanto al Piano, Sangre Negra, Camino de la Reina,...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 de Noviembre del 2026 | A las 19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alameda Alfonso XI, San Roque. Cádiz - Teatro Juan Luis Galiardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aromas-del-sur-cuarteto-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aromas del Sur Cuarteto, en Arcos de la Frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Diego Valdivia DURACIÓN: 80 Minutos Se trata de un concierto de Piano de Cola, acompañado de set completo de percusión, guitarra acústica-española y bailarín de danza española. En dichos conciertos interpretamos composiciones propias de temátic social y familiar diversa así como versiones muy personales como Llanto al Piano, Sangre Negra, Camino de la Reina,...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 de Septiembre del 2026 | A las 21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza del Cabildo, Arcos de la Frontera. Cádiz - Plaza del Cabildo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aromas-del-sur-cuarteto-en-arcos-de-la-frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arte contemporáneo y yoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te invitamos a vivir una experiencia de bienestar y conexión a través de una sesión de yoga en el interior de “El Baño”, la emblemática obra de Huang Yong Ping impartida por Elsa, de Olas De Luz. Un entorno único donde el arte contemporáneo, la naturaleza y la práctica consciente se unen para ofrecer un momento de calma, equilibrio e inspiración en pleno corazón de la Fundación Montenmedio Contemporánea.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 de Agosto del 2026 | 10:00h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dehesa de Montenmedio Carretera A-48 (N-340) Km. 42,5, Vejer de la Frontera. Cádiz - Fundación Montenmedio Contemporánea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agenda infantil y juvenil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 de Agosto del 2026 | 10:00h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monumentos y Espacios Culturales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 de Agosto del 2026 | 10:00h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 de Agosto del 2026 | 10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arte contemporáneo y yoga para niños</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los más pequeños podrán disfrutar de una divertida sesión de yoga infantil en el interior de “El Baño”, la singular obra de Huang Yong Ping impartida por Elsa, de Olas De Luz. A través del juego, la respiración y el movimiento, los niños y niñas explorarán su creatividad y aprenderán a conectar con su cuerpo en un entorno donde el arte contemporáneo y la naturaleza se convierten en el mejor escenario para la imaginación y el bienestar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 de Agosto del 2026 | 10:30h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-para-ninos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barquichuelo de Papel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: La Canela Teatro de Títeres DURACIÓN: 50 minutos Espectáculo de títeres y narración para público infantil y familiar.
+    <t>30 de Octubre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>Calle Teatro, s/n, Línea de la Concepción (La). Cádiz - Teatro Paseo de  La Velada</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aires-hojas-al-viento-3</t>
+  </si>
+  <si>
+    <t>Aromas del Sur Cuarteto</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Diego Valdivia DURACIÓN: 80 Minutos Se trata de un concierto de Piano de Cola (se incluye en caché si fuese necesario), acompañado de set completo de percusión, guitarra acústica-española y bailarín de danza española. En dichos conciertos interpretamos composiciones propias de temátic social y familiar diversa así como versiones muy personales como Llanto al Piano, Sangre Negra, Camino de la Reina,...</t>
+  </si>
+  <si>
+    <t>21 de Noviembre del 2026 | A las 19:00</t>
+  </si>
+  <si>
+    <t>Alameda Alfonso XI, San Roque. Cádiz - Teatro Juan Luis Galiardo</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aromas-del-sur-cuarteto-3</t>
+  </si>
+  <si>
+    <t>Aromas del Sur Cuarteto, en Arcos de la Frontera</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Diego Valdivia DURACIÓN: 80 Minutos Se trata de un concierto de Piano de Cola, acompañado de set completo de percusión, guitarra acústica-española y bailarín de danza española. En dichos conciertos interpretamos composiciones propias de temátic social y familiar diversa así como versiones muy personales como Llanto al Piano, Sangre Negra, Camino de la Reina,...</t>
+  </si>
+  <si>
+    <t>25 de Septiembre del 2026 | A las 21:00</t>
+  </si>
+  <si>
+    <t>Plaza del Cabildo, Arcos de la Frontera. Cádiz - Plaza del Cabildo</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aromas-del-sur-cuarteto-en-arcos-de-la-frontera</t>
+  </si>
+  <si>
+    <t>Arte contemporáneo y yoga</t>
+  </si>
+  <si>
+    <t>Te invitamos a vivir una experiencia de bienestar y conexión a través de una sesión de yoga en el interior de “El Baño”, la emblemática obra de Huang Yong Ping impartida por Elsa, de Olas De Luz. Un entorno único donde el arte contemporáneo, la naturaleza y la práctica consciente se unen para ofrecer un momento de calma, equilibrio e inspiración en pleno corazón de la Fundación Montenmedio Contemporánea.</t>
+  </si>
+  <si>
+    <t>10 de Agosto del 2026 | 10:00h</t>
+  </si>
+  <si>
+    <t>Dehesa de Montenmedio Carretera A-48 (N-340) Km. 42,5, Vejer de la Frontera. Cádiz - Fundación Montenmedio Contemporánea</t>
+  </si>
+  <si>
+    <t>Agenda infantil y juvenil</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-0</t>
+  </si>
+  <si>
+    <t>15 de Agosto del 2026 | 10:00h</t>
+  </si>
+  <si>
+    <t>Monumentos y Espacios Culturales</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-1</t>
+  </si>
+  <si>
+    <t>22 de Agosto del 2026 | 10:00h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-2</t>
+  </si>
+  <si>
+    <t>29 de Agosto del 2026 | 10:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-3</t>
+  </si>
+  <si>
+    <t>Arte contemporáneo y yoga para niños</t>
+  </si>
+  <si>
+    <t>Los más pequeños podrán disfrutar de una divertida sesión de yoga infantil en el interior de “El Baño”, la singular obra de Huang Yong Ping impartida por Elsa, de Olas De Luz. A través del juego, la respiración y el movimiento, los niños y niñas explorarán su creatividad y aprenderán a conectar con su cuerpo en un entorno donde el arte contemporáneo y la naturaleza se convierten en el mejor escenario para la imaginación y el bienestar.</t>
+  </si>
+  <si>
+    <t>13 de Agosto del 2026 | 10:30h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-para-ninos</t>
+  </si>
+  <si>
+    <t>Barquichuelo de Papel</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: La Canela Teatro de Títeres DURACIÓN: 50 minutos Espectáculo de títeres y narración para público infantil y familiar.
 Basado en el cuento “Barquichuelo de papel”, de María Puncel y Nivio López. Colección Chiquicuentos, Editorial Bruño.  Dirección: Miguel Oyarzun. El Chon-Chon
 Es un proyecto en colaboración con la Junta de Andalucía. Consejería de Cultura. 
 Sinopsis de la obra:
@@ -198,344 +203,344 @@
 Los dos saltaron del barquito al mismo tiempo. Cuando estuvieron a salvo se dijeron - ¡Ahora ya sabemos mirarnos! ¡Y cada uno recordara al otro que puede salvarse solo!</t>
   </si>
   <si>
-    <t xml:space="preserve">29 de Noviembre del 2026 | A las 12:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calleFernán Caballero, nº 2, Puerto de Santa María (El). Cádiz - Teatro Municipal Pedro Muñoz Seca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/barquichuelo-de-papel-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabaret Festival. El Puerto de Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabaret Festival reinventa el concepto de Cabaret adaptándolo a nuestros tiempos, evoca el ambiente de estas salas de espectáculos que surgieron en los barrios bohemios de París a finales del S.XIX, caracterizados por una decoración seductora y sofisticada, donde se ofrecía una amplia oferta de espectáculos elegantes y transgresores, con el objetivo de convertirse de nuevo en el epicentro del arte y la cultura. Se trata de una experiencia única en la que un público reducido podrá asistir a los espectáculos de sus artistas favoritos en un espacio íntimo y exclusivo. Programación en el Puerto de Santa María confirmada 14 de agosto - Dani Martín 15 de agosto - Vanesa Martín 16 de agosto - Antonio Orozco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 de Agosto del 2026 - 16 de Agosto del 2026 | Consultar programación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pl. de Elías Ahuja, s/n, El Puerto de Santa María. Cádiz - Plaza de Toros de El Puerto de Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cabaret-festival-el-puerto-de-santa-maria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabaret festival. Algeciras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabaret Festival reinventa el concepto de Cabaret adaptándolo a nuestros tiempos, evoca el ambiente de estas salas de espectáculos que surgieron en los barrios bohemios de París a finales del S.XIX, caracterizados por una decoración seductora y sofisticada, donde se ofrecía una amplia oferta de espectáculos elegantes y transgresores, con el objetivo de convertirse de nuevo en el epicentro del arte y la cultura. Programación: 31 de julio: Gente de zona 1 de Agosto: La plazuela 5 de Agosto: Camela 9 de Agosto: Vanesa Martín 10 de agosto: Juan Magán + DJS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 de Julio del 2026 - 12 de Agosto del 2026 | Consultar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zona Plaza de Toros 3, Algeciras. Cádiz - Plaza de Toros Las Palomas, Algeciras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cabaret-festival-algeciras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo Abierto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Ian Scionti DURACIÓN: 70 min Explorando los límites entre el jazz y el flamenco, el Ian Scionti Trio establece un diálogo natural y congruente entre las dos tradiciones musicales propuestas. Campo Abierto, título del disco debut, nace de una reflexión sobre las divisiones y confluencias estéticas d e estos géneros musicales y la evolución lingüística de los dos, ofreciendo un espectáculo que cruza fronteras musicales y culturales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 de Noviembre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Laguna, s/n, Conil de la Frontera. Cádiz - Casa de la Cultura - Teatro Municipal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/campo-abierto-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centro de Interpretación del mar, las almadrabas y el atún. Conil. Recinto de la Chanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Temporada alta (abril a septiembre): lunes a domingos, de 10:30 a 13:30; martes a sábados, de 18:30 a 22:00 horas. Domingos, cerrado. • Temporada baja (enero a marzo y de octubre a diciembre): martes a viernes, de 10:30 a 13:30 y de 17:00 a 20:00 horas. sábados 10:30 a 13:30.
+    <t>29 de Noviembre del 2026 | A las 12:30</t>
+  </si>
+  <si>
+    <t>calleFernán Caballero, nº 2, Puerto de Santa María (El). Cádiz - Teatro Municipal Pedro Muñoz Seca</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/barquichuelo-de-papel-12</t>
+  </si>
+  <si>
+    <t>Cabaret Festival. El Puerto de Santa María</t>
+  </si>
+  <si>
+    <t>Cabaret Festival reinventa el concepto de Cabaret adaptándolo a nuestros tiempos, evoca el ambiente de estas salas de espectáculos que surgieron en los barrios bohemios de París a finales del S.XIX, caracterizados por una decoración seductora y sofisticada, donde se ofrecía una amplia oferta de espectáculos elegantes y transgresores, con el objetivo de convertirse de nuevo en el epicentro del arte y la cultura. Se trata de una experiencia única en la que un público reducido podrá asistir a los espectáculos de sus artistas favoritos en un espacio íntimo y exclusivo. Programación en el Puerto de Santa María confirmada 14 de agosto - Dani Martín 15 de agosto - Vanesa Martín 16 de agosto - Antonio Orozco</t>
+  </si>
+  <si>
+    <t>14 de Agosto del 2026 - 16 de Agosto del 2026 | Consultar programación</t>
+  </si>
+  <si>
+    <t>Pl. de Elías Ahuja, s/n, El Puerto de Santa María. Cádiz - Plaza de Toros de El Puerto de Santa María</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cabaret-festival-el-puerto-de-santa-maria</t>
+  </si>
+  <si>
+    <t>Cabaret festival. Algeciras</t>
+  </si>
+  <si>
+    <t>Cabaret Festival reinventa el concepto de Cabaret adaptándolo a nuestros tiempos, evoca el ambiente de estas salas de espectáculos que surgieron en los barrios bohemios de París a finales del S.XIX, caracterizados por una decoración seductora y sofisticada, donde se ofrecía una amplia oferta de espectáculos elegantes y transgresores, con el objetivo de convertirse de nuevo en el epicentro del arte y la cultura. Programación: 31 de julio: Gente de zona 1 de Agosto: La plazuela 5 de Agosto: Camela 9 de Agosto: Vanesa Martín 10 de agosto: Juan Magán + DJS</t>
+  </si>
+  <si>
+    <t>31 de Julio del 2026 - 12 de Agosto del 2026 | Consultar.</t>
+  </si>
+  <si>
+    <t>Zona Plaza de Toros 3, Algeciras. Cádiz - Plaza de Toros Las Palomas, Algeciras</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cabaret-festival-algeciras</t>
+  </si>
+  <si>
+    <t>Campo Abierto</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Ian Scionti DURACIÓN: 70 min Explorando los límites entre el jazz y el flamenco, el Ian Scionti Trio establece un diálogo natural y congruente entre las dos tradiciones musicales propuestas. Campo Abierto, título del disco debut, nace de una reflexión sobre las divisiones y confluencias estéticas d e estos géneros musicales y la evolución lingüística de los dos, ofreciendo un espectáculo que cruza fronteras musicales y culturales.</t>
+  </si>
+  <si>
+    <t>14 de Noviembre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>Calle Laguna, s/n, Conil de la Frontera. Cádiz - Casa de la Cultura - Teatro Municipal</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/campo-abierto-0</t>
+  </si>
+  <si>
+    <t>Centro de Interpretación del mar, las almadrabas y el atún. Conil. Recinto de la Chanca</t>
+  </si>
+  <si>
+    <t>• Temporada alta (abril a septiembre): lunes a domingos, de 10:30 a 13:30; martes a sábados, de 18:30 a 22:00 horas. Domingos, cerrado. • Temporada baja (enero a marzo y de octubre a diciembre): martes a viernes, de 10:30 a 13:30 y de 17:00 a 20:00 horas. sábados 10:30 a 13:30.
 Entrada gratuita.
 La Chanca del Duque de Conil de la Frontera - llamada así por el Duque de Medina Sidonia, que la construyó a mediados del siglo XVI - se ha rehabilitado recientemente. Las excavaciones arqueológicas que se han realizado por este motivo han permitido el estudio del uso de la chanca, de la pesca del atún con almadraba así como objetos relacionados con esta actividad y con la vida cotidiana de los almadraberos. La Chanca del Duque fue destruida por el maremoto que se produjo en las costas del Golfo de Cádiz, consecuencia del terremoto de Lisboa, el 1 de noviembre de 1755. El actual  Centro de Interpretación y Documentación del Mar, el Atún y las Almadrabas de la Chanca de Conil , acerca al visitante a sentir como el milenario arte de la almadraba ha determinado la vida y la evolución de todo un pueblo; acercarse a comprobar cómo funcionaba un edificio industrial renacentista; y si más allá aún deseáis entender el porqué de un litoral y un mar de unas características únicas y especiales, no podéis dejar de visitarnos.
 • Temporada alta (abril a septiembre): lunes a domingos, de 10:30 a 13:30; martes a sábados, de 18:30 a 22:00 horas. Domingos, cerrado. • Temporada baja (enero a marzo y de octubre a diciembre): martes a viernes, de 10:30 a 13:30 y de 17:00 a 20:00 horas. sábados 10:30 a 13:30.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Temporada alta (abril a septiembre): lunes a domingos, de 10:30 a 13:30; martes a sábados, de 18:30 a 22:00 horas. Domingos, cerrado. • Temporada baja (enero a marzo y de octubre a diciembre): martes a viernes, de 10:30 a 13:30 y de 17:00 a 20:00 horas. sábados 10:30 a 13:30.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centros culturales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exposiciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/centro-de-interpretacion-del-mar-las-almadrabas-y-el-atun-conil-recinto-de-la-chanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciclo Música del Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En el Muelle Reina Victoria
+    <t>• Temporada alta (abril a septiembre): lunes a domingos, de 10:30 a 13:30; martes a sábados, de 18:30 a 22:00 horas. Domingos, cerrado. • Temporada baja (enero a marzo y de octubre a diciembre): martes a viernes, de 10:30 a 13:30 y de 17:00 a 20:00 horas. sábados 10:30 a 13:30.</t>
+  </si>
+  <si>
+    <t>Centros culturales</t>
+  </si>
+  <si>
+    <t>Exposiciones</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/centro-de-interpretacion-del-mar-las-almadrabas-y-el-atun-conil-recinto-de-la-chanca</t>
+  </si>
+  <si>
+    <t>Ciclo Música del Mar</t>
+  </si>
+  <si>
+    <t>En el Muelle Reina Victoria
 Desde 2017, el Ciclo Música del Mar ha traído la mejor programación a la capital gaditana. Internacionales como Ricky Martin, o el mejor nacional como Manuel Carrasco, Leiva, Robe, etc, han pasado por nuestro escenario en los últimos 5 años. Confirmados: Fito y Fitipaldis, 1 de mayo 2026 MEDINA AZAHARA + Alan Nepa: 10 JULIO RVFV : 11 JULIO Caribe Mix Festival: Sábado 18 de julio de 2026 1 de agosto de 2026, Molan los 90 MAR LATINO FEST : 7 AGOSTO FESTIVAL NO SIN MÚSICA 2026. Sábado, 15 de agosto de 2026 MORAD : 21 AGOSTO</t>
   </si>
   <si>
-    <t xml:space="preserve">01 de Mayo del 2026 - 21 de Agosto del 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza de Espańa, 17, Cádiz. Cádiz - Puerto de Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/ciclo-musica-del-mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cine de verano de Rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Con películas de estreno como Lilo &amp; Stitch, Michael, Karate Kid: Legends o Final Destination Bloodlines.
+    <t>01 de Mayo del 2026 - 21 de Agosto del 2026</t>
+  </si>
+  <si>
+    <t>Plaza de Espańa, 17, Cádiz. Cádiz - Puerto de Cádiz</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/ciclo-musica-del-mar</t>
+  </si>
+  <si>
+    <t>Cine de verano de Rota</t>
+  </si>
+  <si>
+    <t>Con películas de estreno como Lilo &amp; Stitch, Michael, Karate Kid: Legends o Final Destination Bloodlines.
 📽️ Cine de Verano de Rota 2026 El Cine de Verano de Rota se celebrará del 1 de julio al 30 de agosto de 2026 en el Colegio San José de Calasanz . Las proyecciones tendrán lugar todos los días a las 22:00 horas , ofreciendo una programación de películas de estreno pensada para todos los públicos, con especial enfoque en el cine familiar y de entretenimiento. 20 JUL · 22:30: MINIONS &amp; MONSTERS: 90 min · +7 (6€) 25 a 29 JUL · 22:30: TOY STORY 5: 102 min · TP (6€) ¿DÓNDE? Rota · Cádiz C. Inmaculada Concepción, 6</t>
   </si>
   <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 30 de Agosto del 2026 | 22:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C. Inmaculada Concepción, 6, Rota. Cádiz - Colegio San José de Calasanz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-de-rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cine de verano en Chipiona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programación: 20 de Julio: Haciendo amigos 21, 22, 23 y 24 de Julio: Vaiana 25, 26 y 27 de Julio: Odisea 28 y 29 de julio: Toy Story 5 30 y 31 de julio: Torrente Presidente ¿Dónde? Avda. de Huelva S/N, junto al Colegio Virgen de Regla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 de Julio del 2026 - 31 de Julio del 2026 | 22:30 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Av. Padre Ángel Nebreda, s/n, Chipiona. Cádiz - Colegio Virgen de Regla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-chipiona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cine de verano en el patio de la Casa del Niño Jesús</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Entrada libre hasta completar aforo - 1 invitación por persona - Entrada desde una hora antes del comiezo de la película -
+    <t>01 de Julio del 2026 - 30 de Agosto del 2026 | 22:00 horas</t>
+  </si>
+  <si>
+    <t>C. Inmaculada Concepción, 6, Rota. Cádiz - Colegio San José de Calasanz</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-de-rota</t>
+  </si>
+  <si>
+    <t>Cine de verano en Chipiona</t>
+  </si>
+  <si>
+    <t>Programación: 20 de Julio: Haciendo amigos 21, 22, 23 y 24 de Julio: Vaiana 25, 26 y 27 de Julio: Odisea 28 y 29 de julio: Toy Story 5 30 y 31 de julio: Torrente Presidente ¿Dónde? Avda. de Huelva S/N, junto al Colegio Virgen de Regla</t>
+  </si>
+  <si>
+    <t>20 de Julio del 2026 - 31 de Julio del 2026 | 22:30 h.</t>
+  </si>
+  <si>
+    <t>Av. Padre Ángel Nebreda, s/n, Chipiona. Cádiz - Colegio Virgen de Regla</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-chipiona</t>
+  </si>
+  <si>
+    <t>Cine de verano en el patio de la Casa del Niño Jesús</t>
+  </si>
+  <si>
+    <t>- Entrada libre hasta completar aforo - 1 invitación por persona - Entrada desde una hora antes del comiezo de la película -
 El ciclo arrancará el 2 de julio con la proyección de SuperWings: Máxima velocidad’, una coproducción de China y Corea del Sur basada en la popular serie de animación. Programación Cine en Familia 2026 2 julio: SuperWings: Máxima velocidad (89 min, TP) 9 julio: Los aitas (88 min, +12) 16 julio: Cómo entrenar a tu dragón (92 min, consultar clasificación de edades) 23 julio: Quién es quién (95 min, TP) 30 julio: Super Agente Hitpig (90 min, TP) 6 agosto: Tipos malos 2 (104 min, TP) 13 agosto: Futbolísimos 2 (95 min, TP) 20 agosto: Los exploradores (88 min, TP) 27 agosto: Pitufos: la aventura se tiñe de azul (92 min, TP)</t>
   </si>
   <si>
-    <t xml:space="preserve">02 de Julio del 2026 - 27 de Agosto del 2026 | Julio: 22:30 h. y Agosto: 22:00 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avenida Fernández Ladreda, Cádiz. Cádiz - Patio de la Casa del Niño Jesús</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-el-patio-de-la-casa-del-nino-jesus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cine de verano en la Línea de la Concepción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📽️ Cine de Verano de La Línea de la Concepción 2026 Cine de Verano de #LaLínea , que se desarrollará íntegramente en Casa de la Juventud con seis películas en cinco sesiones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 de Julio del 2026 - 21 de Agosto del 2026 | 22:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.º Andrés Viñas, 3, La Línea de la Concepción. Cádiz - Casa de la Juventud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-la-linea-de-la-concepcion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cine de verano en la Palma del Condado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📽️ Cine de Verano en La Palma del Condado 2026 Cine de Verano La Palma del Condado 2026 que se desarrollará dentro de la programación de verano 1 de julio: Mufasa 30 de julio: Minecraft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 30 de Julio del 2026 | 22:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-la-palma-del-condado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cine de verano en playas, Algeciras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En la playa de Getares se emitirá: 1 de julio ‘Lilo &amp; Stitch’, el 15 de julio ‘Del revés 2’, el 29 de julio ‘Minecraft’, el 12 de agosto ‘Los Futbolísimos 2’, y el 26 de agosto ‘Héroes de Central Park’. Mientras que en la playa de El Rinconcillo: 8 de julio ‘Elio’, 22 de julio ‘La Sirenita’, 5 de agosto ‘El Gran Premio: A todo gas’, y el 19 de agosto ‘Transformers One’. Es un ciclo de cine familiar gratuito al aire libre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 26 de Agosto del 2026 | Las películas se proyectarán todos los miércoles de julio y agosto a las 22:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">, Algeciras. Cádiz - Varios lugares en el municipio, Algeciras, Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-playas-algeciras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circodéliko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Gate 52 DURACIÓN: 1 hora En un escenario utópico un grupo de amigos se reúnen para compartir sus sueños. Y dentro de este marco mágico transcurren los números
+    <t>02 de Julio del 2026 - 27 de Agosto del 2026 | Julio: 22:30 h. y Agosto: 22:00 h.</t>
+  </si>
+  <si>
+    <t>Avenida Fernández Ladreda, Cádiz. Cádiz - Patio de la Casa del Niño Jesús</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-el-patio-de-la-casa-del-nino-jesus</t>
+  </si>
+  <si>
+    <t>Cine de verano en la Línea de la Concepción</t>
+  </si>
+  <si>
+    <t>📽️ Cine de Verano de La Línea de la Concepción 2026 Cine de Verano de #LaLínea , que se desarrollará íntegramente en Casa de la Juventud con seis películas en cinco sesiones.</t>
+  </si>
+  <si>
+    <t>10 de Julio del 2026 - 21 de Agosto del 2026 | 22:00 horas</t>
+  </si>
+  <si>
+    <t>P.º Andrés Viñas, 3, La Línea de la Concepción. Cádiz - Casa de la Juventud</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-la-linea-de-la-concepcion</t>
+  </si>
+  <si>
+    <t>Cine de verano en la Palma del Condado</t>
+  </si>
+  <si>
+    <t>📽️ Cine de Verano en La Palma del Condado 2026 Cine de Verano La Palma del Condado 2026 que se desarrollará dentro de la programación de verano 1 de julio: Mufasa 30 de julio: Minecraft</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 30 de Julio del 2026 | 22:00 horas</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-la-palma-del-condado</t>
+  </si>
+  <si>
+    <t>Cine de verano en playas, Algeciras</t>
+  </si>
+  <si>
+    <t>En la playa de Getares se emitirá: 1 de julio ‘Lilo &amp; Stitch’, el 15 de julio ‘Del revés 2’, el 29 de julio ‘Minecraft’, el 12 de agosto ‘Los Futbolísimos 2’, y el 26 de agosto ‘Héroes de Central Park’. Mientras que en la playa de El Rinconcillo: 8 de julio ‘Elio’, 22 de julio ‘La Sirenita’, 5 de agosto ‘El Gran Premio: A todo gas’, y el 19 de agosto ‘Transformers One’. Es un ciclo de cine familiar gratuito al aire libre.</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 26 de Agosto del 2026 | Las películas se proyectarán todos los miércoles de julio y agosto a las 22:00 horas</t>
+  </si>
+  <si>
+    <t>, Algeciras. Cádiz - Varios lugares en el municipio, Algeciras, Cádiz</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-playas-algeciras</t>
+  </si>
+  <si>
+    <t>Circodéliko</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Gate 52 DURACIÓN: 1 hora En un escenario utópico un grupo de amigos se reúnen para compartir sus sueños. Y dentro de este marco mágico transcurren los números
 artísticos: malabares, acrobacia aérea y de suelo, música y humor.</t>
   </si>
   <si>
-    <t xml:space="preserve">26 de Diciembre del 2026 | A las 17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza del Ayuntamiento, 1, Villamartín. Cádiz - Plaza del Ayuntamiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/circodeliko-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Con Mucho clown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Petit Teatro DURACIÓN: 55 Juegos, magia, canciones y acrobacias. Disfrutarán un buen rato con Nasu y Basi, dos payasos desternillantes que no le dejarán indiferente. Como si de un circo se tratara, nos enseñarán los sketches mas espectaculares desde una visión diferente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 de Diciembre del 2026 | A las 17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/con-mucho-clown-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concert Music Festival en Sancti Petri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva edición del Concert Music Festival Sancti Petri.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 de Julio del 2026 - 17 de Agosto del 2026 | 22:30 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poblado de Sancti Petri.  Calle Barlovento, Chiclana de la Frontera. Cádiz - Chiclana. Poblado de Sancti Petri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concert-music-festival-en-sancti-petri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concierto de Andy en Cádiz - Solo Tour 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una gira de conciertos en los que los seguidores del artista podrán conocer de primera mano todo el proyecto personal de ANDY, repasando su evolución artística acompañado de una puesta en escena muy especial.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 de Septiembre del 2026 | Próximamente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza Fragela, s/n, Cádiz. Cádiz - Gran Teatro Falla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-andy-en-cadiz-solo-tour-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concierto de Andy en El Bosque - Solo Tour 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 de Diciembre del 2026 | A las 21:00 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-372, Carretera de El Bosque a Arcos , El Bosque. Cádiz - Plaza de toros de El Bosque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-andy-en-el-bosque-solo-tour-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concierto de Brothers in Band en Barco La Pepa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mas que un concierto es una experiencia para los sentidos. Navegar por la desembocadura del rio Guadalquivir, escuchando música en directo y disfrutando de unas vistas espectaculares del entorno del Coto de Doñana es algo único. Los conciertos en el Buque La Pepa en Sanlúcar de Barrameda son espectáculos que no dejan indiferente a nadie y hacen disfrutar tanto al público asistente como a los propios artistas que se suben al escenario. BROTHERS IN BAND ha recorrido ya con su «The Very Best of dIRE sTRAITS Show» buena parte del mundo tocando en España, Alemania, Países Bajos, Francia, Portugal, Bélgica, Andorra, Luxemburgo, Reino Unido, así como en Sudamérica, con shows en Colombia, México y Perú, transportándonos en su particular máquina del tiempo a través de un seleccionado, cuidado y amplio repertorio que pertenece ya a la memoria colectiva de varias generaciones, siendo reconocidos a nivel europeo por el público como uno de los mejores shows homenaje a dIRE sTRAITS de la actualidad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 de Julio del 2026 | A las 20:30 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantalán de Bajo de Guía, Sanlúcar de Barrameda. Cádiz - La Pepa Barco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-brothers-band-en-barco-la-pepa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concierto de Gipsy Kings en Barco La Pepa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mas que un concierto es una experiencia para los sentidos. Navegar por la desembocadura del rio Guadalquivir, escuchando música en directo y disfrutando de unas vistas espectaculares del entorno del Coto de Doñana es algo único. Los conciertos en el Buque La Pepa en Sanlúcar de Barrameda son espectáculos que no dejan indiferente a nadie y hacen disfrutar tanto al público asistente como a los propios artistas que se suben al escenario.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 de Agosto del 2026 | A las 20:30 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flamenco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-gipsy-kings-en-barco-la-pepa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concierto de José Manuel Soto en Barco La Pepa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 de Agosto del 2026 | A las 20:30 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-jose-manuel-soto-en-barco-la-pepa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conjunto Arqueológico de Baelo Claudia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Del 21 de marzo al 20 de junio: Martes a sábado de 09:00 a 21:00. Domingos, festivos y lunes víspera de festivo, de 09:00 a 15:00 horas. Del 21 de junio al 20 de septiembre: Martes a sábado de 09:00 a 15:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. Del 21 de septiembre al 20 de marzo: Martes a sábado de 09:00 a 18:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. FESTIVOS CON APERTURA AÑO 2024: 28 de febrero /28 de marzo 29 de marzo / 15 de agosto / 12 de octubre / 1 de noviembre / 6 de diciembre / 8 de diciembre / 2 días de festivos locales CERRADO TOS LOS LUNES EXCEPTO: 9 de diciembre
+    <t>26 de Diciembre del 2026 | A las 17:00</t>
+  </si>
+  <si>
+    <t>Plaza del Ayuntamiento, 1, Villamartín. Cádiz - Plaza del Ayuntamiento</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/circodeliko-5</t>
+  </si>
+  <si>
+    <t>Con Mucho clown</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Petit Teatro DURACIÓN: 55 Juegos, magia, canciones y acrobacias. Disfrutarán un buen rato con Nasu y Basi, dos payasos desternillantes que no le dejarán indiferente. Como si de un circo se tratara, nos enseñarán los sketches mas espectaculares desde una visión diferente.</t>
+  </si>
+  <si>
+    <t>19 de Diciembre del 2026 | A las 17:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/con-mucho-clown-16</t>
+  </si>
+  <si>
+    <t>Concert Music Festival en Sancti Petri</t>
+  </si>
+  <si>
+    <t>Nueva edición del Concert Music Festival Sancti Petri.</t>
+  </si>
+  <si>
+    <t>10 de Julio del 2026 - 17 de Agosto del 2026 | 22:30 horas</t>
+  </si>
+  <si>
+    <t>Poblado de Sancti Petri.  Calle Barlovento, Chiclana de la Frontera. Cádiz - Chiclana. Poblado de Sancti Petri</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concert-music-festival-en-sancti-petri</t>
+  </si>
+  <si>
+    <t>Concierto de Andy en Cádiz - Solo Tour 2026</t>
+  </si>
+  <si>
+    <t>Una gira de conciertos en los que los seguidores del artista podrán conocer de primera mano todo el proyecto personal de ANDY, repasando su evolución artística acompañado de una puesta en escena muy especial.</t>
+  </si>
+  <si>
+    <t>25 de Septiembre del 2026 | Próximamente</t>
+  </si>
+  <si>
+    <t>Plaza Fragela, s/n, Cádiz. Cádiz - Gran Teatro Falla</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-andy-en-cadiz-solo-tour-2026</t>
+  </si>
+  <si>
+    <t>Concierto de Andy en El Bosque - Solo Tour 2026</t>
+  </si>
+  <si>
+    <t>05 de Diciembre del 2026 | A las 21:00 horas.</t>
+  </si>
+  <si>
+    <t>A-372, Carretera de El Bosque a Arcos , El Bosque. Cádiz - Plaza de toros de El Bosque</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-andy-en-el-bosque-solo-tour-2026</t>
+  </si>
+  <si>
+    <t>Concierto de Brothers in Band en Barco La Pepa</t>
+  </si>
+  <si>
+    <t>Mas que un concierto es una experiencia para los sentidos. Navegar por la desembocadura del rio Guadalquivir, escuchando música en directo y disfrutando de unas vistas espectaculares del entorno del Coto de Doñana es algo único. Los conciertos en el Buque La Pepa en Sanlúcar de Barrameda son espectáculos que no dejan indiferente a nadie y hacen disfrutar tanto al público asistente como a los propios artistas que se suben al escenario. BROTHERS IN BAND ha recorrido ya con su «The Very Best of dIRE sTRAITS Show» buena parte del mundo tocando en España, Alemania, Países Bajos, Francia, Portugal, Bélgica, Andorra, Luxemburgo, Reino Unido, así como en Sudamérica, con shows en Colombia, México y Perú, transportándonos en su particular máquina del tiempo a través de un seleccionado, cuidado y amplio repertorio que pertenece ya a la memoria colectiva de varias generaciones, siendo reconocidos a nivel europeo por el público como uno de los mejores shows homenaje a dIRE sTRAITS de la actualidad.</t>
+  </si>
+  <si>
+    <t>31 de Julio del 2026 | A las 20:30 horas.</t>
+  </si>
+  <si>
+    <t>Pantalán de Bajo de Guía, Sanlúcar de Barrameda. Cádiz - La Pepa Barco</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-brothers-band-en-barco-la-pepa</t>
+  </si>
+  <si>
+    <t>Concierto de Gipsy Kings en Barco La Pepa</t>
+  </si>
+  <si>
+    <t>Mas que un concierto es una experiencia para los sentidos. Navegar por la desembocadura del rio Guadalquivir, escuchando música en directo y disfrutando de unas vistas espectaculares del entorno del Coto de Doñana es algo único. Los conciertos en el Buque La Pepa en Sanlúcar de Barrameda son espectáculos que no dejan indiferente a nadie y hacen disfrutar tanto al público asistente como a los propios artistas que se suben al escenario.</t>
+  </si>
+  <si>
+    <t>07 de Agosto del 2026 | A las 20:30 horas.</t>
+  </si>
+  <si>
+    <t>Flamenco</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-gipsy-kings-en-barco-la-pepa</t>
+  </si>
+  <si>
+    <t>Concierto de José Manuel Soto en Barco La Pepa</t>
+  </si>
+  <si>
+    <t>02 de Agosto del 2026 | A las 20:30 horas.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-jose-manuel-soto-en-barco-la-pepa</t>
+  </si>
+  <si>
+    <t>Conjunto Arqueológico de Baelo Claudia</t>
+  </si>
+  <si>
+    <t>Del 21 de marzo al 20 de junio: Martes a sábado de 09:00 a 21:00. Domingos, festivos y lunes víspera de festivo, de 09:00 a 15:00 horas. Del 21 de junio al 20 de septiembre: Martes a sábado de 09:00 a 15:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. Del 21 de septiembre al 20 de marzo: Martes a sábado de 09:00 a 18:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. FESTIVOS CON APERTURA AÑO 2024: 28 de febrero /28 de marzo 29 de marzo / 15 de agosto / 12 de octubre / 1 de noviembre / 6 de diciembre / 8 de diciembre / 2 días de festivos locales CERRADO TOS LOS LUNES EXCEPTO: 9 de diciembre
 El acceso al Conjunto Arqueológico de Baelo Claudia es libre e individual, sin necesidad de reserva previa, dentro del horario de apertura establecido (ver apartado "Horario"). Será necesario reservar en caso de visita de grupo y visita guiada.
 La ciudad de Baelo Claudia nace en el s. II a.C. en una zona altamente  estratégica como lo es el Estrecho de Gibraltar. Su origen y posterior desarrollo están muy ligados al desarrollo de las industrias salazoneras y al comercio con el norte de África, siendo puerto de unión con la actual Tánger. Baelo Claudia representa un claro referente para el conocimiento del urbanismo romano y la vida en una ciudad durante el Imperio Romano, ya que aquí se localizan todos los elementos representativos que constituyen la esencia de una ciudad romana, es decir: el foro, los templos, la basílica, los edificios de carácter administrativo como la curia o el archivo, el mercado, el teatro, las termas, el barrio industrial, acueductos, la muralla completa, etc. La Junta de Andalucía crea en 1990 el Conjunto Arqueológico de Baelo Claudia, encargado a partir de entonces de velar permanentemente por su conservación, difusión e investigación. Fuente y más información: Página web oficial
 Del 21 de marzo al 20 de junio: Martes a sábado de 09:00 a 21:00. Domingos, festivos y lunes víspera de festivo, de 09:00 a 15:00 horas. Del 21 de junio al 20 de septiembre: Martes a sábado de 09:00 a 15:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. Del 21 de septiembre al 20 de marzo: Martes a sábado de 09:00 a 18:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. FESTIVOS CON APERTURA AÑO 2024: 28 de febrero /28 de marzo 29 de marzo / 15 de agosto / 12 de octubre / 1 de noviembre / 6 de diciembre / 8 de diciembre / 2 días de festivos locales CERRADO TOS LOS LUNES EXCEPTO: 9 de diciembre</t>
   </si>
   <si>
-    <t xml:space="preserve">Del 21 de marzo al 20 de junio: Martes a sábado de 09:00 a 21:00. Domingos, festivos y lunes víspera de festivo, de 09:00 a 15:00 horas. Del 21 de junio al 20 de septiembre: Martes a sábado de 09:00 a 15:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. Del 21 de septiembre al 20 de marzo: Martes a sábado de 09:00 a 18:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. FESTIVOS CON APERTURA AÑO 2024: 28 de febrero /28 de marzo 29 de marzo / 15 de agosto / 12 de octubre / 1 de noviembre / 6 de diciembre / 8 de diciembre / 2 días de festivos locales CERRADO TOS LOS LUNES EXCEPTO: 9 de diciembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enclaves y conjuntos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/conjunto-arqueologico-de-baelo-claudia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conjunto Arqueológico de Baelo Claudia en verano 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conjunto Arqueológico Baelo Claudia . Tarifa Pieza del mes: Cencerro Fecha y hora:  mes de julio. Durante el horario de apertura del centro. Público:  general Descripción: Durante este mes nos centraremos con una curiosa pieza hallada en la excavación del documanus maximus, un cencerro para el ganado ovino datado en el s. IV d.C. Reserva y aforo:  Sin aforo/sin reserva. Visita guiada: “Baelo oculto.  Las termas marítimas”. Fecha y hora:  viernes 3, 10, 17, 24 y 31 de julio  (11:00 h). Público: Público general, a partir de 12 años. Descripción:  Realizaremos una visita guiada a manos de un arqueólogo a diversas zonas no incluidas en el circuito de visitas, por razón de accesibilidad o de especial protección del patrimonio. En esta ocasión  accederemos a las termas marítimas, uno de los elementos arquitectónicos que hacen único a la ciudad de Baelo Claudia. Reserva y aforo:  Reserva en la web del Conjunto. Aforo limitado (30 personas). Visita guiada: “Visitas guiadas de verano ”. Fecha y hora:   sábados 4, 11, 18, 25 y domingos 5, 12, 19 y 26 de julio a las10:30 h. Público: Público general. Descripción: conoceremos en detalla la ciudad romana a manos de un guía arqueólogo que presenta un conocimiento extenso y profundo de las maravillas del enclave, las particularidades, anécdotas, hallazgos actuales y la historia de toda una zona fundamental en la historia a lo largo de varios siglos. Reserva y aforo: Reserva previa en visitasbaelo2026@gmail.com .  Aforo limitado (30 personas). Concierto: “Festival Baelo Jazz”. Primer concierto. Fecha y hora:  jueves 23 (21:30 h) Público: Público adulto. Descripción: Comenzamos la 3ª edición del Festival Baelo Jazz con Jorge Pardo Trío. Reserva y aforo: Reserva en la web del Conjunto. Aforo limitado (350 personas). Concierto: “Festival Baelo Jazz”. Segundo concierto. Fecha y hora:  jueves 30 (21:30 h) Público: Público adulto. Descripción: Segundo concierto de la 3ª edición del Festival Baelo Jazz con el Trio Garum. Reserva y aforo: Reserva en la web del conjunto. Aforo limitado (350 personas). Representación: “Teatro y Filosofía: un teatro cómico y filosófico participativo” . Fecha y hora:  sábado 1 de agosto a las 21:30 h Público: Público general (se recomienda a partir de  12 años). Descripción: Presentamos el proyecto “Escena y Pensamiento” donde el teatro se enlaza con la crítica. Con la colaboración de la Asociación cultural “Dialexis – Hagamos Filosofía” y UNESCO se ofrecerá al público varias representaciones de micro-obras teatrales cómicas, que tocarán temas actuales y que, desde el humor, darán lugar a interesantes coloquios por parte de los filósofos David Pastor (Vico) y Jonatán Romero, en donde harán participar al público en un diálogo que seguro nos hará que pensar y reír. Reserva y aforo: Reserva en la web del Conjunto. Aforo limitado (300 personas). Visita guiada: “Visitas guiadas de verano” . Fecha y hora:   sábados 1, 8, 15, 22, 29 y domingos 2, 9, 16, 23 y 30 de agosto a las 10:30 h. Público: Público general. Descripción: conoceremos en detalla la ciudad romana a manos de un guía arqueólogo que presenta un conocimiento extenso y profundo de las maravillas del enclave, las particularidades, anécdotas, hallazgos actuales y la historia de toda una zona fundamental en la historia a lo largo de varios siglos. Reserva y aforo:  Reserva previa en visitasbaelo2026@gmail.com .  Aforo limitado (30 personas). Concierto: “Festival Baelo Jazz”. Tercer concierto. Fecha y hora:  jueves 6 de agosto, 21:30 h. Público: Público adulto. Descripción: Finalizamos la 3ª edición del Festival Baelo Jazz con el concierto del grupo Piet Bervist Sextet y la participación de la cantante Alicia Carrasco. Reserva y aforo: Reserva en la web del Conjunto. Aforo limitado (350 personas).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 30 de Agosto del 2026 | Distintos pases horarios en período estival.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 30 de Agosto del 2026 Distintos pases horarios en período estival.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/conjunto-arqueologico-de-baelo-claudia-en-verano-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connectivity 5tet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: NATALIA RUCIERO DURACIÓN: 60 min. aprox. La formación llamada Natalia Ruciero es una propuesta de esta cantante de Jazz nacida en Sevilla con amplia experiencia en este género musical . En 2023 Natalia se reúne con tres instrumentistas de Jazz con quienes ya ha colaborado en otros proyectos, entre otros Four Women Quartet, y les propone acompañarle en esta nueva propuesta, su proyecto más personal hasta la fecha al tratarse de sus composiciones originales: Natalia Ruciero, cantante Adriana Calvo, saxo Alto o Nacho Guarrochena, saxo Tenor en sustitución si fuera necesario Martina Mollo, pianista Blanca Barranco, contrabajista Nacho Megina, batería</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 de Octubre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/connectivity-5tet-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cualquier Verdura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Compañía Chimichurri DURACIÓN: 50 min Todo está en equilibrio. El Hombre, a veces no.
+    <t>Del 21 de marzo al 20 de junio: Martes a sábado de 09:00 a 21:00. Domingos, festivos y lunes víspera de festivo, de 09:00 a 15:00 horas. Del 21 de junio al 20 de septiembre: Martes a sábado de 09:00 a 15:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. Del 21 de septiembre al 20 de marzo: Martes a sábado de 09:00 a 18:00. Domingos, festivos y lunes víspera de festivo, de 9:00 a 15:00 horas. FESTIVOS CON APERTURA AÑO 2024: 28 de febrero /28 de marzo 29 de marzo / 15 de agosto / 12 de octubre / 1 de noviembre / 6 de diciembre / 8 de diciembre / 2 días de festivos locales CERRADO TOS LOS LUNES EXCEPTO: 9 de diciembre</t>
+  </si>
+  <si>
+    <t>Enclaves y conjuntos</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/conjunto-arqueologico-de-baelo-claudia</t>
+  </si>
+  <si>
+    <t>Conjunto Arqueológico de Baelo Claudia en verano 2026</t>
+  </si>
+  <si>
+    <t>Conjunto Arqueológico Baelo Claudia . Tarifa Pieza del mes: Cencerro Fecha y hora:  mes de julio. Durante el horario de apertura del centro. Público:  general Descripción: Durante este mes nos centraremos con una curiosa pieza hallada en la excavación del documanus maximus, un cencerro para el ganado ovino datado en el s. IV d.C. Reserva y aforo:  Sin aforo/sin reserva. Visita guiada: “Baelo oculto.  Las termas marítimas”. Fecha y hora:  viernes 3, 10, 17, 24 y 31 de julio  (11:00 h). Público: Público general, a partir de 12 años. Descripción:  Realizaremos una visita guiada a manos de un arqueólogo a diversas zonas no incluidas en el circuito de visitas, por razón de accesibilidad o de especial protección del patrimonio. En esta ocasión  accederemos a las termas marítimas, uno de los elementos arquitectónicos que hacen único a la ciudad de Baelo Claudia. Reserva y aforo:  Reserva en la web del Conjunto. Aforo limitado (30 personas). Visita guiada: “Visitas guiadas de verano ”. Fecha y hora:   sábados 4, 11, 18, 25 y domingos 5, 12, 19 y 26 de julio a las10:30 h. Público: Público general. Descripción: conoceremos en detalla la ciudad romana a manos de un guía arqueólogo que presenta un conocimiento extenso y profundo de las maravillas del enclave, las particularidades, anécdotas, hallazgos actuales y la historia de toda una zona fundamental en la historia a lo largo de varios siglos. Reserva y aforo: Reserva previa en visitasbaelo2026@gmail.com .  Aforo limitado (30 personas). Concierto: “Festival Baelo Jazz”. Primer concierto. Fecha y hora:  jueves 23 (21:30 h) Público: Público adulto. Descripción: Comenzamos la 3ª edición del Festival Baelo Jazz con Jorge Pardo Trío. Reserva y aforo: Reserva en la web del Conjunto. Aforo limitado (350 personas). Concierto: “Festival Baelo Jazz”. Segundo concierto. Fecha y hora:  jueves 30 (21:30 h) Público: Público adulto. Descripción: Segundo concierto de la 3ª edición del Festival Baelo Jazz con el Trio Garum. Reserva y aforo: Reserva en la web del conjunto. Aforo limitado (350 personas). Representación: “Teatro y Filosofía: un teatro cómico y filosófico participativo” . Fecha y hora:  sábado 1 de agosto a las 21:30 h Público: Público general (se recomienda a partir de  12 años). Descripción: Presentamos el proyecto “Escena y Pensamiento” donde el teatro se enlaza con la crítica. Con la colaboración de la Asociación cultural “Dialexis – Hagamos Filosofía” y UNESCO se ofrecerá al público varias representaciones de micro-obras teatrales cómicas, que tocarán temas actuales y que, desde el humor, darán lugar a interesantes coloquios por parte de los filósofos David Pastor (Vico) y Jonatán Romero, en donde harán participar al público en un diálogo que seguro nos hará que pensar y reír. Reserva y aforo: Reserva en la web del Conjunto. Aforo limitado (300 personas). Visita guiada: “Visitas guiadas de verano” . Fecha y hora:   sábados 1, 8, 15, 22, 29 y domingos 2, 9, 16, 23 y 30 de agosto a las 10:30 h. Público: Público general. Descripción: conoceremos en detalla la ciudad romana a manos de un guía arqueólogo que presenta un conocimiento extenso y profundo de las maravillas del enclave, las particularidades, anécdotas, hallazgos actuales y la historia de toda una zona fundamental en la historia a lo largo de varios siglos. Reserva y aforo:  Reserva previa en visitasbaelo2026@gmail.com .  Aforo limitado (30 personas). Concierto: “Festival Baelo Jazz”. Tercer concierto. Fecha y hora:  jueves 6 de agosto, 21:30 h. Público: Público adulto. Descripción: Finalizamos la 3ª edición del Festival Baelo Jazz con el concierto del grupo Piet Bervist Sextet y la participación de la cantante Alicia Carrasco. Reserva y aforo: Reserva en la web del Conjunto. Aforo limitado (350 personas).</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 30 de Agosto del 2026 | Distintos pases horarios en período estival.</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 30 de Agosto del 2026 Distintos pases horarios en período estival.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/conjunto-arqueologico-de-baelo-claudia-en-verano-2026</t>
+  </si>
+  <si>
+    <t>Connectivity 5tet</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: NATALIA RUCIERO DURACIÓN: 60 min. aprox. La formación llamada Natalia Ruciero es una propuesta de esta cantante de Jazz nacida en Sevilla con amplia experiencia en este género musical . En 2023 Natalia se reúne con tres instrumentistas de Jazz con quienes ya ha colaborado en otros proyectos, entre otros Four Women Quartet, y les propone acompañarle en esta nueva propuesta, su proyecto más personal hasta la fecha al tratarse de sus composiciones originales: Natalia Ruciero, cantante Adriana Calvo, saxo Alto o Nacho Guarrochena, saxo Tenor en sustitución si fuera necesario Martina Mollo, pianista Blanca Barranco, contrabajista Nacho Megina, batería</t>
+  </si>
+  <si>
+    <t>24 de Octubre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/connectivity-5tet-2</t>
+  </si>
+  <si>
+    <t>Cualquier Verdura</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Compañía Chimichurri DURACIÓN: 50 min Todo está en equilibrio. El Hombre, a veces no.
 Como Rafael Dante. Su desequilibrio se asemeja al de cualquier otro.
 Pero su equilibrio no.
 De un lado de la balanza la técnica, la precisión, la concentración.
@@ -544,128 +549,128 @@
 Como el Artista sobre sus objetos.Como nuestro ADN en su estructura, o como el de cualquier verdura...</t>
   </si>
   <si>
-    <t xml:space="preserve">30 de Agosto del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parque Alcalde Antonio Álvarez, Puerto de Santa María (El). Cádiz - Parque Alcalde Antonio Álvarez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cualquier-verdura-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cádiz. Exposición sobre Caballero Bonald en la Facultad de Filosofía y Letras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Centro Andaluz de las Letras colabora con la Facultad de Filosofía y Letras de la Universidad de Cádiz con la exposición sobre José Manuel Caballero Bonald, titulada La aventura de escribir. Comisariada por el también escritor Felipe Benítez Reyes, amigo del jerezano, la muestra nos propone un recorrido cronológico a través de su vida y su obra, que se podrá ver hasta el 25 de mayo en la Biblioteca de Humanidades de dicha facultad, situada en la avenida Dr. Gómez Ulla de Cádiz. Permanecerá abierta del 15 de abril al 31 de julio de 2026, y se podrá visitar de lunes a viernes de 9:00 a 21:00 horas. Esta actividad forma parte del Programa Expositivo del Centro Andaluz de las Letras, cuyo objetivo es difundir la obra de las escritoras y escritores de Andalucía, en relación con su vida, a través de imágenes y textos que ofrecen una idea global de su importancia de manera sencilla y visual, pero con gran rigor intelectual. Así, se pretende transmitir al público la importancia que supone la protección y conservación del patrimonio intelectual.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 de Abril del 2026 - 31 de Julio del 2026 | De lunes a viernes de 9:00 a 21:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avenida Doctor Gómez Ulla, 1, Cádiz. Cádiz - Facultad de Filosofía y Letras (UCA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Libros y literatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-exposicion-sobre-caballero-bonald-en-la-facultad-de-filosofia-y-letras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cádiz. Música de Lobo: Carmen Camacho y Javier Prieto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Centro Andaluz de las Letras colabora con la Fundación Carlos Edmundo de Ory en el ciclo Música de Lobo . Dentro de esta serie de encuentros artístico literarios que se celebrarán en Cádiz , la escritora Carmen Camacho y el músico Javier Prieto participarán con Deslengua . Será el jueves 10 de septiembre a partir de las 20.30 horas en los ficus de los Jardines Clara Campoamor. Con esta cita, como dice Carmen Camacho, se levanta "la palabra de la página", y se produce el encuentro entre las artes. De hecho, la escritora tiene una amplia experiencia en este tipo de arte activo, ya que en muchos de sus encuentros con el público ha logrado conjugar palabra, danza, o canto, entre otras muchas disciplinas. Este espectáculo, en el que comparte escenario con el actor, profesor y percusionista Javier Prieto, está basado en su libro Deslengua (Libros de la Herida). La asistencia a este encuentro cultural, organizado por la Fundación Carlos Edmundo de Ory , con la colaboración de la Fundación Municipal de Cultura del Ayuntamiento de Cádiz , la Universidad de Cádiz y el Centro Andaluz de las Letras , es libre y gratuita. Foto: Luis Castilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 de Septiembre del 2026 | 20.30 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alameda Clara Campoamor, s/n, Cádiz. Cádiz - Jardines Clara Campoamor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-musica-de-lobo-carmen-camacho-y-javier-prieto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cádiz. Música de Lobo: David Eloy Rodríguez y Virginia Moreno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Centro Andaluz de las Letras colabora con la Fundación Carlos Edmundo de Ory en el ciclo Música de Lobo . Dentro de esta serie de encuentros artístico literarios, el poeta David Eloy Rodríguez y la compositora Virginia Moreno participarán con Animales heridos en la ciudad de Cádiz . Será el jueves 3 de septiembre a partir de las 20.30 horas en los ficus de los Jardines Clara Campoamor. Este espectáculo musical y poético combina la palabra con otras disciplinas artísticas, partiendo de una premisa: "¿Qué palabras escogeríamos para compartir si supiéramos que esta es la última noche en La Tierra? ¿Cómo sonarían, cómo se entenderían, si supiéramos que no hay tiempo, que esto se acaba?". Intentando dar respuesta a estas preguntas, los versos y palabras del poeta quedan ratificadas gracias a la fuerza del sonido de los instrumentos. La asistencia a este encuentro cultural, organizado por la Fundación Carlos Edmundo de Ory , con la colaboración de la Fundación Municipal de Cultura del Ayuntamiento de Cádiz , la Universidad de Cádiz y el Centro Andaluz de las Letras , es libre y gratuita. Foto: La Palabra Itinerante/Oliver Ojeda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03 de Septiembre del 2026 | 20.30 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-musica-de-lobo-david-eloy-rodriguez-y-virginia-moreno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danzas latinoamericanas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Cuarteto Bruma DURACIÓN: 60 minutos El programa "Danzas latinoamericanas" del Cuarteto Bruma presenta un vibrante recorrido musical por América Latina, destacando obras de Heitor Villa-Lobos, José Elizondo y Astor Piazzolla. El cuarteto selecciona piezas que fusionan tradición y modernidad, capturando la esencia de la música latinoamericana. Villa-Lobos, considerado el padre de la música clásica brasileña, infunde sus composiciones con una riqueza armónica y rítmica que refleja la bossa nova, el folclore y la música indígena de Brasil. Su obra evoca paisajes tropicales y la cultura brasileña. José Elizondo contribuye con "Danzas Latinoamericanas", que se inspira en ritmos y melodías de diversas regiones del continente. Sus piezas celebran la diversidad cultural y la riqueza melódica de América Latina, abarcando una gama de emociones que van desde lo contemplativo hasta lo vibrante. Por su parte, Astor Piazzolla, al fusionar tango con jazz y música clásica contemporánea, crea una obra innovadora inspirada en las "Cuatro Estaciones" de Vivaldi. Aunque no fue concebida como suite, su interpretación conjunta ha llevado a esta obra a convertirse en un referente del tango y la música de cámara moderna. El Cuarteto Bruma invita a los asistentes a un viaje sonoro, explorando temas como el amor, la nostalgia y la celebración, mientras honra tanto la tradición como la innovación musical de América Latina.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 de Octubre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza Romero Martínez, s/n, Jerez de la Frontera. Cádiz - Teatro Villamarta de Jerez de la Frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/danzas-latinoamericanas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desayunos con arte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desayunos con Arte propone un encuentro distendido con Rocío Gutiérrez, directora de la Fundación Montenmedio Contemporánea, para descubrir de primera mano la historia, la filosofía y el proyecto de la Fundación, en un espacio abierto al diálogo y al intercambio de ideas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 de Julio del 2026 | 10:30H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 de Agosto del 2026 | 10:30h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 de Agosto del 2026 | 10:30h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diábolo Classic Metal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Hermanos Infoncundibles DURACIÓN: 55 minutos El concierto está a punto de comenzar. Los excéntricos hermanos terminan de prepararlo todo con un calculado desorden. Pero aun queda una duda: Si Beethoven hubiese nacido hoy... ¿Sería rockero o malabarista? Efectivamente, ellos tampoco lo saben. Rompiendo constantemente una inexistente cuarta pared, hacen cómplice al público de sus constantes conflictos clásicos entre hermanos. Nos encontramos ante una extraña mezcla de música, circo y humor... sobre todo humor. Haciendo guiños a diferentes estilos (flamenco, clásico y rock) sus protagonistas evolucionan con diferentes formas de entender los malabares, combinando un elevado nivel técnico con refinados gustos musicales (evidentemente, esto último lo han escrito ellos mismos).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 de Agosto del 2026 | A las 22:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/diabolo-classic-metal-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELLAS DE ORO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: La Líquida DURACIÓN: 90 minutos ELLAS DE ORO es una divertida, curiosa y emocionante mirada a las mujeres más libres y cultas de su época, a la gramática forjadora de imperios, a las bobas damas que no lo eran tanto, a aquella apretada cazuela reconvertida en gallinero, al lenguaje silencioso de las que no podían hablar, a los personajes que hablaban por ellas y a las prohibiciones por hacerlo, a la educación que rompe cadenas y a la inefable magia de la escena.
+    <t>30 de Agosto del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>Parque Alcalde Antonio Álvarez, Puerto de Santa María (El). Cádiz - Parque Alcalde Antonio Álvarez</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cualquier-verdura-9</t>
+  </si>
+  <si>
+    <t>Cádiz. Exposición sobre Caballero Bonald en la Facultad de Filosofía y Letras</t>
+  </si>
+  <si>
+    <t>El Centro Andaluz de las Letras colabora con la Facultad de Filosofía y Letras de la Universidad de Cádiz con la exposición sobre José Manuel Caballero Bonald, titulada La aventura de escribir. Comisariada por el también escritor Felipe Benítez Reyes, amigo del jerezano, la muestra nos propone un recorrido cronológico a través de su vida y su obra, que se podrá ver hasta el 25 de mayo en la Biblioteca de Humanidades de dicha facultad, situada en la avenida Dr. Gómez Ulla de Cádiz. Permanecerá abierta del 15 de abril al 31 de julio de 2026, y se podrá visitar de lunes a viernes de 9:00 a 21:00 horas. Esta actividad forma parte del Programa Expositivo del Centro Andaluz de las Letras, cuyo objetivo es difundir la obra de las escritoras y escritores de Andalucía, en relación con su vida, a través de imágenes y textos que ofrecen una idea global de su importancia de manera sencilla y visual, pero con gran rigor intelectual. Así, se pretende transmitir al público la importancia que supone la protección y conservación del patrimonio intelectual.</t>
+  </si>
+  <si>
+    <t>15 de Abril del 2026 - 31 de Julio del 2026 | De lunes a viernes de 9:00 a 21:00 horas</t>
+  </si>
+  <si>
+    <t>Avenida Doctor Gómez Ulla, 1, Cádiz. Cádiz - Facultad de Filosofía y Letras (UCA)</t>
+  </si>
+  <si>
+    <t>Libros y literatura</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-exposicion-sobre-caballero-bonald-en-la-facultad-de-filosofia-y-letras</t>
+  </si>
+  <si>
+    <t>Cádiz. Música de Lobo: Carmen Camacho y Javier Prieto</t>
+  </si>
+  <si>
+    <t>El Centro Andaluz de las Letras colabora con la Fundación Carlos Edmundo de Ory en el ciclo Música de Lobo . Dentro de esta serie de encuentros artístico literarios que se celebrarán en Cádiz , la escritora Carmen Camacho y el músico Javier Prieto participarán con Deslengua . Será el jueves 10 de septiembre a partir de las 20.30 horas en los ficus de los Jardines Clara Campoamor. Con esta cita, como dice Carmen Camacho, se levanta "la palabra de la página", y se produce el encuentro entre las artes. De hecho, la escritora tiene una amplia experiencia en este tipo de arte activo, ya que en muchos de sus encuentros con el público ha logrado conjugar palabra, danza, o canto, entre otras muchas disciplinas. Este espectáculo, en el que comparte escenario con el actor, profesor y percusionista Javier Prieto, está basado en su libro Deslengua (Libros de la Herida). La asistencia a este encuentro cultural, organizado por la Fundación Carlos Edmundo de Ory , con la colaboración de la Fundación Municipal de Cultura del Ayuntamiento de Cádiz , la Universidad de Cádiz y el Centro Andaluz de las Letras , es libre y gratuita. Foto: Luis Castilla</t>
+  </si>
+  <si>
+    <t>10 de Septiembre del 2026 | 20.30 horas</t>
+  </si>
+  <si>
+    <t>Alameda Clara Campoamor, s/n, Cádiz. Cádiz - Jardines Clara Campoamor</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-musica-de-lobo-carmen-camacho-y-javier-prieto</t>
+  </si>
+  <si>
+    <t>Cádiz. Música de Lobo: David Eloy Rodríguez y Virginia Moreno</t>
+  </si>
+  <si>
+    <t>El Centro Andaluz de las Letras colabora con la Fundación Carlos Edmundo de Ory en el ciclo Música de Lobo . Dentro de esta serie de encuentros artístico literarios, el poeta David Eloy Rodríguez y la compositora Virginia Moreno participarán con Animales heridos en la ciudad de Cádiz . Será el jueves 3 de septiembre a partir de las 20.30 horas en los ficus de los Jardines Clara Campoamor. Este espectáculo musical y poético combina la palabra con otras disciplinas artísticas, partiendo de una premisa: "¿Qué palabras escogeríamos para compartir si supiéramos que esta es la última noche en La Tierra? ¿Cómo sonarían, cómo se entenderían, si supiéramos que no hay tiempo, que esto se acaba?". Intentando dar respuesta a estas preguntas, los versos y palabras del poeta quedan ratificadas gracias a la fuerza del sonido de los instrumentos. La asistencia a este encuentro cultural, organizado por la Fundación Carlos Edmundo de Ory , con la colaboración de la Fundación Municipal de Cultura del Ayuntamiento de Cádiz , la Universidad de Cádiz y el Centro Andaluz de las Letras , es libre y gratuita. Foto: La Palabra Itinerante/Oliver Ojeda</t>
+  </si>
+  <si>
+    <t>03 de Septiembre del 2026 | 20.30 horas</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-musica-de-lobo-david-eloy-rodriguez-y-virginia-moreno</t>
+  </si>
+  <si>
+    <t>Danzas latinoamericanas</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Cuarteto Bruma DURACIÓN: 60 minutos El programa "Danzas latinoamericanas" del Cuarteto Bruma presenta un vibrante recorrido musical por América Latina, destacando obras de Heitor Villa-Lobos, José Elizondo y Astor Piazzolla. El cuarteto selecciona piezas que fusionan tradición y modernidad, capturando la esencia de la música latinoamericana. Villa-Lobos, considerado el padre de la música clásica brasileña, infunde sus composiciones con una riqueza armónica y rítmica que refleja la bossa nova, el folclore y la música indígena de Brasil. Su obra evoca paisajes tropicales y la cultura brasileña. José Elizondo contribuye con "Danzas Latinoamericanas", que se inspira en ritmos y melodías de diversas regiones del continente. Sus piezas celebran la diversidad cultural y la riqueza melódica de América Latina, abarcando una gama de emociones que van desde lo contemplativo hasta lo vibrante. Por su parte, Astor Piazzolla, al fusionar tango con jazz y música clásica contemporánea, crea una obra innovadora inspirada en las "Cuatro Estaciones" de Vivaldi. Aunque no fue concebida como suite, su interpretación conjunta ha llevado a esta obra a convertirse en un referente del tango y la música de cámara moderna. El Cuarteto Bruma invita a los asistentes a un viaje sonoro, explorando temas como el amor, la nostalgia y la celebración, mientras honra tanto la tradición como la innovación musical de América Latina.</t>
+  </si>
+  <si>
+    <t>10 de Octubre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>Plaza Romero Martínez, s/n, Jerez de la Frontera. Cádiz - Teatro Villamarta de Jerez de la Frontera</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/danzas-latinoamericanas</t>
+  </si>
+  <si>
+    <t>Desayunos con arte</t>
+  </si>
+  <si>
+    <t>Desayunos con Arte propone un encuentro distendido con Rocío Gutiérrez, directora de la Fundación Montenmedio Contemporánea, para descubrir de primera mano la historia, la filosofía y el proyecto de la Fundación, en un espacio abierto al diálogo y al intercambio de ideas.</t>
+  </si>
+  <si>
+    <t>30 de Julio del 2026 | 10:30H</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-0</t>
+  </si>
+  <si>
+    <t>06 de Agosto del 2026 | 10:30h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-1</t>
+  </si>
+  <si>
+    <t>27 de Agosto del 2026 | 10:30h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-2</t>
+  </si>
+  <si>
+    <t>Diábolo Classic Metal</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Hermanos Infoncundibles DURACIÓN: 55 minutos El concierto está a punto de comenzar. Los excéntricos hermanos terminan de prepararlo todo con un calculado desorden. Pero aun queda una duda: Si Beethoven hubiese nacido hoy... ¿Sería rockero o malabarista? Efectivamente, ellos tampoco lo saben. Rompiendo constantemente una inexistente cuarta pared, hacen cómplice al público de sus constantes conflictos clásicos entre hermanos. Nos encontramos ante una extraña mezcla de música, circo y humor... sobre todo humor. Haciendo guiños a diferentes estilos (flamenco, clásico y rock) sus protagonistas evolucionan con diferentes formas de entender los malabares, combinando un elevado nivel técnico con refinados gustos musicales (evidentemente, esto último lo han escrito ellos mismos).</t>
+  </si>
+  <si>
+    <t>11 de Agosto del 2026 | A las 22:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/diabolo-classic-metal-1</t>
+  </si>
+  <si>
+    <t>ELLAS DE ORO</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: La Líquida DURACIÓN: 90 minutos ELLAS DE ORO es una divertida, curiosa y emocionante mirada a las mujeres más libres y cultas de su época, a la gramática forjadora de imperios, a las bobas damas que no lo eran tanto, a aquella apretada cazuela reconvertida en gallinero, al lenguaje silencioso de las que no podían hablar, a los personajes que hablaban por ellas y a las prohibiciones por hacerlo, a la educación que rompe cadenas y a la inefable magia de la escena.
 Si los cómicos siempre han tenido complicada su existencia, imagínense a las cómicas del Siglo de Oro… Esposa, disoluta o monja eran las posibles salidas. ¡Aunque había un estado más! ¡Actriz de mal vivir pero buena libertad! ¡Vicio perjudicial es el teatro! ¡Gentes de vida licenciosa son los que hacen oficio en corrales y caminos! ¡Pero ellas… ellas… ¡Ellas aún más! ¡Peligroso ejemplo para la cazuela!</t>
   </si>
   <si>
-    <t xml:space="preserve">20 de Noviembre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/ellas-de-oro-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Viento es Salvaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Las Niñas de Cádiz DURACIÓN: 85 minutos Dos amigas. Tan amigas que son hermanas. Solo una sombra sobre su amistad:
+    <t>20 de Noviembre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/ellas-de-oro-1</t>
+  </si>
+  <si>
+    <t>El Viento es Salvaje</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Las Niñas de Cádiz DURACIÓN: 85 minutos Dos amigas. Tan amigas que son hermanas. Solo una sombra sobre su amistad:
 “Mientras que una crecía confiada
 Mimada por la vida y sonriente
 La otra se sentía desgraciada…”
@@ -673,367 +678,367 @@
 Nuestro nuevo espectáculo es una reflexión lúdica y “jonda” sobre la suerte y la culpa. Una tragedia atravesada por la carcajada, como no podía ser de otra manera en un espectáculo de Las Niñas de Cádiz. Porque sabemos que en toda historia terrible hay una paradoja que puede llevar a la comedia; y, al contrario, en todo arranque de humor hay siempre un fondo trágico</t>
   </si>
   <si>
-    <t xml:space="preserve">19 de Septiembre del 2026 | A las 21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza Artesanía, s/n, Guadalcacín. Cádiz - Teatro Municipal   "Julián Oslé Muñoz"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-viento-es-salvaje-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El asesino de la regañá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Sofía Aguilar Producciones de Arte y Producciones Circulares DURACIÓN: 80 minutos Un asesino en serie tiene en jaque a la ciudad de Sevilla. Se trata de un misterioso criminal que asegura matar para preservar la pureza sevillana, de sevillanas maneras. Burlando una y otra vez la investigación policial, ya ha cometido siete asesinatos, firmados todos con el inconfundible sello de su peculiar arma homicida: una afilada cuña de regañá. El inspector Villanueva -llegado de Madrid para hacerse cargo del caso de la mano del muy sevillano agente Jiménez- está destrozado, y se dispone a regresar a Madrid con la amarga sensación del fracaso más estrepitoso de su carrera. Pero hoy es Jueves Santo, y en Sevilla, en Jueves Santo, puede pasar cualquier cosa…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 de Octubre del 2026 | A las 21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-asesino-de-la-regana-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El clavecín español, en Arcos de la Frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Concerto Málaga DURACIÓN: 60 minutos La característica que más ha llamado la atención de musicólogos e intérpretes sobre la música para teclado de Domenico Scarlatti ha sido la de poder reconocer rasgos propios de la música folclórica española, especialmente de Andalucía, en algunas de ellas. Scarlatti llegó a Sevilla con la princesa portuguesa María Bárbara, en 1729, el mismo año en el que nació Antonio Soler en Olot (Gerona, Cataluña). Durante los cuatro años siguientes, el período denominado Lustro Real (1729-1733), el alcázar de Sevilla sería la principal residencia de la corte española y ese tesoro andaluz que sigue inalterable aún en nuestros días, plagado de cantes y toques flamencos, enriqueció indudablemente la obra para clave de Scarlatti quien, a partir de este momento, se convertiría en un músico español. En 1756, Scarlatti empezó a relacionarse con el Padre Antonio Soler, cuya obra refleja más que ningún otro compositor la influencia del maestro italiano. No está claro si Soler fue realmente alumno de Scarlatti, ni tampoco si las lecciones que pudo tomar del italiano fueron esporádicas o más continuas, pero lo que parece evidente es que Soler se considera a sí mismo deudor de Scarlatti, aunque su fuerte personalidad sería suficiente para ir más allá que su maestro y crear una tipología y un estilo propios en el mundo de la sonata en plena transición del periodo preclásico al clasicismo como tal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 de Diciembre del 2026 | A las 12:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C. Corredera, 5, Arcos de la Frontera. Cádiz - Iglesia de San Juan de Dios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-clavecin-espanol-en-arcos-de-la-frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El crimen del palodú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Sofía Aguilar Producciones de Arte y Producciones Circulares DURACIÓN: 75m Estamos en la Feria del Abril del 2019, la última feria antes de la pandemia, cuando nadie podía ni imaginar la que se nos vendría encima. El agente Jiménez y el inspector Villanueva, que ya resolvieron con éxito -y a su manera- los asesinatos de la regañá, andan ahora enfrascados en otra investigación: Una nueva serie de crímenes tiene en jaque a Sevilla. El arma utilizada en esta ocasión es aún más peculiar, aunque las víctimas siguen siendo personas que, de una u otra manera, amenazan las tradiciones y la pureza de esta ciudad.
+    <t>19 de Septiembre del 2026 | A las 21:00</t>
+  </si>
+  <si>
+    <t>Plaza Artesanía, s/n, Guadalcacín. Cádiz - Teatro Municipal   "Julián Oslé Muñoz"</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-viento-es-salvaje-6</t>
+  </si>
+  <si>
+    <t>El asesino de la regañá</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Sofía Aguilar Producciones de Arte y Producciones Circulares DURACIÓN: 80 minutos Un asesino en serie tiene en jaque a la ciudad de Sevilla. Se trata de un misterioso criminal que asegura matar para preservar la pureza sevillana, de sevillanas maneras. Burlando una y otra vez la investigación policial, ya ha cometido siete asesinatos, firmados todos con el inconfundible sello de su peculiar arma homicida: una afilada cuña de regañá. El inspector Villanueva -llegado de Madrid para hacerse cargo del caso de la mano del muy sevillano agente Jiménez- está destrozado, y se dispone a regresar a Madrid con la amarga sensación del fracaso más estrepitoso de su carrera. Pero hoy es Jueves Santo, y en Sevilla, en Jueves Santo, puede pasar cualquier cosa…</t>
+  </si>
+  <si>
+    <t>10 de Octubre del 2026 | A las 21:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-asesino-de-la-regana-20</t>
+  </si>
+  <si>
+    <t>El clavecín español, en Arcos de la Frontera</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Concerto Málaga DURACIÓN: 60 minutos La característica que más ha llamado la atención de musicólogos e intérpretes sobre la música para teclado de Domenico Scarlatti ha sido la de poder reconocer rasgos propios de la música folclórica española, especialmente de Andalucía, en algunas de ellas. Scarlatti llegó a Sevilla con la princesa portuguesa María Bárbara, en 1729, el mismo año en el que nació Antonio Soler en Olot (Gerona, Cataluña). Durante los cuatro años siguientes, el período denominado Lustro Real (1729-1733), el alcázar de Sevilla sería la principal residencia de la corte española y ese tesoro andaluz que sigue inalterable aún en nuestros días, plagado de cantes y toques flamencos, enriqueció indudablemente la obra para clave de Scarlatti quien, a partir de este momento, se convertiría en un músico español. En 1756, Scarlatti empezó a relacionarse con el Padre Antonio Soler, cuya obra refleja más que ningún otro compositor la influencia del maestro italiano. No está claro si Soler fue realmente alumno de Scarlatti, ni tampoco si las lecciones que pudo tomar del italiano fueron esporádicas o más continuas, pero lo que parece evidente es que Soler se considera a sí mismo deudor de Scarlatti, aunque su fuerte personalidad sería suficiente para ir más allá que su maestro y crear una tipología y un estilo propios en el mundo de la sonata en plena transición del periodo preclásico al clasicismo como tal.</t>
+  </si>
+  <si>
+    <t>27 de Diciembre del 2026 | A las 12:00 horas</t>
+  </si>
+  <si>
+    <t>C. Corredera, 5, Arcos de la Frontera. Cádiz - Iglesia de San Juan de Dios</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-clavecin-espanol-en-arcos-de-la-frontera</t>
+  </si>
+  <si>
+    <t>El crimen del palodú</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Sofía Aguilar Producciones de Arte y Producciones Circulares DURACIÓN: 75m Estamos en la Feria del Abril del 2019, la última feria antes de la pandemia, cuando nadie podía ni imaginar la que se nos vendría encima. El agente Jiménez y el inspector Villanueva, que ya resolvieron con éxito -y a su manera- los asesinatos de la regañá, andan ahora enfrascados en otra investigación: Una nueva serie de crímenes tiene en jaque a Sevilla. El arma utilizada en esta ocasión es aún más peculiar, aunque las víctimas siguen siendo personas que, de una u otra manera, amenazan las tradiciones y la pureza de esta ciudad.
 Así que nos espera una intensa y estrambótica noche en el bar de Pepe. Sin salir de esas cuatro paredes, nuestros protagonistas harán un viaje en busca de respuestas, aunque quizá no solo encuentren lo que buscan, alguien quiere advertirles de algo relacionado con un virus que atacará al mundo. Venga ya, ¿un virus? Sí, sí, y el paciente menos uno, el primer portador del bicho que se propagará por todo el planeta, puede estar cerca...</t>
   </si>
   <si>
-    <t xml:space="preserve">12 de Agosto del 2026 | A las 21:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Nueva, 20, Chiclana de la Frontera. Cádiz - Teatro Moderno de Chiclana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-crimen-del-palodu-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El pianista de la mano izquierda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Asociación española del músico distonico DURACIÓN: 1.30 h Presentamos tres propuestas de comcierto solo para la mano izquierda En un ambiente muy íntimo, iluminado por una luz tenue, que enfoque en mi mano izquierda, y una pequeña velas en el fondo del piano. “ El arte de la mano izquierda” Un programa inédito, pensado solo para la mano izquierda, composiciones y arreglos inéditos a nivel mundial para la mano izquierda, algunas obras en vídeo y en Spotify, adjunto el link de las obras y canciones que en este momento están grabadas Aquí pueden ver una selección en mi canal de YouTube https://youtube.com/@manuellopezpiano236?si=TImz9VjdWM9p9kWo PRIMERA propuesta de Programación: Centrado en los grandes clásicos de toda la vida con obras de Beethoven, Liszt, Chopin ( Nocturnos adaptados al mano izquierda.) Joaquín Rodrigo ( Versión Propia para la mano izquierda del concierto de Aranjuez)., C. Debussy ( claro de luna), y nuestra música española ( Adaptaciones para izquierda.) de Albéniz, Granados, versiones inéditas como el Concierto de Aranjuez del maestro Rodrigo, los nocturnos de Chopin, el Claro de Luna de Debussy, solo para la mano izquierda. Primera parte BACH / BRAHMS Chacona en rem, BWV 10 https://youtu.be/HcDsXtqjOpU?si=pHiGIEgHuAMMcb0l BACH / GOUNOD Preludio en C mayor (Ave María) L.V. BEETHOVEN (1.er mov.) de la Sonata Claro de Luna en Do # menor F. CHOPIN (Arr. Manuel López) Preludio, Op.28 n 4 en Mi menor https://open.spotify.com/album/5VVgkGAtc7pV6HdIz5ISNp?si=Qw9Jmt5BSvGJRwQlbLe9qg Preludio, Op.28 n 7 en La mayor Nocturno, Op.9 n 2 en Mi bemol mayor https://youtu.be/6GxLk9yhJ18?si=P-45x3ytxe-aqoGg F. LISZT / ZICHY Sueño de Amor n 3 en La bemol mayor A. SCRIABIN Preludio y Nocturno para la mano izquierda, Op.9 Auditorio Nacional (Sala de Cámara) C. DEBUSSY (Arr. Manuel López) Arabesque M 1 en Mi mayor Claro de Luna de la "Suite bergamasque" en Re bemol mayor, 2ª parte Segunda parte LUDOVICO EINAUDI (Arr. Manuel López) Una Mattina Leo Nuvole Bianche M. LÓPEZ (Composición propia) Prelude for Margaret en Do menor E. GRANADOS (Arr. Manuel López) Danza Española n 2 - “La oriental” en Do menor Danza Española n 5 - “La Española” en Mi menor J. RODRIGO (Arr. Manuel López) Concierto de Aranjuez en Re mayor I. ALBÉNIZ (Arr. Manuel López) Asturias, de la Suite española en Sol menor SEGUNDA Propuesta de programación Se trata de un propuesta muy original con una mezcla, de cuatro estilos diferentes. Dedicado a los tributos de grandes neoclásicos: Yurima, Ludovico, canciones de época y bandas sonoras de sueño. Acabando con una segunda parte, rindiendo tributo a nuestro flamenco más actual: Paco de Lucía, Dorantes, Joaquín Rodrigo, Charo Domínguez y Felipe Campuzano. 1 parte - Yurima tributo * Rivers flow in you  * Kiss the rain  Banda sonora de película. ( John Williams , Hans Zimmer) Forest Gump Interestelar Piratas del caribe  Grandes éxitos de canciones. Élie Goulding  - Love Like You Do -  Elthon John -  Your song  Mecano - hijo de la luna Ludovico - Tributo  ( reducciones propias para la mano izquierda)  * Una Martina ( link al auditorio Nacional) * Leo ( link Spotify)  * Nuevo Bianche  * Divenire  Cold play  - A start Full of Sky  2 parte  - tributo a nuestra música española, Y nuestros flamenco más actual. Joaquin, Rodrigo - El concierto de Aranjuez vs para la mano izquierda ( link a YouTube Rodrigo)  M Lopez, composición propia - for Margaret Paco de Lucía - Entre dos aguas   Dorantes - Obroy   Felipe Campuzano, las Salinas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 de Octubre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-pianista-de-la-mano-izquierda-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espacios, en Conil de la Frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Nacho Loring DURACIÓN: 1h 15min El programa de este espectáculo es el álbum Espacios de Nacho Loring al completo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 de Octubre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/espacios-en-conil-de-la-frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espejo de las estrellas (Desirée Martín &amp; Juan Manuel Román)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El próximo viernes 7 de agosto, El Jardín de Berta acogerá el concierto "Espejo de las Estrellas", un proyecto musical de la multinstrumentista y cantante Desirée Martín y el contrabajista Juan Manuel Román, que ofrecerá un viaje sonoro singular a través del folclore y la tradición oral de la Península Ibérica. El programa nace de la idea de que muchas de las letras de nuestro folklore se dirigen a los elementos naturales (el mar, la luna, las estrellas...) como si fuesen seres animados que nos pueden comprender, y a quienes dirigir nuestras emociones y nuestros cantos. Con una delicada instrumentación que entrelaza el arpa celta, la flauta travesera y la profundidad del contrabajo, el dúo reinterpretará cantigas medievales, melodías sefardíes y cantos tradicionales. Una velada íntima bajo el cielo estrellado de Jerez para conectar la música ancestral con la naturaleza y la emoción contemporánea. Martín &amp; Román han sido ganadores del 1º premio en la edición 2026 del Trebufestival. El dúo, que nació en 2025, ha actuado por diversos escenarios de Andalucía, Cáceres y Madrid, con muy buena acogida por su propuesta innovadora, sensibilidad y cercanía con el público. Las entradas tienen un precio de 12€ y se adquieren en la puerta. Rerservas telf. 614 330 883 · 636 960 019 · 660 750 490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 de Agosto del 2026 | 21:30h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C/ Caballeros, 36, Jerez de la Frontera. Cádiz - El Jardín de Berta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/espejo-de-las-estrellas-desiree-martin-juan-manuel-roman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exiliada. Mujeres en el arte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Saudade Música DURACIÓN: 60 minutos Desde que somos pequeñas, en el conservatorio nos llenan la cabeza de nombres de compositores y los libros de historia se llenan de párrafos hablando de la gran contribución a los cambios musicales de cada época que realizó cada uno de esos hombres. ¿Y las mujeres? Qué extraño que sólo sean dos nombres femeninos los que se citan en el 8M y qué casualidad que sean la "esposa de" o "hija de". Las mujeres estuvieron; las mujeres crearon; las mujeres interpretaron. Y es por ello que cremos necesario tomar esos fantasmas invisibles en que convirtieron a tantas y traer a algunas del exilio artístico en el que se desarrollaron, porque, la verdad es que la obra de todas ellas no cabría en una vida de espectáculo. Nuestro concierto nace de una visión empática y se desarrolla por una necesidad de verdad. Somos mujeres que, a través de nuestra mirada y desde la humildad, creemos necesaria esta pequeña reivindicación del arte de otras que lucharon por vivir de su pasión.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 de Octubre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza Romero Martínez, s/n, Jerez de la Frontera. Cádiz - Teatro Villamarta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exiliada-mujeres-en-el-arte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exposición en Rota: RotArte 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El salón multiusos del Palacio Municipal Castillo de Luna acoge desde el jueves 16 de julio la exposición colectiva "RotArte 2026", una iniciativa organizada por la Sección de Artes Plásticas del Ateneo de Rota dentro de la programación del verano cultural de la localidad. La muestra, que cuenta con la colaboración de la Delegación de Cultura y Patrimonio Histórico del Ayuntamiento de Rota, reúne obras de pintura, escultura y acuarela de los artistas Raquel Suero, Lola Torrado, Esther Ezcurra, Lola Morales y Julio Malvido, poniendo en valor la riqueza y diversidad del arte local. La exposición podrá visitarse hasta el 31 de julio, en horario de 10:00 a 14:00 horas y de 18:00 a 22:00 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 de Julio del 2026 - 31 de Julio del 2026 | De 10:00 a 14:00 horas y de 18:00 a 22:00 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Cuna, 2, Rota. Cádiz - Palacio Municipal Castillo de Luna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exposicion-en-rota-rotarte-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exposición permanente 'El Valle de los Caídos' (1980-1987), de Costus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una muestra compuesta por un total de 19 piezas de la serie realizadas en acrílico sobre tabla y enmarcadas dentro del estilo Pop, destacando su riqueza cromática y efectos lumínicos. La muestra se complementa con piezas que ayudan a contextualizar la evolución e importancia de estos artistas, en lo que posteriormente algunos denominarán movida madrileña de los años 80.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Enero del 2024 - 31 de Diciembre del 2034 | De lunes a sábado de 11 a 21 horas y domingos y festivos de 11 a 15 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paseo Carlos III, 5. SALA 5, Cádiz. Cádiz - Espacio de Cultura Contemporánea de Cádiz - ECCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exposicion-permanente-el-valle-de-los-caidos-1980-1987-de-costus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Festival de Jazz de Baelo Claudia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva en la web del Conjunto (días antes de cada concierto). Aforo limitado (350 personas).
+    <t>12 de Agosto del 2026 | A las 21:30</t>
+  </si>
+  <si>
+    <t>Calle Nueva, 20, Chiclana de la Frontera. Cádiz - Teatro Moderno de Chiclana</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-crimen-del-palodu-21</t>
+  </si>
+  <si>
+    <t>El pianista de la mano izquierda</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Asociación española del músico distonico DURACIÓN: 1.30 h Presentamos tres propuestas de comcierto solo para la mano izquierda En un ambiente muy íntimo, iluminado por una luz tenue, que enfoque en mi mano izquierda, y una pequeña velas en el fondo del piano. “ El arte de la mano izquierda” Un programa inédito, pensado solo para la mano izquierda, composiciones y arreglos inéditos a nivel mundial para la mano izquierda, algunas obras en vídeo y en Spotify, adjunto el link de las obras y canciones que en este momento están grabadas Aquí pueden ver una selección en mi canal de YouTube https://youtube.com/@manuellopezpiano236?si=TImz9VjdWM9p9kWo PRIMERA propuesta de Programación: Centrado en los grandes clásicos de toda la vida con obras de Beethoven, Liszt, Chopin ( Nocturnos adaptados al mano izquierda.) Joaquín Rodrigo ( Versión Propia para la mano izquierda del concierto de Aranjuez)., C. Debussy ( claro de luna), y nuestra música española ( Adaptaciones para izquierda.) de Albéniz, Granados, versiones inéditas como el Concierto de Aranjuez del maestro Rodrigo, los nocturnos de Chopin, el Claro de Luna de Debussy, solo para la mano izquierda. Primera parte BACH / BRAHMS Chacona en rem, BWV 10 https://youtu.be/HcDsXtqjOpU?si=pHiGIEgHuAMMcb0l BACH / GOUNOD Preludio en C mayor (Ave María) L.V. BEETHOVEN (1.er mov.) de la Sonata Claro de Luna en Do # menor F. CHOPIN (Arr. Manuel López) Preludio, Op.28 n 4 en Mi menor https://open.spotify.com/album/5VVgkGAtc7pV6HdIz5ISNp?si=Qw9Jmt5BSvGJRwQlbLe9qg Preludio, Op.28 n 7 en La mayor Nocturno, Op.9 n 2 en Mi bemol mayor https://youtu.be/6GxLk9yhJ18?si=P-45x3ytxe-aqoGg F. LISZT / ZICHY Sueño de Amor n 3 en La bemol mayor A. SCRIABIN Preludio y Nocturno para la mano izquierda, Op.9 Auditorio Nacional (Sala de Cámara) C. DEBUSSY (Arr. Manuel López) Arabesque M 1 en Mi mayor Claro de Luna de la "Suite bergamasque" en Re bemol mayor, 2ª parte Segunda parte LUDOVICO EINAUDI (Arr. Manuel López) Una Mattina Leo Nuvole Bianche M. LÓPEZ (Composición propia) Prelude for Margaret en Do menor E. GRANADOS (Arr. Manuel López) Danza Española n 2 - “La oriental” en Do menor Danza Española n 5 - “La Española” en Mi menor J. RODRIGO (Arr. Manuel López) Concierto de Aranjuez en Re mayor I. ALBÉNIZ (Arr. Manuel López) Asturias, de la Suite española en Sol menor SEGUNDA Propuesta de programación Se trata de un propuesta muy original con una mezcla, de cuatro estilos diferentes. Dedicado a los tributos de grandes neoclásicos: Yurima, Ludovico, canciones de época y bandas sonoras de sueño. Acabando con una segunda parte, rindiendo tributo a nuestro flamenco más actual: Paco de Lucía, Dorantes, Joaquín Rodrigo, Charo Domínguez y Felipe Campuzano. 1 parte - Yurima tributo * Rivers flow in you  * Kiss the rain  Banda sonora de película. ( John Williams , Hans Zimmer) Forest Gump Interestelar Piratas del caribe  Grandes éxitos de canciones. Élie Goulding  - Love Like You Do -  Elthon John -  Your song  Mecano - hijo de la luna Ludovico - Tributo  ( reducciones propias para la mano izquierda)  * Una Martina ( link al auditorio Nacional) * Leo ( link Spotify)  * Nuevo Bianche  * Divenire  Cold play  - A start Full of Sky  2 parte  - tributo a nuestra música española, Y nuestros flamenco más actual. Joaquin, Rodrigo - El concierto de Aranjuez vs para la mano izquierda ( link a YouTube Rodrigo)  M Lopez, composición propia - for Margaret Paco de Lucía - Entre dos aguas   Dorantes - Obroy   Felipe Campuzano, las Salinas</t>
+  </si>
+  <si>
+    <t>02 de Octubre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-pianista-de-la-mano-izquierda-1</t>
+  </si>
+  <si>
+    <t>Espacios, en Conil de la Frontera</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Nacho Loring DURACIÓN: 1h 15min El programa de este espectáculo es el álbum Espacios de Nacho Loring al completo.</t>
+  </si>
+  <si>
+    <t>10 de Octubre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/espacios-en-conil-de-la-frontera</t>
+  </si>
+  <si>
+    <t>Espejo de las estrellas (Desirée Martín &amp; Juan Manuel Román)</t>
+  </si>
+  <si>
+    <t>El próximo viernes 7 de agosto, El Jardín de Berta acogerá el concierto "Espejo de las Estrellas", un proyecto musical de la multinstrumentista y cantante Desirée Martín y el contrabajista Juan Manuel Román, que ofrecerá un viaje sonoro singular a través del folclore y la tradición oral de la Península Ibérica. El programa nace de la idea de que muchas de las letras de nuestro folklore se dirigen a los elementos naturales (el mar, la luna, las estrellas...) como si fuesen seres animados que nos pueden comprender, y a quienes dirigir nuestras emociones y nuestros cantos. Con una delicada instrumentación que entrelaza el arpa celta, la flauta travesera y la profundidad del contrabajo, el dúo reinterpretará cantigas medievales, melodías sefardíes y cantos tradicionales. Una velada íntima bajo el cielo estrellado de Jerez para conectar la música ancestral con la naturaleza y la emoción contemporánea. Martín &amp; Román han sido ganadores del 1º premio en la edición 2026 del Trebufestival. El dúo, que nació en 2025, ha actuado por diversos escenarios de Andalucía, Cáceres y Madrid, con muy buena acogida por su propuesta innovadora, sensibilidad y cercanía con el público. Las entradas tienen un precio de 12€ y se adquieren en la puerta. Rerservas telf. 614 330 883 · 636 960 019 · 660 750 490</t>
+  </si>
+  <si>
+    <t>07 de Agosto del 2026 | 21:30h</t>
+  </si>
+  <si>
+    <t>C/ Caballeros, 36, Jerez de la Frontera. Cádiz - El Jardín de Berta</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/espejo-de-las-estrellas-desiree-martin-juan-manuel-roman</t>
+  </si>
+  <si>
+    <t>Exiliada. Mujeres en el arte.</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Saudade Música DURACIÓN: 60 minutos Desde que somos pequeñas, en el conservatorio nos llenan la cabeza de nombres de compositores y los libros de historia se llenan de párrafos hablando de la gran contribución a los cambios musicales de cada época que realizó cada uno de esos hombres. ¿Y las mujeres? Qué extraño que sólo sean dos nombres femeninos los que se citan en el 8M y qué casualidad que sean la "esposa de" o "hija de". Las mujeres estuvieron; las mujeres crearon; las mujeres interpretaron. Y es por ello que cremos necesario tomar esos fantasmas invisibles en que convirtieron a tantas y traer a algunas del exilio artístico en el que se desarrollaron, porque, la verdad es que la obra de todas ellas no cabría en una vida de espectáculo. Nuestro concierto nace de una visión empática y se desarrolla por una necesidad de verdad. Somos mujeres que, a través de nuestra mirada y desde la humildad, creemos necesaria esta pequeña reivindicación del arte de otras que lucharon por vivir de su pasión.</t>
+  </si>
+  <si>
+    <t>29 de Octubre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>Plaza Romero Martínez, s/n, Jerez de la Frontera. Cádiz - Teatro Villamarta</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exiliada-mujeres-en-el-arte</t>
+  </si>
+  <si>
+    <t>Exposición en Rota: RotArte 2026</t>
+  </si>
+  <si>
+    <t>El salón multiusos del Palacio Municipal Castillo de Luna acoge desde el jueves 16 de julio la exposición colectiva "RotArte 2026", una iniciativa organizada por la Sección de Artes Plásticas del Ateneo de Rota dentro de la programación del verano cultural de la localidad. La muestra, que cuenta con la colaboración de la Delegación de Cultura y Patrimonio Histórico del Ayuntamiento de Rota, reúne obras de pintura, escultura y acuarela de los artistas Raquel Suero, Lola Torrado, Esther Ezcurra, Lola Morales y Julio Malvido, poniendo en valor la riqueza y diversidad del arte local. La exposición podrá visitarse hasta el 31 de julio, en horario de 10:00 a 14:00 horas y de 18:00 a 22:00 horas.</t>
+  </si>
+  <si>
+    <t>16 de Julio del 2026 - 31 de Julio del 2026 | De 10:00 a 14:00 horas y de 18:00 a 22:00 horas.</t>
+  </si>
+  <si>
+    <t>Calle Cuna, 2, Rota. Cádiz - Palacio Municipal Castillo de Luna</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exposicion-en-rota-rotarte-2026</t>
+  </si>
+  <si>
+    <t>Exposición permanente 'El Valle de los Caídos' (1980-1987), de Costus</t>
+  </si>
+  <si>
+    <t>Una muestra compuesta por un total de 19 piezas de la serie realizadas en acrílico sobre tabla y enmarcadas dentro del estilo Pop, destacando su riqueza cromática y efectos lumínicos. La muestra se complementa con piezas que ayudan a contextualizar la evolución e importancia de estos artistas, en lo que posteriormente algunos denominarán movida madrileña de los años 80.</t>
+  </si>
+  <si>
+    <t>01 de Enero del 2024 - 31 de Diciembre del 2034 | De lunes a sábado de 11 a 21 horas y domingos y festivos de 11 a 15 horas.</t>
+  </si>
+  <si>
+    <t>Paseo Carlos III, 5. SALA 5, Cádiz. Cádiz - Espacio de Cultura Contemporánea de Cádiz - ECCO</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exposicion-permanente-el-valle-de-los-caidos-1980-1987-de-costus</t>
+  </si>
+  <si>
+    <t>Festival de Jazz de Baelo Claudia</t>
+  </si>
+  <si>
+    <t>Reserva en la web del Conjunto (días antes de cada concierto). Aforo limitado (350 personas).
 El Festival de Jazz de Baelo Claudia comenzará el 23 de julio de 2026 en el Conjunto Arqueológico de Baelo Claudia. Concierto: “Festival Baelo Jazz”. Primer concierto. Fecha y hora:  jueves 23 de julio (21:30 h) Público: Público adulto. Descripción: Comenzamos la 3ª edición del Festival Baelo Jazz con Jorge Pardo Trío. Concierto: “Festival Baelo Jazz”. Segundo concierto. Fecha y hora:  jueves 30 de julio (21:30 h) Público: Público adulto. Descripción: Segundo concierto de la 3ª edición del Festival Baelo Jazz con el Trio Garum y Paula Bilá Concierto: “Festival Baelo Jazz”. Tercer concierto. Fecha y hora:  jueves 6 de agosto (21:30 h.) Público: Público adulto. Descripción: Finalizamos la 3ª edición del Festival Baelo Jazz con el concierto del grupo Piet Bervist y la participación de la cantante Alicia Carrasco.</t>
   </si>
   <si>
-    <t xml:space="preserve">23 de Julio del 2026 - 06 de Agosto del 2026 | 21:30 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 de Julio del 2026 - 06 de Agosto del 2026 21:30 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/festival-de-jazz-de-baelo-claudia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiestas de la Urta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Fiesta de la Urta es declarada de Interés Turístico Nacional de Andalucía y se celebra durante cuatro días a principios del mes de Agosto. Para la ocasión se montan diversas casetas, una pequeña zona de atracciones y un gran escenario en el que actuarán cantautores andaluces, animación infantil, etc Uno de dichos días está dedicado a la urta, celebrándose un concurso de preparación, presentación y posterior degustación del típico plato de nuestra Villa: Urta a la Roteña.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 de Julio del 2026 - 02 de Agosto del 2026 | Consultar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">, Rota. Cádiz - Varios lugares en el municipio, Rota, Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiestas y tradiciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/fiestas-de-la-urta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floridance festival en Rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El festival destacado en la región seleccionada es el Floridance Fest 2026 . A continuación, encontrarás los detalles clave del evento y los artistas confirmados en este avance de cartel: Información básica Fecha: Sábado 05 de septiembre de 2026. Lugar: Estadio Municipal Antonio Pazos Puyana "Monago", Rota (Cádiz). Horario: De 18:00h a 07:00h. Restricción: Prohibida la entrada a menores de 18 años. Avance del cartel (Lineup) La Gore Atomic Hooligan DJ Man vs DJ Shemma Tortu / Bad Legs Aldo Ferrari / Perfect Kombo Maribel / Rueda / Killerblitz Leeroy Thornhill (Ex-Prodigy) Anuschka / Norbak Yo Speed / Wally Tilla Pink / Kill2Beat Deekbass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 de Septiembre del 2026 | Horario de 19:00h a 07:00h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avenida de la Diputación, 164, Rota. Cádiz - Estadio Municipal Alcalde Navarro Flores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/floridance-festival-en-rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gran noche de carnaval, en Rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evento carnavalesco en Rota, Cádiz. Se trata de la "Gran Noche de Carnaval" dentro de las Noches de Rota. La función está programada para el 15 de agosto de 2026 a las 22:00h en el C.E.I.P. Maestro Eduardo Lobillo. Incluye las actuaciones de DSAS3, Los Amish del Mono, SSSHHHHH!! Los Saeteros, y Los Locos. Entradas: Las entradas se pueden adquirir a través de giglon.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 de Agosto del 2026 | A las 22:00 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Neptuno, 4, Rota. Cádiz - Colegio Público Maestro Eduardo Lobillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/gran-noche-de-carnaval-en-rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guitarricadelafuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guitarricadelafuente… Muchos son los elementos de Álvaro Lafuente que remiten a sus raíces, comenzando por el diminutivo de su nombre artístico, que fluye desde el pueblo aragonés de sus abuelos. O esa inseparable guitarra acústica que también le bautizó. Por eso la sofisticación que afronta adquiere en su música una dimensión especial: fascinante y seductora. El Guitarrica de 2021 se doctora desde una originalidad extrema, la misma que le convierte en uno de los artistas más prometedores de nueva década.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 de Agosto del 2026 | 22:00 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/guitarricadelafuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historia de la luz eléctrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De martes a sábado de 20 a 23 horas, entrada libre, hasta el 8 de agosto.
+    <t>23 de Julio del 2026 - 06 de Agosto del 2026 | 21:30 horas</t>
+  </si>
+  <si>
+    <t>23 de Julio del 2026 - 06 de Agosto del 2026 21:30 horas</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/festival-de-jazz-de-baelo-claudia</t>
+  </si>
+  <si>
+    <t>Fiestas de la Urta</t>
+  </si>
+  <si>
+    <t>La Fiesta de la Urta es declarada de Interés Turístico Nacional de Andalucía y se celebra durante cuatro días a principios del mes de Agosto. Para la ocasión se montan diversas casetas, una pequeña zona de atracciones y un gran escenario en el que actuarán cantautores andaluces, animación infantil, etc Uno de dichos días está dedicado a la urta, celebrándose un concurso de preparación, presentación y posterior degustación del típico plato de nuestra Villa: Urta a la Roteña.</t>
+  </si>
+  <si>
+    <t>30 de Julio del 2026 - 02 de Agosto del 2026 | Consultar.</t>
+  </si>
+  <si>
+    <t>, Rota. Cádiz - Varios lugares en el municipio, Rota, Cádiz</t>
+  </si>
+  <si>
+    <t>Fiestas y tradiciones</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/fiestas-de-la-urta</t>
+  </si>
+  <si>
+    <t>Floridance festival en Rota</t>
+  </si>
+  <si>
+    <t>El festival destacado en la región seleccionada es el Floridance Fest 2026 . A continuación, encontrarás los detalles clave del evento y los artistas confirmados en este avance de cartel: Información básica Fecha: Sábado 05 de septiembre de 2026. Lugar: Estadio Municipal Antonio Pazos Puyana "Monago", Rota (Cádiz). Horario: De 18:00h a 07:00h. Restricción: Prohibida la entrada a menores de 18 años. Avance del cartel (Lineup) La Gore Atomic Hooligan DJ Man vs DJ Shemma Tortu / Bad Legs Aldo Ferrari / Perfect Kombo Maribel / Rueda / Killerblitz Leeroy Thornhill (Ex-Prodigy) Anuschka / Norbak Yo Speed / Wally Tilla Pink / Kill2Beat Deekbass</t>
+  </si>
+  <si>
+    <t>05 de Septiembre del 2026 | Horario de 19:00h a 07:00h</t>
+  </si>
+  <si>
+    <t>Avenida de la Diputación, 164, Rota. Cádiz - Estadio Municipal Alcalde Navarro Flores</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/floridance-festival-en-rota</t>
+  </si>
+  <si>
+    <t>Gran noche de carnaval, en Rota</t>
+  </si>
+  <si>
+    <t>Evento carnavalesco en Rota, Cádiz. Se trata de la "Gran Noche de Carnaval" dentro de las Noches de Rota. La función está programada para el 15 de agosto de 2026 a las 22:00h en el C.E.I.P. Maestro Eduardo Lobillo. Incluye las actuaciones de DSAS3, Los Amish del Mono, SSSHHHHH!! Los Saeteros, y Los Locos. Entradas: Las entradas se pueden adquirir a través de giglon.com</t>
+  </si>
+  <si>
+    <t>15 de Agosto del 2026 | A las 22:00 h.</t>
+  </si>
+  <si>
+    <t>Calle Neptuno, 4, Rota. Cádiz - Colegio Público Maestro Eduardo Lobillo</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/gran-noche-de-carnaval-en-rota</t>
+  </si>
+  <si>
+    <t>Guitarricadelafuente</t>
+  </si>
+  <si>
+    <t>Guitarricadelafuente… Muchos son los elementos de Álvaro Lafuente que remiten a sus raíces, comenzando por el diminutivo de su nombre artístico, que fluye desde el pueblo aragonés de sus abuelos. O esa inseparable guitarra acústica que también le bautizó. Por eso la sofisticación que afronta adquiere en su música una dimensión especial: fascinante y seductora. El Guitarrica de 2021 se doctora desde una originalidad extrema, la misma que le convierte en uno de los artistas más prometedores de nueva década.</t>
+  </si>
+  <si>
+    <t>09 de Agosto del 2026 | 22:00 h.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/guitarricadelafuente</t>
+  </si>
+  <si>
+    <t>Historia de la luz eléctrica</t>
+  </si>
+  <si>
+    <t>De martes a sábado de 20 a 23 horas, entrada libre, hasta el 8 de agosto.
 "Historia de la luz eléctrica" es una muestra donde trece artistas exploran en El Puerto de Santa María cómo la luz transformó la mirada sobre la pintura. El Palacete Fernán Caballero acoge un proyecto que pone en diálogo el patrimonio de la ciudad con la creación contemporánea. El proyecto parte de una premisa central: la historia de la pintura es, en el fondo, la historia de la luz. Antes de la iluminación eléctrica, los cuadros y los objetos devocionales solo existían bajo luces naturales, litúrgicas o de vela, envueltos en un misterio y una penumbra que formaban parte inseparable de su sentido. La llegada de la luz artificial cambió radicalmente esa relación: bajo un foco blanco y uniforme, la imagen se vuelve más nítida, pero también pierde parte de su masa, su textura y su capacidad de sugerir. Frente a esa claridad que “vende” y “aplana” lo pintado, el proyecto reivindica la penumbra como el espacio donde la pintura recupera su misterio y su presencia física, en un recorrido que va del museo a oscuras hasta el objeto devocional, y de ahí a la sala de exposición contemporánea. La muestra reúne obra de Carlos Pesudo (Castellón, 1992), Armando (Gijón, 1928), Narowé (Brasil, 1993), Luis Vasallo (Madrid, 1981), Ana Cubero (España), un Anónimo andaluz del siglo XVIII, Mateo Paccella (Argentina), Cristina de Miguel (Sevilla, 1987), Maillo (Getafe, 1987), Rubén Guerrero (Utrera, Sevilla, 1976), Julia Santa Olalla (Granada, 1985), Eloy Arribas (Valladolid, 1992) y Sergio Gómez, Srger (Sevilla). Trece artistas de generaciones, procedencias y trayectorias muy distintas.</t>
   </si>
   <si>
-    <t xml:space="preserve">11 de Julio del 2026 - 08 de Agosto del 2026 | De 20:00 a 23:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Fernán Caballero 6, El Puerto de Santa María. Cádiz - Palacete Fernán Caballero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/historia-de-la-luz-electrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invisible y todas las demás</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Alas Circo Teatro DURACIÓN: 50min María vive feliz en su propio mundo, en su burbuja¿particular. Todo parece encajar en una perfecta rutina diaria y así pasan los minutos, las horas y los días. 
+    <t>11 de Julio del 2026 - 08 de Agosto del 2026 | De 20:00 a 23:00 horas</t>
+  </si>
+  <si>
+    <t>Calle Fernán Caballero 6, El Puerto de Santa María. Cádiz - Palacete Fernán Caballero</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/historia-de-la-luz-electrica</t>
+  </si>
+  <si>
+    <t>Invisible y todas las demás</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Alas Circo Teatro DURACIÓN: 50min María vive feliz en su propio mundo, en su burbuja¿particular. Todo parece encajar en una perfecta rutina diaria y así pasan los minutos, las horas y los días. 
 Y tal como el hombre de la caverna de Platón que descubre realidad más allá de esas proyecciones y sombras, María abre los ojos y comprende que es presa de un destino que ella misma ha creado. 
 Comienza a pensar por qué su vida es la que tiene. y que únicamente depende de una misma ver una nueva frontera y realidad.¿no vale vivir sentenciada por una cuestión de género y por eso, renuncia a seguir viviendo en otra burbuja más. 
 Invisible y TODAS LAS DEMÁS: es María y todas esas mujeres que la acompañan de manera inherente por el¿hecho de formar parte de una familia. Hilos que siguen entrelazados de manera invisible con la abuela, la madre, hermanas, hijas...La mujer ni está sola ni es una sola</t>
   </si>
   <si>
-    <t xml:space="preserve">25 de Septiembre del 2026 | 19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Amargura, nº 59, Puerto Real. Cádiz - Teatro Principal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/invisible-y-todas-las-demas-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joana Jiménez, en Rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artista: Joana Jiménez, cantante española reconocida por ganar la primera edición del concurso musical "Se llama copla" de Canal Sur. Espectáculo: Noches de Rota: Joana Jiménez. Gira 2026. Fecha y Hora: 13 de agosto de 2026 a las 22:00h. Lugar: Colegio Eduardo Lobillo en Rota, Cádi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 de Agosto del 2026 | A las 22:00 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/joana-jimenez-en-rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Amodeo, en Rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"013 Origen". Contenido: Humor rápido, improvisación y reflexiones personales sobre su infancia y el barrio. Gira 2026: El show se está presentando en diversas ciudades de España durante 2026, incluyendo Santander, Mijas y Mérida. Entradas: Se pueden adquirir a través de plataformas como Giglon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 de Agosto del 2026 | A las 22:00 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juan-amodeo-en-rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Medina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: JAZZ WORLD ELECTRONIC DURACIÓN: 80 minutos Juan Medina, vuelve con fuerza con un nuevo proyecto de flamenco y jazz, liderando a manos de su guitarra, un excepcional cuarteto formado por artistas de primer nivel. Con la salida de su próximo disco, “FUGAZ”, el artista gaditano dará a conocer otro de sus grandes talentos y pasiones, la guitarra flamenca en todo su esplendor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 de Octubre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juan-medina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juanita con mayúsculas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Helena Amado y Pepe Fernández DURACIÓN: 60 minutos —Sinopsis Este proyecto nace del compromiso interpretativo y de la sensibilidad compartida entre Helena Amado y Pepe Fernández, ambos unidos en la recuperación y adaptación escénica de repertorios tradicionales desde una perspectiva camerística. La propuesta se articula como un recorrido íntimo y profundamente emocional por la figura de Juanita Reina, símbolo de la copla andaluza. Desde una perspectiva actual, Amado y Fernández abordan una selección de sus obras más emblemáticas, reivindicando su valor poético, musical y escénico. —Programa Juanita con mayúsculas Francisco Alegre (Antonio Quintero, Rafael de León y Manuel Quiroga) Y sin embargo te quiero (Antonio Quintero, Rafael de León y Manuel Quiroga) Carmen de España (Rafael de León y Manuel Quiroga) Lola la Piconera (Antonio Quintero, Rafael de León y Manuel Quiroga) Doña Mariquita de los Dolores (Rafael de León y Manuel Quiroga) Compuesta y sin novio (Antonio Quintero, Rafael de León y Manuel Quiroga) Tururú (Antonio Quintero, Rafael de León y Manuel Quiroga) Capote de grana y oro (Antonio Quintero, Rafael de León y Manuel Quiroga) Yo soy… esa (Antonio Quintero, Rafael de León y Manuel Quiroga) Una Cantaora (Antonio Quintero y Manuel Quiroga) Lagartijera (Antonio Quintero, Rafael de León y Manuel Quiroga) Soltera yo no me quedo (Rafael León y Antonio Quintero) Ni hablar del peluquín (Antonio Quintero, Rafael de León y Manuel Quiroga) Filigrana de oro puro (Antonio Quintero, Rafael de León y Manuel Quiroga) —</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Cadenas, s/n, Arcos de la Frontera. Cádiz - Plaza del Cananeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juanita-con-mayusculas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LXV Festival Flamenco Velada de las Nieves en Arcos de la Frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LXV FESTIVAL FLAMENCO VELADAS DE LAS NIEVES 3 y 4 de agosto de 2026 La localidad gaditana de Arcos de la Frontera acoge el 3 y 4 de agosto la LVX edición de su Festival Flamenco Velada de las Nieves. Se le entregará la Medalla de Oro del Festival a Manuel Gallardo Barroso "Manolo Zapata". La programación, que cuenta con la colaboración del Instituto Andaluz del Flamenco, es la siguiente: 3 de agosto, 22:00 horas, Atrio de San Pedro. Ana de Caro con la guitarra de Javier Ibáñez. 4 de agosto, 22:00 horas, Plaza del Cabildo: Al baile, Titi Flores. Al cante: Jesús Méndez con la guitarra de Antonio Higuero. María Terremoto con la guitarra de Nono Jero. Manuel Moreno "El Pele" con la guitarra de Niño Seve. Artista invitado al baile: Farruquito.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03 de Agosto del 2026 - 04 de Agosto del 2026 | 22:00 horas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">, Arcos de la Frontera. Cádiz - Varios lugares en el municipio, Arcos de la Frontera, Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/lxv-festival-flamenco-velada-de-las-nieves-en-arcos-de-la-frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Coquette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Kanbahiota Troup. DURACIÓN: 50 min Una gran estrella de circo “La Coquette" de los años 50 viene dispuesta a triunfar , para ello su partener, el cual es el encargado de tener todo preparado intenta salvar todos los problemas que le surgen , siempre esperando contentarla y enamorarla . Van superando los obstáculos para finalmente realizar el gran número de trapecio entre los dos. Espectáculos en clave de clown , donde la técnica de circo , la magia y sobre todo el humor se entre mezclan para el disfrute de todos los público .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 de Diciembre del 2026 | A las 12:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paseo de Andalucía, s/n, Arcos de la Frontera. Cádiz - Explanada biblioteca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-coquette-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Gallina de los huevos de oro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Zum Zum Teatre. DURACIÓN: 50 ¿os gusta el dinero? ¿mucho? Los granjeros de esta historia no perdían el tiempo pensando en el dinero y siempre repartían lo poco que tenían con quien más lo necesitaba, pero un día una gallina llegó a su granja y puso un huevo de oro. ¿Os imaginais si os pasara a vosotros? LA GALLINA DE LOS HUEVOS DE ORO es una historia que cuenta que el dinero es un "cuento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 de Noviembre del 2026 | A las 12:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Av. San Fernando, 79, Rota. Cádiz - Teatro Municipal Alcalde Felipe Benítez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-gallina-de-los-huevos-de-oro-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina Brava</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Las Niñas de Cádiz DURACIÓN: 75 minutos Esta es la historia de un magnicidio. El asesinato de una reina a la que todos odian pero a la que nadie se atreve a enfrentar cara a cara.Solo una madre, movida por el ansia de venganza, será capaz de saltarse todas las normas, dando muerte sin ningún tipo de misericordia a la mujer que ha destrozado la vida de su hija. Luego vendrán el revuelo, la conmoción, un juicio vergonzante en el que todos miente, y una implacable condena al olvido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paseo de la Alameda, s/n, Tarifa. Cádiz - Teatro Municipal Alameda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-reina-brava-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 de Octubre del 2026 | A las 19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-reina-brava-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La venganza de Don Mendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: El perro producciones DURACIÓN: 90 Pedro Muñoz Seca escribió más de 300 obras pero es esencialmente conocido por LA VENGANZA DE DON MENDO, una comedia que se asienta sobre dos grandes
+    <t>25 de Septiembre del 2026 | 19:00</t>
+  </si>
+  <si>
+    <t>Calle Amargura, nº 59, Puerto Real. Cádiz - Teatro Principal</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/invisible-y-todas-las-demas-0</t>
+  </si>
+  <si>
+    <t>Joana Jiménez, en Rota</t>
+  </si>
+  <si>
+    <t>Artista: Joana Jiménez, cantante española reconocida por ganar la primera edición del concurso musical "Se llama copla" de Canal Sur. Espectáculo: Noches de Rota: Joana Jiménez. Gira 2026. Fecha y Hora: 13 de agosto de 2026 a las 22:00h. Lugar: Colegio Eduardo Lobillo en Rota, Cádi</t>
+  </si>
+  <si>
+    <t>13 de Agosto del 2026 | A las 22:00 h.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/joana-jimenez-en-rota</t>
+  </si>
+  <si>
+    <t>Juan Amodeo, en Rota</t>
+  </si>
+  <si>
+    <t>"013 Origen". Contenido: Humor rápido, improvisación y reflexiones personales sobre su infancia y el barrio. Gira 2026: El show se está presentando en diversas ciudades de España durante 2026, incluyendo Santander, Mijas y Mérida. Entradas: Se pueden adquirir a través de plataformas como Giglon</t>
+  </si>
+  <si>
+    <t>14 de Agosto del 2026 | A las 22:00 h.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juan-amodeo-en-rota</t>
+  </si>
+  <si>
+    <t>Juan Medina</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: JAZZ WORLD ELECTRONIC DURACIÓN: 80 minutos Juan Medina, vuelve con fuerza con un nuevo proyecto de flamenco y jazz, liderando a manos de su guitarra, un excepcional cuarteto formado por artistas de primer nivel. Con la salida de su próximo disco, “FUGAZ”, el artista gaditano dará a conocer otro de sus grandes talentos y pasiones, la guitarra flamenca en todo su esplendor.</t>
+  </si>
+  <si>
+    <t>02 de Octubre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juan-medina</t>
+  </si>
+  <si>
+    <t>Juanita con mayúsculas</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Helena Amado y Pepe Fernández DURACIÓN: 60 minutos —Sinopsis Este proyecto nace del compromiso interpretativo y de la sensibilidad compartida entre Helena Amado y Pepe Fernández, ambos unidos en la recuperación y adaptación escénica de repertorios tradicionales desde una perspectiva camerística. La propuesta se articula como un recorrido íntimo y profundamente emocional por la figura de Juanita Reina, símbolo de la copla andaluza. Desde una perspectiva actual, Amado y Fernández abordan una selección de sus obras más emblemáticas, reivindicando su valor poético, musical y escénico. —Programa Juanita con mayúsculas Francisco Alegre (Antonio Quintero, Rafael de León y Manuel Quiroga) Y sin embargo te quiero (Antonio Quintero, Rafael de León y Manuel Quiroga) Carmen de España (Rafael de León y Manuel Quiroga) Lola la Piconera (Antonio Quintero, Rafael de León y Manuel Quiroga) Doña Mariquita de los Dolores (Rafael de León y Manuel Quiroga) Compuesta y sin novio (Antonio Quintero, Rafael de León y Manuel Quiroga) Tururú (Antonio Quintero, Rafael de León y Manuel Quiroga) Capote de grana y oro (Antonio Quintero, Rafael de León y Manuel Quiroga) Yo soy… esa (Antonio Quintero, Rafael de León y Manuel Quiroga) Una Cantaora (Antonio Quintero y Manuel Quiroga) Lagartijera (Antonio Quintero, Rafael de León y Manuel Quiroga) Soltera yo no me quedo (Rafael León y Antonio Quintero) Ni hablar del peluquín (Antonio Quintero, Rafael de León y Manuel Quiroga) Filigrana de oro puro (Antonio Quintero, Rafael de León y Manuel Quiroga) —</t>
+  </si>
+  <si>
+    <t>Calle Cadenas, s/n, Arcos de la Frontera. Cádiz - Plaza del Cananeo</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juanita-con-mayusculas</t>
+  </si>
+  <si>
+    <t>LXV Festival Flamenco Velada de las Nieves en Arcos de la Frontera</t>
+  </si>
+  <si>
+    <t>LXV FESTIVAL FLAMENCO VELADAS DE LAS NIEVES 3 y 4 de agosto de 2026 La localidad gaditana de Arcos de la Frontera acoge el 3 y 4 de agosto la LVX edición de su Festival Flamenco Velada de las Nieves. Se le entregará la Medalla de Oro del Festival a Manuel Gallardo Barroso "Manolo Zapata". La programación, que cuenta con la colaboración del Instituto Andaluz del Flamenco, es la siguiente: 3 de agosto, 22:00 horas, Atrio de San Pedro. Ana de Caro con la guitarra de Javier Ibáñez. 4 de agosto, 22:00 horas, Plaza del Cabildo: Al baile, Titi Flores. Al cante: Jesús Méndez con la guitarra de Antonio Higuero. María Terremoto con la guitarra de Nono Jero. Manuel Moreno "El Pele" con la guitarra de Niño Seve. Artista invitado al baile: Farruquito.</t>
+  </si>
+  <si>
+    <t>03 de Agosto del 2026 - 04 de Agosto del 2026 | 22:00 horas.</t>
+  </si>
+  <si>
+    <t>, Arcos de la Frontera. Cádiz - Varios lugares en el municipio, Arcos de la Frontera, Cádiz</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/lxv-festival-flamenco-velada-de-las-nieves-en-arcos-de-la-frontera</t>
+  </si>
+  <si>
+    <t>La Coquette</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Kanbahiota Troup. DURACIÓN: 50 min Una gran estrella de circo “La Coquette" de los años 50 viene dispuesta a triunfar , para ello su partener, el cual es el encargado de tener todo preparado intenta salvar todos los problemas que le surgen , siempre esperando contentarla y enamorarla . Van superando los obstáculos para finalmente realizar el gran número de trapecio entre los dos. Espectáculos en clave de clown , donde la técnica de circo , la magia y sobre todo el humor se entre mezclan para el disfrute de todos los público .</t>
+  </si>
+  <si>
+    <t>06 de Diciembre del 2026 | A las 12:30</t>
+  </si>
+  <si>
+    <t>Paseo de Andalucía, s/n, Arcos de la Frontera. Cádiz - Explanada biblioteca</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-coquette-6</t>
+  </si>
+  <si>
+    <t>La Gallina de los huevos de oro</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Zum Zum Teatre. DURACIÓN: 50 ¿os gusta el dinero? ¿mucho? Los granjeros de esta historia no perdían el tiempo pensando en el dinero y siempre repartían lo poco que tenían con quien más lo necesitaba, pero un día una gallina llegó a su granja y puso un huevo de oro. ¿Os imaginais si os pasara a vosotros? LA GALLINA DE LOS HUEVOS DE ORO es una historia que cuenta que el dinero es un "cuento.</t>
+  </si>
+  <si>
+    <t>15 de Noviembre del 2026 | A las 12:30</t>
+  </si>
+  <si>
+    <t>Av. San Fernando, 79, Rota. Cádiz - Teatro Municipal Alcalde Felipe Benítez</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-gallina-de-los-huevos-de-oro-6</t>
+  </si>
+  <si>
+    <t>La Reina Brava</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Las Niñas de Cádiz DURACIÓN: 75 minutos Esta es la historia de un magnicidio. El asesinato de una reina a la que todos odian pero a la que nadie se atreve a enfrentar cara a cara.Solo una madre, movida por el ansia de venganza, será capaz de saltarse todas las normas, dando muerte sin ningún tipo de misericordia a la mujer que ha destrozado la vida de su hija. Luego vendrán el revuelo, la conmoción, un juicio vergonzante en el que todos miente, y una implacable condena al olvido.</t>
+  </si>
+  <si>
+    <t>Paseo de la Alameda, s/n, Tarifa. Cádiz - Teatro Municipal Alameda</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-reina-brava-1</t>
+  </si>
+  <si>
+    <t>09 de Octubre del 2026 | A las 19:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-reina-brava-4</t>
+  </si>
+  <si>
+    <t>La venganza de Don Mendo</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: El perro producciones DURACIÓN: 90 Pedro Muñoz Seca escribió más de 300 obras pero es esencialmente conocido por LA VENGANZA DE DON MENDO, una comedia que se asienta sobre dos grandes
 tradiciones: la del teatro en verso y la de la parodia. 
 La obra, construida con un gran instinto teatral, no es una pieza, como algunos podrían pensar, destinada a compañías de aficionados, todo lo contrario, como todas las obras que funcionan sobre el escenario, exige un buen conocimiento del medio y no es casualidad que haya sido tan representada desde el día de su estreno hasta hoy.
 DON MENDO es una de esas obras que gustan por igual a la gente de teatro y al público en general. A los de la profesión nos gusta porque está construida (muy bien construida) con amor, muchísimo ingenio, un conocimiento erudito de los
@@ -1045,97 +1050,97 @@
 Con una escenografía poco convencional, un vestuario acorde con la escenografía, una adaptación que le imprime un ritmo escénico actual, una puesta al día de los chistes que han perdido sus referencias y unos toques de TRICICLE, los Muñoz Seca del teatro gestual.</t>
   </si>
   <si>
-    <t xml:space="preserve">11 de Octubre del 2026 | A las 19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-venganza-de-don-mendo-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La voz que aún resuena. Mujeres de las tres culturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Veterum Musicae DURACIÓN: 1hora 10min Como motivo de veneración en las cantigas de Alfonso X, como objeto de devoción en los cantos de trovadores, como modelo de inspiración en los poemas andalusíes, como protagonista en los cantos tradicionales sefardíes, como poeta, compositora y trobairitz… El espectáculo LA VOZ QUE AUN RESUENA: MUJERES DE LAS TRES CULTURAS (nace con el objeto de visibilizar la figura femenina y sus diversas facetas en la música del mundo antiguo, y lo hace a través de las voces inconfundibles de tres mujeres de hoy que toman el testigo de las mujeres del pasado para traer hasta nosotros sus historias, sus pensamientos, sus inquietudes, la manera en que fueron vistas y en que ellas se vieron a sí mismas y al mundo que habitaron. Ángeles Núñez, Imán Kandoussi y Lucía Marsella se convierten así en mensajeras de las mujeres de las Tres Culturas y las traen de nuevo al presente para que su legado y su memoria sigan vivos a través de sus voces.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 de Noviembre del 2026 | A las 19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-voz-que-aun-resuena-mujeres-de-las-tres-culturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Noches Blancas de Medina Sidonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Este verano, disfruta de las Noches Blancas de Medina Sidonia todos los viernes de julio y agosto. Se abrirán gratuitamente sus monumentos más emblemáticos en horario nocturno, para que puedas disfrutar de su belleza bajo la luz de las estrellas. Todos los viernes de julio y agosto, de 18:00h a 00:00h. Podrán visitarse gratuitamente el Ayuntamiento, el Museo Arqueológico, la Calzada Romana, el Museo Etnográfico y el Espacio Arqueológico del Castillo. También habrá conciertos, mercadillo artesanal, exposiciones, observaciones astronómicas desde el castillo,  talleres infantiles... Consulta el Programa completo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03 de Julio del 2026 - 28 de Agosto del 2026 | De 18:00h a 00:00h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arco de la Pastora, Medina-Sidonia. Cádiz - Centro Histórico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/las-noches-blancas-de-medina-sidonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Ana F. Melero DURACIÓN: 11 minutos Latente es un solo para 1 intérprete de danza contemporánea para calle y espacio no convencional. El adjetivo latente describe aquello que está oculto o, en apariencia, inactivo.
+    <t>11 de Octubre del 2026 | A las 19:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-venganza-de-don-mendo-10</t>
+  </si>
+  <si>
+    <t>La voz que aún resuena. Mujeres de las tres culturas</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Veterum Musicae DURACIÓN: 1hora 10min Como motivo de veneración en las cantigas de Alfonso X, como objeto de devoción en los cantos de trovadores, como modelo de inspiración en los poemas andalusíes, como protagonista en los cantos tradicionales sefardíes, como poeta, compositora y trobairitz… El espectáculo LA VOZ QUE AUN RESUENA: MUJERES DE LAS TRES CULTURAS (nace con el objeto de visibilizar la figura femenina y sus diversas facetas en la música del mundo antiguo, y lo hace a través de las voces inconfundibles de tres mujeres de hoy que toman el testigo de las mujeres del pasado para traer hasta nosotros sus historias, sus pensamientos, sus inquietudes, la manera en que fueron vistas y en que ellas se vieron a sí mismas y al mundo que habitaron. Ángeles Núñez, Imán Kandoussi y Lucía Marsella se convierten así en mensajeras de las mujeres de las Tres Culturas y las traen de nuevo al presente para que su legado y su memoria sigan vivos a través de sus voces.</t>
+  </si>
+  <si>
+    <t>12 de Noviembre del 2026 | A las 19:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-voz-que-aun-resuena-mujeres-de-las-tres-culturas</t>
+  </si>
+  <si>
+    <t>Las Noches Blancas de Medina Sidonia</t>
+  </si>
+  <si>
+    <t>Este verano, disfruta de las Noches Blancas de Medina Sidonia todos los viernes de julio y agosto. Se abrirán gratuitamente sus monumentos más emblemáticos en horario nocturno, para que puedas disfrutar de su belleza bajo la luz de las estrellas. Todos los viernes de julio y agosto, de 18:00h a 00:00h. Podrán visitarse gratuitamente el Ayuntamiento, el Museo Arqueológico, la Calzada Romana, el Museo Etnográfico y el Espacio Arqueológico del Castillo. También habrá conciertos, mercadillo artesanal, exposiciones, observaciones astronómicas desde el castillo,  talleres infantiles... Consulta el Programa completo</t>
+  </si>
+  <si>
+    <t>03 de Julio del 2026 - 28 de Agosto del 2026 | De 18:00h a 00:00h.</t>
+  </si>
+  <si>
+    <t>Arco de la Pastora, Medina-Sidonia. Cádiz - Centro Histórico</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/las-noches-blancas-de-medina-sidonia</t>
+  </si>
+  <si>
+    <t>Latente</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Ana F. Melero DURACIÓN: 11 minutos Latente es un solo para 1 intérprete de danza contemporánea para calle y espacio no convencional. El adjetivo latente describe aquello que está oculto o, en apariencia, inactivo.
 El contenido latente de los sueños es aquello que se conecta con el inconsciente, lo real, la esencia. 
 El calor latente es la cantidad de energía requerida por una sustancia para cambiar de fase.
 El conflicto latente está compuesto por fuerzas que empujan en direcciones opuestas.LATENTE es la exploración de los contrastes y los extremos, el control y el descontrol, un viaje sobre la sutileza en lo explosivo para convertirse en adjetivo, contenido y conflicto provocando así el cambio de fase.</t>
   </si>
   <si>
-    <t xml:space="preserve">03 de Octubre del 2026 | A las 19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza Artesanía, s/n, Guadalcacín. Cádiz - Plaza Artesanía</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/latente-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 de Agosto del 2026 | A las 21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza Santa Catalina, Conil de la Frontera. Cádiz - Centro Cultural Santa Catalina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/latente-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los viajes de Bowa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: La Gata Japonesa DURACIÓN: 50 Bowa, nómada, huérfana de raíces y de sueños, un día encontró una botella a orillas del mar. En su interior halló un mensaje y algo impulsó una búsqueda hasta su destinatario. El camino fue tan rico que se convirtió casi en una obsesión. Horas de espera y kilómetros de búsqueda para hacer llegar a su destino cientos de mensajes que navegaron encerrados en el cristal brillante de alguna botella. Un mensaje le ha traído justo a este lugar, en el que espera encontrarse con alguien que lanzó un mensaje al mar esperando que llegase de vuelta. Esa persona no aparecerá, pero algo especial tiene este lugar, algo familiar, algo tan extraño para ella como el calor de un hogar. Y leerá un nuevo mensaje. Éste escrito por el mar, ese viejo sabio, testigo de sus hazañas y consciente de sus ausencias. Es el mar el que ha guiado sus pasos hasta allí, es en ese lugar, donde las alas de Bowa encontrarán tierra para anclar sus raíces. El espectáculo transita por diferentes estados emocionales del personaje, que se apoyan en un lenguaje circense multidisciplinar: Efectos de magia, que surgen de una forma accidental, reforzando la peculiaridad de ese espacio. Desarrollo de una investigación sobre las botellas: manipulación, equilibrios, y desmitificación del objeto, haciéndolo personaje, escenografía, o mero elemento de apoyo. Acrobacia aérea, de carga técnica, pero desarrollada de forma orgánica y coherente y, por supuesto, humor y poesía como elementos transversales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 de Septiembre del 2026 | A las 12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paseo El Ejido, San Roque. Cádiz - Plaza de la Igualdad (Calle)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/los-viajes-de-bowa-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACHADO FLAMENCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: JOSE LUIS MONTON DURACIÓN: 85 “Machado Flamenco” nace de las notas de la guitarra del Maestro José Luis Montón y la idea y texto de Lara Carrasco. Ambos logran aunar la vida y obra del poeta Antonio Machado en una emocionante narración que viaja por su historia personal, escritos y poemas entrelazados por las composiciones musicales que, en esta ocasión, nos regala de manera magistral el reconocido Maestro de Guitarra Flamenca José Luis Montón. Y todo ello acompañado al cante con la fuerza vocal de la cantaora Inma “La Carbonera”,Este espectáculo surge, también, de la necesidad de rendir un personal homenaje a la figura del poeta y a la influencia del flamenco en su poesía. Sobre el telón de fondo de sus versos el flamenco pasea silencioso marcando una rítmica poética que encaja en cualquiera de sus palos. Su poesía rezuma Flamenco en cada uno de sus versos, que logran convertirse en seguirillas, bulerías, alegrías o tangos casi de forma natural, mientras la guitarra tañe sus notas convirtiendo sus poemas en cantes, sin realizar apenas esfuerzo. Lo cierto es que el universal poeta andaluz recibió la influencia del flamenco en su Sevilla natal y de la mano de su padre, Antonio Machado Álvarez, de sobrenombre “ “Demófilo”, reconocido recopilador de folklore español, que publicaría, en 1881, la primera Colección de Cantes Flamencos, un hito sin precedentes en la Historia del Cante.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 de Noviembre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/machado-flamenco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mamá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: La Perfecta Compañía DURACIÓN: 60' El personaje de Manuela, continua contando historias después de su primera obra, "Perfecta".
+    <t>03 de Octubre del 2026 | A las 19:00</t>
+  </si>
+  <si>
+    <t>Plaza Artesanía, s/n, Guadalcacín. Cádiz - Plaza Artesanía</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/latente-2</t>
+  </si>
+  <si>
+    <t>28 de Agosto del 2026 | A las 21:00</t>
+  </si>
+  <si>
+    <t>Plaza Santa Catalina, Conil de la Frontera. Cádiz - Centro Cultural Santa Catalina</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/latente-1</t>
+  </si>
+  <si>
+    <t>Los viajes de Bowa</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: La Gata Japonesa DURACIÓN: 50 Bowa, nómada, huérfana de raíces y de sueños, un día encontró una botella a orillas del mar. En su interior halló un mensaje y algo impulsó una búsqueda hasta su destinatario. El camino fue tan rico que se convirtió casi en una obsesión. Horas de espera y kilómetros de búsqueda para hacer llegar a su destino cientos de mensajes que navegaron encerrados en el cristal brillante de alguna botella. Un mensaje le ha traído justo a este lugar, en el que espera encontrarse con alguien que lanzó un mensaje al mar esperando que llegase de vuelta. Esa persona no aparecerá, pero algo especial tiene este lugar, algo familiar, algo tan extraño para ella como el calor de un hogar. Y leerá un nuevo mensaje. Éste escrito por el mar, ese viejo sabio, testigo de sus hazañas y consciente de sus ausencias. Es el mar el que ha guiado sus pasos hasta allí, es en ese lugar, donde las alas de Bowa encontrarán tierra para anclar sus raíces. El espectáculo transita por diferentes estados emocionales del personaje, que se apoyan en un lenguaje circense multidisciplinar: Efectos de magia, que surgen de una forma accidental, reforzando la peculiaridad de ese espacio. Desarrollo de una investigación sobre las botellas: manipulación, equilibrios, y desmitificación del objeto, haciéndolo personaje, escenografía, o mero elemento de apoyo. Acrobacia aérea, de carga técnica, pero desarrollada de forma orgánica y coherente y, por supuesto, humor y poesía como elementos transversales.</t>
+  </si>
+  <si>
+    <t>24 de Septiembre del 2026 | A las 12:00</t>
+  </si>
+  <si>
+    <t>Paseo El Ejido, San Roque. Cádiz - Plaza de la Igualdad (Calle)</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/los-viajes-de-bowa-3</t>
+  </si>
+  <si>
+    <t>MACHADO FLAMENCO</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: JOSE LUIS MONTON DURACIÓN: 85 “Machado Flamenco” nace de las notas de la guitarra del Maestro José Luis Montón y la idea y texto de Lara Carrasco. Ambos logran aunar la vida y obra del poeta Antonio Machado en una emocionante narración que viaja por su historia personal, escritos y poemas entrelazados por las composiciones musicales que, en esta ocasión, nos regala de manera magistral el reconocido Maestro de Guitarra Flamenca José Luis Montón. Y todo ello acompañado al cante con la fuerza vocal de la cantaora Inma “La Carbonera”,Este espectáculo surge, también, de la necesidad de rendir un personal homenaje a la figura del poeta y a la influencia del flamenco en su poesía. Sobre el telón de fondo de sus versos el flamenco pasea silencioso marcando una rítmica poética que encaja en cualquiera de sus palos. Su poesía rezuma Flamenco en cada uno de sus versos, que logran convertirse en seguirillas, bulerías, alegrías o tangos casi de forma natural, mientras la guitarra tañe sus notas convirtiendo sus poemas en cantes, sin realizar apenas esfuerzo. Lo cierto es que el universal poeta andaluz recibió la influencia del flamenco en su Sevilla natal y de la mano de su padre, Antonio Machado Álvarez, de sobrenombre “ “Demófilo”, reconocido recopilador de folklore español, que publicaría, en 1881, la primera Colección de Cantes Flamencos, un hito sin precedentes en la Historia del Cante.</t>
+  </si>
+  <si>
+    <t>14 de Noviembre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/machado-flamenco</t>
+  </si>
+  <si>
+    <t>Mamá</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: La Perfecta Compañía DURACIÓN: 60' El personaje de Manuela, continua contando historias después de su primera obra, "Perfecta".
 Con MAMÁ viajará a la llamada de la
 maternidad, adentrándose en inseguridades,
 responsabilidades y amor incondicional: una
@@ -1148,100 +1153,100 @@
 normativos embarazados.</t>
   </si>
   <si>
-    <t xml:space="preserve">21 de Noviembre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/mama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manolo Morera en Conil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manolo Morera hace escala en Conil el próximo 23 de agosto. Adéntrate en el Universo Morera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 de Agosto del 2026 | 22:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 de Agosto del 2026 22:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/manolo-morera-en-conil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melody, concierto en La Mina Conil de la Frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melody es una artista española conocida por su evolución artística y proyectos internacionales. Su gira recorrerá varias ciudades de España como Bilbao, Barcelona, y Granada. El espectáculo promete ser renovado, mostrando una faceta más madura y poderosa de la artista.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 de Agosto del 2026 | 21:30 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salida 26 de la Autovía A-48, Conil de la Frontera. Cádiz - La Mina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/melody-concierto-en-la-mina-conil-de-la-frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miguel Campello, concierto en La Mina Conil de la Frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El concierto de Miguel Campello en La Mina (Conil de la Frontera) será el sábado 22 de agosto de 2026 a las 21:30 . Las entradas están disponibles e incluyen zonas de pista y grada. Detalles clave del evento: Lugar: Espacio cultural al aire libre La Mina, Autovía A-48, Salida 26 (Conil Playas), Cádiz. Fecha y Hora: Sábado, 22 de agosto de 2026, a las 21:30. Precio: Entradas desde 27,50 € (General Pista) y 33,00 € (General Grada), con gastos de gestión incluidos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 de Agosto del 2026 | 21:30 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/miguel-campello-concierto-en-la-mina-conil-de-la-frontera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molan los 90 en Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El festival Molan los 90 , se celebrará en Cádiz el 1 de agosto de 2026 . El evento tendrá lugar en el Muelle Reina Victoria de 20:00 a 02:00 horas. El cartel incluye actuaciones de artistas como Tina Cousins, Paco Pil, Locomía, Los Inhumanos, entre otros. Las entradas ya están a la venta en el sitio web oficial, molanlos90.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Agosto del 2026 | A las 22:00 h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mlle. Ciudad, Cádiz. Cádiz - Muelle Reina Victoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/molan-los-90-en-cadiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morera for president en Rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manolo Morera se lanza con una nueva obra en solitario, Morera for president , un gobierno de risa. Un auténtico talento del humor sinónimo de humor blanco y garantía de desconexión con la que arrancará de nuevo las carcajadas del público con sus ocurrentes soluciones para salvar el país. Un sello personal e inconfundible que hace que todos se tronchen de risa. Adéntrate en el Universo Morera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 de Agosto del 2026 | 22:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C/ María Auxiliadora 2, Rota. Cádiz - Colegio Nuestra Señora del Rosario, Salesianos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/morera-president-en-rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Sin Música Festival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El festival musical gaditano NoSinMúsica calienta motores para su edición de 20256. Sol, mar, verano, vida, buen clima... Sin duda la mezcla perfecta para una magnífica velada musical. Artistas: LOve of lesbian, Alcalá Norte, Denisdenis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 de Agosto del 2026 | Consultar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/no-sin-musica-festival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noches de soul y blues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Quique Bonal y Vicky Luna DURACIÓN: 60 minutos Programa
+    <t>21 de Noviembre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/mama</t>
+  </si>
+  <si>
+    <t>Manolo Morera en Conil</t>
+  </si>
+  <si>
+    <t>Manolo Morera hace escala en Conil el próximo 23 de agosto. Adéntrate en el Universo Morera.</t>
+  </si>
+  <si>
+    <t>23 de Agosto del 2026 | 22:00 horas</t>
+  </si>
+  <si>
+    <t>23 de Agosto del 2026 22:00 horas</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/manolo-morera-en-conil</t>
+  </si>
+  <si>
+    <t>Melody, concierto en La Mina Conil de la Frontera</t>
+  </si>
+  <si>
+    <t>Melody es una artista española conocida por su evolución artística y proyectos internacionales. Su gira recorrerá varias ciudades de España como Bilbao, Barcelona, y Granada. El espectáculo promete ser renovado, mostrando una faceta más madura y poderosa de la artista.</t>
+  </si>
+  <si>
+    <t>23 de Agosto del 2026 | 21:30 horas</t>
+  </si>
+  <si>
+    <t>Salida 26 de la Autovía A-48, Conil de la Frontera. Cádiz - La Mina</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/melody-concierto-en-la-mina-conil-de-la-frontera</t>
+  </si>
+  <si>
+    <t>Miguel Campello, concierto en La Mina Conil de la Frontera</t>
+  </si>
+  <si>
+    <t>El concierto de Miguel Campello en La Mina (Conil de la Frontera) será el sábado 22 de agosto de 2026 a las 21:30 . Las entradas están disponibles e incluyen zonas de pista y grada. Detalles clave del evento: Lugar: Espacio cultural al aire libre La Mina, Autovía A-48, Salida 26 (Conil Playas), Cádiz. Fecha y Hora: Sábado, 22 de agosto de 2026, a las 21:30. Precio: Entradas desde 27,50 € (General Pista) y 33,00 € (General Grada), con gastos de gestión incluidos.</t>
+  </si>
+  <si>
+    <t>22 de Agosto del 2026 | 21:30 horas</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/miguel-campello-concierto-en-la-mina-conil-de-la-frontera</t>
+  </si>
+  <si>
+    <t>Molan los 90 en Cádiz</t>
+  </si>
+  <si>
+    <t>El festival Molan los 90 , se celebrará en Cádiz el 1 de agosto de 2026 . El evento tendrá lugar en el Muelle Reina Victoria de 20:00 a 02:00 horas. El cartel incluye actuaciones de artistas como Tina Cousins, Paco Pil, Locomía, Los Inhumanos, entre otros. Las entradas ya están a la venta en el sitio web oficial, molanlos90.com</t>
+  </si>
+  <si>
+    <t>01 de Agosto del 2026 | A las 22:00 h</t>
+  </si>
+  <si>
+    <t>Mlle. Ciudad, Cádiz. Cádiz - Muelle Reina Victoria</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/molan-los-90-en-cadiz</t>
+  </si>
+  <si>
+    <t>Morera for president en Rota</t>
+  </si>
+  <si>
+    <t>Manolo Morera se lanza con una nueva obra en solitario, Morera for president , un gobierno de risa. Un auténtico talento del humor sinónimo de humor blanco y garantía de desconexión con la que arrancará de nuevo las carcajadas del público con sus ocurrentes soluciones para salvar el país. Un sello personal e inconfundible que hace que todos se tronchen de risa. Adéntrate en el Universo Morera.</t>
+  </si>
+  <si>
+    <t>07 de Agosto del 2026 | 22:00 horas</t>
+  </si>
+  <si>
+    <t>C/ María Auxiliadora 2, Rota. Cádiz - Colegio Nuestra Señora del Rosario, Salesianos</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/morera-president-en-rota</t>
+  </si>
+  <si>
+    <t>No Sin Música Festival</t>
+  </si>
+  <si>
+    <t>El festival musical gaditano NoSinMúsica calienta motores para su edición de 20256. Sol, mar, verano, vida, buen clima... Sin duda la mezcla perfecta para una magnífica velada musical. Artistas: LOve of lesbian, Alcalá Norte, Denisdenis</t>
+  </si>
+  <si>
+    <t>15 de Agosto del 2026 | Consultar.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/no-sin-musica-festival</t>
+  </si>
+  <si>
+    <t>Noches de soul y blues</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Quique Bonal y Vicky Luna DURACIÓN: 60 minutos Programa
 Noches de soul y blues
 Fine &amp; Dandy (Q.Bonal / M.Vernon)
 It Was You (Q.Bonal)
@@ -1260,268 +1265,268 @@
 Noches de Soul y Blues es un viaje íntimo por las emociones más profundas del alma, con un repertorio que combina composiciones originales y clásicos atemporales del género. Las piezas de Q. Bonal, como It Was You o Every Girl, aportan una sensibilidad contemporánea que dialoga con la calidez de la tradición. Fever y That’s Alright, Mama evocan el magnetismo del soul y el rock primitivo, mientras que temas como Trouble In Mind y There'll Be Some Changes Made nos sumergen en la esencia melancólica y combativa del blues. Con guiños al jazz de Ellington y al legado sureño de Dixie, esta velada es una celebración del sentimiento, el ritmo y la autenticidad.</t>
   </si>
   <si>
-    <t xml:space="preserve">05 de Septiembre del 2026 | A las 21:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avda. Sombrero de Tres Picos, s/n, Arcos de la Frontera. Cádiz - Playa de Arcos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/noches-de-soul-y-blues-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pando el mago, en Rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Este cartel anuncia un espectáculo del ilusionista conocido como Pando el Mago, reconocido por espectáculos de magia modernos y familiares, con apariciones tanto en redes sociales como en televisióEl show se llevará a cabo en el Colegio Eduardo Lobillo en Rota. Está programado para el 16 de agosto a las 22:00h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 de Agosto del 2026 | A las 22:00 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/pando-el-mago-en-rota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pies de gallina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Ana F. Melero y Luna Sánchez DURACIÓN: 15 PIES DE GALLINA es el cuerpo común creado por dos mujeres que bailan sus sincronías y discordancias. La obra se inspira en las expresiones “Tener la piel de gallina” y “Andar con pies de plomo”, indagando en el contraste entre lo instintivo y lo racional. Estos dos cuerpos exploran el entendimiento y apoyo como base de supervivencia, generando un volumen en perpetuo derrumbamiento que sostiene y es sostenido. PIES DE GALLINA es un viaje sobre la importancia de ser una sola y de ser en conjunto, proponiendo soporte y desequilibrio a la relación mutante de sus dos intérpretes y creadoras. No se pretendía hablar de amor, pero qué es el amor si no es dejarse caer y sostener.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 de Noviembre del 2026 | A las 12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASEO DE ANDALUCIA S/N, Arcos de la Frontera. Cádiz - EL PASEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/pies-de-gallina-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programación de actividades en la BPE-Biblioteca Provincial de Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programación de actividades de julio en la BPE-Biblioteca Provincial de Cádiz: Programación de actividades en la BPE-BP de Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 31 de Julio del 2026 | Consultar programación de actividades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avda. Cuatro de Diciembre de 1977, 16, Cádiz. Cádiz - Biblioteca Pública Provincial del Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-de-actividades-en-la-bpe-biblioteca-provincial-de-cadiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programación de verano en el Museo de Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Museo de Cádiz Taller “Retratos con Alma: Arte Figurativo Contemporáneo en el Museo de Cádiz” . Fecha y hora:  2 de Julio a las 11.30 hrs. Público: Infantil – juvenil. Descripción: Este taller invita a explorar la representación de la figura humana y las escenas cotidianas mediante la observación de obras realistas y figurativas del siglo XX. A partir de piezas como Muchacha haciendo medias de Eugenio Hermoso y el Retrato de Micaela Aramburu de Ignacio Zuloaga, los participantes trabajarán la identidad, las emociones y la narración visual. En la parte práctica, crearán retratos y escenas figurativas utilizando acrílico, acuarela y pasteles, experimentando con el color, la textura y la expresión para desarrollar composiciones personales inspiradas en las obras de referencia. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller de movimiento. “Ritmos de Oriente: Danza Oriental en la Protohistoria”. Fecha y hora:  7 de Julio a las 11.00 hrs. Duración 2 horas. Público: Infantil de 3 a 7 años. Descripción: A partir de las célebres terracotas femeninas conservadas en el Museo de Cádiz, los participantes descubrirán el papel de la música, la danza y las manifestaciones rituales en las sociedades fenicias y púnicas. La actividad combinará una introducción histórica con una experiencia participativa que permitirá acercarse a estas expresiones culturales desde una perspectiva divulgativa y vivencial. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller de Ilustración. “Bestiario gaditanos: Ilustrando seres, mitos y criaturas”. Fecha y hora:  9 y 30 de julio a las  11.00 hrs. Público: General. Descripción:En las obras del Museo de Cádiz, desde las piezas fenicias hasta las más modernas, habitan bestias. Animales y criaturas que parecen comunicarse entre sí, saltando épocas y recorriendo salas, pasillos y escaleras. Este taller para público infantil y juvenil propone una exploración de ese bestiario oculto que aguarda nuestra mirada y tiene historias que contar. A continuación, a través de la ilustración y el cómic, cada participante creará su propia bestia inspirada en las colecciones del museo. Finalmente, reuniremos todas las creaciones en un catálogo ilustrado colectivo, dispuesto para quienes se atrevan a descubrirlo. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Teatro familiar:  “Belinda y el hueso de mamut”. Fecha y hora:  14 de Julio a las 19.00 hrs. Público: Familiar. Descripción: Belinda es una paleontóloga y divulgadora científica que trabaja en el Museo de Cádiz. Muy comprometida con el cuidado del planeta dedica sus días a investigar antiguos hallazgos. Todo cambia cuando llega al museo una pieza excepcional: un hueso de mamut hallado en la provincia de Cádiz. Intrigada por su origen, Belinda emprenderá una fascinante aventura para resolver el misterio, viajando a través del tiempo. Lugar: Museo de Cádiz_Patio central Reserva y aforo: Aforo 50 personas. Reserva previa en web museo Detectives del tiempo: el enigma del modelo fantasma. Fecha y hora: 14 de Julio a las 11.00 y 12.00. hrs. 2 pases. Público: Familiar. Descripción: según cuentan algunos testigos, el fantasma de un antiguo modelo que posó para varios pintores del pasado, vaga por las salas del museo intentando zanjar asuntos pendientes.  Un detective del tiempo, con apoyo de los asistentes, tratará de invocarlo para ayudarlo a lograr el descanso eterno. A cambio, le pedirá información para resolver algunos de los misterios ocultos en varios cuadros del museo. ¿Y tú?, ¿te atreves a remover el tiempo?... Lugar: Museo de Cádiz, patio principal. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller. “Esencias de Roma: El Arte de los Ungüentos Romanos”. Fecha y hora:  21 de Julio a las 11.00 hrs. Público: Infantil de 6 a 10 años. Descripción: Este taller permitirá explorar el mundo de los perfumes y ungüentos utilizados en época romana para la higiene, el cuidado personal, la medicina y los rituales religiosos. Tras una introducción a los productos aromáticos que circulaban por las rutas comerciales mediterráneas, los participantes elaborarán su propio perfume o ungüento utilizando esencias naturales de rosas, lavanda y romero, inspiradas en recetas de la Antigüedad. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller: “El lenguaje de los Símbolos: Arte Abstracto Contemporáneo en el Museo de Cádiz”. Fecha y hora:  23 de Julio a las 11.30 hrs. Público: Infantil – juvenil. Descripción: ¿Y si una mancha de color pudiera expresar una emoción? ¿O una figura convertirse en el punto de partida de una gran historia? En este taller, niños y jóvenes descubrirán el arte contemporáneo del Museo de Cádiz explorando obras abstractas de una forma cercana, divertida y participativa. A través de la observación, el juego y la experimentación con distintas técnicas como el collage los participantes crearán sus propias obras, desarrollando la imaginación, la creatividad y una mirada curiosa hacia el arte. Lugar: Museo de Cádiz Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller. “Recetas y Sabores de Roma”. Fecha y hora:  28 de Julio a las 11.30 hrs. Duración 2 horas. Público: Juvenil de 12 a 15 años. Descripción: ¿Sabes qué comían los romanos y cómo organizaban sus comidas? A través de textos antiguos y restos arqueológicos, los participantes descubrirán los ingredientes, recetas y costumbres gastronómicas de la Antigua Roma. Además, pondrán en práctica estos conocimientos elaborando dos recetas inspiradas en la cocina romana. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Reserva y aforo: Requiere reserva previa en la web museo . Aforo: 25 personas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 de Julio del 2026 - 30 de Julio del 2026 | Consultar horario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaza de Mina, s/n, Cádiz. Cádiz - Museo de Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-de-verano-en-el-museo-de-cadiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programación del ciclo 'Solera y Compás'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veranea en la Bodega de González Byass 2026 ya tiene programación del ciclo ' Solera y Compás '. Programación: 4 julio 2026 Raphael 21:00 - Bodegas González Byass - Tío Pepe 9 julio 2026 Elvis Crespo 21:00 - Bodegas González Byass - Tío Pepe 11 julio 2026 Pastora Soler 21:00 - Bodegas González Byass - Tío Pepe 12 julio 2026 María Terremoto 21:00 - Bodegas González Byass - Tío Pepe 19 julio 2026 G-5 21:00 - Bodegas González Byass - Tío Pepe 26 julio 2026 Israel Fernández 21:00 - Bodegas González Byass - Tío Pepe 1 agosto 2026 Beret 21:00 - Bodegas González Byass - Tío Pepe 2 agosto 2026 Luz Casal 21:00 - Bodegas González Byass - Tío Pepe 4 agosto 2026 M-Clan 21:00 - Bodegas González Byass - Tío Pepe 9 agosto 2026 Antoñito Molina. Con Ismael Jordi, Sabina Puértolas y Óliver Díaz 21:00 - Bodegas González Byass - Tío Pepe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04 de Julio del 2026 - 09 de Agosto del 2026 | A las 21:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Manuel María González, 12, Jerez de la Frontera. Cádiz - Bodegas Tío Pepe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-del-ciclo-solera-y-compas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programación especial de verano del Centro Andaluz de las Letras en Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centro Andaluz de las Letras Título actividad: “El pensamiento erótico” Descripción breve: Encuentro con Sara Torres, con motivo de la publicación de ‘El pensamiento erótico’ (Ed. Reservoir Books), en conversación con Carmen Rojas y Mar Gallego. Lugar: Baluarte de la Candelaria Fecha: 01/07/26 Público destinatario: Adultos Horario    21:30:00 Duración: 90 minutos Aforo/ Entrada libre: Entrada libre Enlace web Observaciones: Esta actividad en colaboración con la Feria del Libro de Cádiz se enmarca en el Ciclo  del Centro “Pensar en Compañía” Título actividad: “Falla y la Literatura. 150 aniversario de su nacimiento” Descripción breve: Mesa redonda con José Ramón Ripoll, Katia-Sofía Hakim y Dácil González Mesa. Lugar:  Baluarte de la Candelaria Fecha: 05/07/26 Público destinatario: General Horario: 12:30:00 Duración: 90 minutos Aforo/ Entrada libre: Entrada libre Enlace web Observaciones: Esta actividad en colaboración con la Feria del Libro de Cádiz se enmarca en el Ciclo del Centro “ Falla y la Literatura. 150 aniversario de su nacimiento” Título actividad: “José Manuel Caballero Bonald. La aventura de escribir" Descripción breve: Exposición itinerante y biográfica, comisariada por Felipe Benítez Reyes y producida por el Centro Andaluz de las Letras, que rinde homenaje a la figura y obra del poeta jerezano. Lugar: Universidad de Cádiz. Facultad de Filosofía y Letras. Biblioteca de Humanidades Fecha inicio: 31/04/26 Fecha fin: 31/07/26 Público destinatario: General Horario: lunes a viernes de 9:00 a 21:00 horas Aforo/ Entrada libre: Entrada libre Enlace web Observaciones: se clausurará el 31 de julio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 31 de Julio del 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alameda Hermanas Carvia Bernal, 6, Cádiz. Cádiz - Baluarte de la Candelaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-especial-de-verano-del-centro-andaluz-de-las-letras-en-cadiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programación especial de verano en el Archivo Histórico Provincial de Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archivo Histórico Provincial Documento destacado bimensual de Julio-Agosto: Cádiz, 250 años de relaciones transatlánticas con los Estados Unidos. Exposición presencial y virtual. Coincidiendo este mes de julio con la celebración de los 250 años de la constitución de los Estados Unidos de América, este archivo realizará esta actividad, que pretenderá narrar las prolijas y extensas relaciones a lo largo del tiempo entre la ciudad gaditana y este país norteamericano. Estará a disposición del público presencialmente en la sede física de este archivo, los días laborales de 09.00 h. a 14.00 h. y en la página web de este archivo dentro de la Web de Archivos de Andalucía en el apartado el archivo recomienda y documentos destacados.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 31 de Agosto del 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Cristóbal Colón, 12, Cádiz. Cádiz - Archivo Histórico Provincial de Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-especial-de-verano-en-el-archivo-historico-provincial-de-cadiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quererte a medias (cuarteto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Maui DURACIÓN: 90' Maui de Utrera presenta ‘Quererte a medias’, un concierto diferente, una nueva performance con aires de fiesta, una feria de canciones a todo color, un abanico de historias contadas y cantadas que celebran el amor, la vida y la guasa con el público como protagonista. Deshojando margaritas y convocando al duende, la de Utrera nos adentra en curiosas aventuras y desventuras amorosas de toda índole, tomando la risa como remedio infalible ante el desencanto. Aires de rumba, bulería o alegrías impregnan este simpático repertorio que zarandea al espectador por dentro y por fuera, a modo experiencia terapéutica, logrando aumentar exponencialmente las ganas de exprimir la vida. "Quererte a medias" se estrena con una puesta en escena sorprendente en la que se rompe la cuarta pared para implicar al espectador en el misterio, la alegría y la cercanía propia de los mejores convites. Disfrutaremos de sus últimas canciones y seremos partícipes del estreno de temas inéditos que se visten de lentejuelas para la ocasión.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 de Octubre del 2026 | A las 21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/quererte-medias-cuarteto-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rota: programación verano cultural y juvenil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📍 Castillo de Luna 📍 Auditorio Municipal Alcalde Felipe Benítez 📍 Plaza Bartolomé Pérez 📍 Plaza de la Merced 📍 Costa Ballena 📍 Parroquia Ntra. Sra. de la O
+    <t>05 de Septiembre del 2026 | A las 21:30</t>
+  </si>
+  <si>
+    <t>Avda. Sombrero de Tres Picos, s/n, Arcos de la Frontera. Cádiz - Playa de Arcos</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/noches-de-soul-y-blues-0</t>
+  </si>
+  <si>
+    <t>Pando el mago, en Rota</t>
+  </si>
+  <si>
+    <t>Este cartel anuncia un espectáculo del ilusionista conocido como Pando el Mago, reconocido por espectáculos de magia modernos y familiares, con apariciones tanto en redes sociales como en televisióEl show se llevará a cabo en el Colegio Eduardo Lobillo en Rota. Está programado para el 16 de agosto a las 22:00h.</t>
+  </si>
+  <si>
+    <t>16 de Agosto del 2026 | A las 22:00 h.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/pando-el-mago-en-rota</t>
+  </si>
+  <si>
+    <t>Pies de gallina</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Ana F. Melero y Luna Sánchez DURACIÓN: 15 PIES DE GALLINA es el cuerpo común creado por dos mujeres que bailan sus sincronías y discordancias. La obra se inspira en las expresiones “Tener la piel de gallina” y “Andar con pies de plomo”, indagando en el contraste entre lo instintivo y lo racional. Estos dos cuerpos exploran el entendimiento y apoyo como base de supervivencia, generando un volumen en perpetuo derrumbamiento que sostiene y es sostenido. PIES DE GALLINA es un viaje sobre la importancia de ser una sola y de ser en conjunto, proponiendo soporte y desequilibrio a la relación mutante de sus dos intérpretes y creadoras. No se pretendía hablar de amor, pero qué es el amor si no es dejarse caer y sostener.</t>
+  </si>
+  <si>
+    <t>06 de Noviembre del 2026 | A las 12:00</t>
+  </si>
+  <si>
+    <t>PASEO DE ANDALUCIA S/N, Arcos de la Frontera. Cádiz - EL PASEO</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/pies-de-gallina-3</t>
+  </si>
+  <si>
+    <t>Programación de actividades en la BPE-Biblioteca Provincial de Cádiz</t>
+  </si>
+  <si>
+    <t>Programación de actividades de julio en la BPE-Biblioteca Provincial de Cádiz: Programación de actividades en la BPE-BP de Cádiz</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 31 de Julio del 2026 | Consultar programación de actividades</t>
+  </si>
+  <si>
+    <t>Avda. Cuatro de Diciembre de 1977, 16, Cádiz. Cádiz - Biblioteca Pública Provincial del Cádiz</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-de-actividades-en-la-bpe-biblioteca-provincial-de-cadiz</t>
+  </si>
+  <si>
+    <t>Programación de verano en el Museo de Cádiz</t>
+  </si>
+  <si>
+    <t>Museo de Cádiz Taller “Retratos con Alma: Arte Figurativo Contemporáneo en el Museo de Cádiz” . Fecha y hora:  2 de Julio a las 11.30 hrs. Público: Infantil – juvenil. Descripción: Este taller invita a explorar la representación de la figura humana y las escenas cotidianas mediante la observación de obras realistas y figurativas del siglo XX. A partir de piezas como Muchacha haciendo medias de Eugenio Hermoso y el Retrato de Micaela Aramburu de Ignacio Zuloaga, los participantes trabajarán la identidad, las emociones y la narración visual. En la parte práctica, crearán retratos y escenas figurativas utilizando acrílico, acuarela y pasteles, experimentando con el color, la textura y la expresión para desarrollar composiciones personales inspiradas en las obras de referencia. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller de movimiento. “Ritmos de Oriente: Danza Oriental en la Protohistoria”. Fecha y hora:  7 de Julio a las 11.00 hrs. Duración 2 horas. Público: Infantil de 3 a 7 años. Descripción: A partir de las célebres terracotas femeninas conservadas en el Museo de Cádiz, los participantes descubrirán el papel de la música, la danza y las manifestaciones rituales en las sociedades fenicias y púnicas. La actividad combinará una introducción histórica con una experiencia participativa que permitirá acercarse a estas expresiones culturales desde una perspectiva divulgativa y vivencial. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller de Ilustración. “Bestiario gaditanos: Ilustrando seres, mitos y criaturas”. Fecha y hora:  9 y 30 de julio a las  11.00 hrs. Público: General. Descripción:En las obras del Museo de Cádiz, desde las piezas fenicias hasta las más modernas, habitan bestias. Animales y criaturas que parecen comunicarse entre sí, saltando épocas y recorriendo salas, pasillos y escaleras. Este taller para público infantil y juvenil propone una exploración de ese bestiario oculto que aguarda nuestra mirada y tiene historias que contar. A continuación, a través de la ilustración y el cómic, cada participante creará su propia bestia inspirada en las colecciones del museo. Finalmente, reuniremos todas las creaciones en un catálogo ilustrado colectivo, dispuesto para quienes se atrevan a descubrirlo. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Teatro familiar:  “Belinda y el hueso de mamut”. Fecha y hora:  14 de Julio a las 19.00 hrs. Público: Familiar. Descripción: Belinda es una paleontóloga y divulgadora científica que trabaja en el Museo de Cádiz. Muy comprometida con el cuidado del planeta dedica sus días a investigar antiguos hallazgos. Todo cambia cuando llega al museo una pieza excepcional: un hueso de mamut hallado en la provincia de Cádiz. Intrigada por su origen, Belinda emprenderá una fascinante aventura para resolver el misterio, viajando a través del tiempo. Lugar: Museo de Cádiz_Patio central Reserva y aforo: Aforo 50 personas. Reserva previa en web museo Detectives del tiempo: el enigma del modelo fantasma. Fecha y hora: 14 de Julio a las 11.00 y 12.00. hrs. 2 pases. Público: Familiar. Descripción: según cuentan algunos testigos, el fantasma de un antiguo modelo que posó para varios pintores del pasado, vaga por las salas del museo intentando zanjar asuntos pendientes.  Un detective del tiempo, con apoyo de los asistentes, tratará de invocarlo para ayudarlo a lograr el descanso eterno. A cambio, le pedirá información para resolver algunos de los misterios ocultos en varios cuadros del museo. ¿Y tú?, ¿te atreves a remover el tiempo?... Lugar: Museo de Cádiz, patio principal. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller. “Esencias de Roma: El Arte de los Ungüentos Romanos”. Fecha y hora:  21 de Julio a las 11.00 hrs. Público: Infantil de 6 a 10 años. Descripción: Este taller permitirá explorar el mundo de los perfumes y ungüentos utilizados en época romana para la higiene, el cuidado personal, la medicina y los rituales religiosos. Tras una introducción a los productos aromáticos que circulaban por las rutas comerciales mediterráneas, los participantes elaborarán su propio perfume o ungüento utilizando esencias naturales de rosas, lavanda y romero, inspiradas en recetas de la Antigüedad. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller: “El lenguaje de los Símbolos: Arte Abstracto Contemporáneo en el Museo de Cádiz”. Fecha y hora:  23 de Julio a las 11.30 hrs. Público: Infantil – juvenil. Descripción: ¿Y si una mancha de color pudiera expresar una emoción? ¿O una figura convertirse en el punto de partida de una gran historia? En este taller, niños y jóvenes descubrirán el arte contemporáneo del Museo de Cádiz explorando obras abstractas de una forma cercana, divertida y participativa. A través de la observación, el juego y la experimentación con distintas técnicas como el collage los participantes crearán sus propias obras, desarrollando la imaginación, la creatividad y una mirada curiosa hacia el arte. Lugar: Museo de Cádiz Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Taller. “Recetas y Sabores de Roma”. Fecha y hora:  28 de Julio a las 11.30 hrs. Duración 2 horas. Público: Juvenil de 12 a 15 años. Descripción: ¿Sabes qué comían los romanos y cómo organizaban sus comidas? A través de textos antiguos y restos arqueológicos, los participantes descubrirán los ingredientes, recetas y costumbres gastronómicas de la Antigua Roma. Además, pondrán en práctica estos conocimientos elaborando dos recetas inspiradas en la cocina romana. Lugar: Museo de Cádiz. Reserva y aforo: Aforo 25 personas. Reserva previa en web museo Reserva y aforo: Requiere reserva previa en la web museo . Aforo: 25 personas.</t>
+  </si>
+  <si>
+    <t>02 de Julio del 2026 - 30 de Julio del 2026 | Consultar horario</t>
+  </si>
+  <si>
+    <t>Plaza de Mina, s/n, Cádiz. Cádiz - Museo de Cádiz</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-de-verano-en-el-museo-de-cadiz</t>
+  </si>
+  <si>
+    <t>Programación del ciclo 'Solera y Compás'</t>
+  </si>
+  <si>
+    <t>Veranea en la Bodega de González Byass 2026 ya tiene programación del ciclo ' Solera y Compás '. Programación: 4 julio 2026 Raphael 21:00 - Bodegas González Byass - Tío Pepe 9 julio 2026 Elvis Crespo 21:00 - Bodegas González Byass - Tío Pepe 11 julio 2026 Pastora Soler 21:00 - Bodegas González Byass - Tío Pepe 12 julio 2026 María Terremoto 21:00 - Bodegas González Byass - Tío Pepe 19 julio 2026 G-5 21:00 - Bodegas González Byass - Tío Pepe 26 julio 2026 Israel Fernández 21:00 - Bodegas González Byass - Tío Pepe 1 agosto 2026 Beret 21:00 - Bodegas González Byass - Tío Pepe 2 agosto 2026 Luz Casal 21:00 - Bodegas González Byass - Tío Pepe 4 agosto 2026 M-Clan 21:00 - Bodegas González Byass - Tío Pepe 9 agosto 2026 Antoñito Molina. Con Ismael Jordi, Sabina Puértolas y Óliver Díaz 21:00 - Bodegas González Byass - Tío Pepe</t>
+  </si>
+  <si>
+    <t>04 de Julio del 2026 - 09 de Agosto del 2026 | A las 21:00 horas</t>
+  </si>
+  <si>
+    <t>Calle Manuel María González, 12, Jerez de la Frontera. Cádiz - Bodegas Tío Pepe</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-del-ciclo-solera-y-compas</t>
+  </si>
+  <si>
+    <t>Programación especial de verano del Centro Andaluz de las Letras en Cádiz</t>
+  </si>
+  <si>
+    <t>Centro Andaluz de las Letras Título actividad: “El pensamiento erótico” Descripción breve: Encuentro con Sara Torres, con motivo de la publicación de ‘El pensamiento erótico’ (Ed. Reservoir Books), en conversación con Carmen Rojas y Mar Gallego. Lugar: Baluarte de la Candelaria Fecha: 01/07/26 Público destinatario: Adultos Horario    21:30:00 Duración: 90 minutos Aforo/ Entrada libre: Entrada libre Enlace web Observaciones: Esta actividad en colaboración con la Feria del Libro de Cádiz se enmarca en el Ciclo  del Centro “Pensar en Compañía” Título actividad: “Falla y la Literatura. 150 aniversario de su nacimiento” Descripción breve: Mesa redonda con José Ramón Ripoll, Katia-Sofía Hakim y Dácil González Mesa. Lugar:  Baluarte de la Candelaria Fecha: 05/07/26 Público destinatario: General Horario: 12:30:00 Duración: 90 minutos Aforo/ Entrada libre: Entrada libre Enlace web Observaciones: Esta actividad en colaboración con la Feria del Libro de Cádiz se enmarca en el Ciclo del Centro “ Falla y la Literatura. 150 aniversario de su nacimiento” Título actividad: “José Manuel Caballero Bonald. La aventura de escribir" Descripción breve: Exposición itinerante y biográfica, comisariada por Felipe Benítez Reyes y producida por el Centro Andaluz de las Letras, que rinde homenaje a la figura y obra del poeta jerezano. Lugar: Universidad de Cádiz. Facultad de Filosofía y Letras. Biblioteca de Humanidades Fecha inicio: 31/04/26 Fecha fin: 31/07/26 Público destinatario: General Horario: lunes a viernes de 9:00 a 21:00 horas Aforo/ Entrada libre: Entrada libre Enlace web Observaciones: se clausurará el 31 de julio</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 31 de Julio del 2026</t>
+  </si>
+  <si>
+    <t>Alameda Hermanas Carvia Bernal, 6, Cádiz. Cádiz - Baluarte de la Candelaria</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-especial-de-verano-del-centro-andaluz-de-las-letras-en-cadiz</t>
+  </si>
+  <si>
+    <t>Programación especial de verano en el Archivo Histórico Provincial de Cádiz</t>
+  </si>
+  <si>
+    <t>Archivo Histórico Provincial Documento destacado bimensual de Julio-Agosto: Cádiz, 250 años de relaciones transatlánticas con los Estados Unidos. Exposición presencial y virtual. Coincidiendo este mes de julio con la celebración de los 250 años de la constitución de los Estados Unidos de América, este archivo realizará esta actividad, que pretenderá narrar las prolijas y extensas relaciones a lo largo del tiempo entre la ciudad gaditana y este país norteamericano. Estará a disposición del público presencialmente en la sede física de este archivo, los días laborales de 09.00 h. a 14.00 h. y en la página web de este archivo dentro de la Web de Archivos de Andalucía en el apartado el archivo recomienda y documentos destacados.</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 31 de Agosto del 2026</t>
+  </si>
+  <si>
+    <t>Calle Cristóbal Colón, 12, Cádiz. Cádiz - Archivo Histórico Provincial de Cádiz</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-especial-de-verano-en-el-archivo-historico-provincial-de-cadiz</t>
+  </si>
+  <si>
+    <t>Quererte a medias (cuarteto)</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Maui DURACIÓN: 90' Maui de Utrera presenta ‘Quererte a medias’, un concierto diferente, una nueva performance con aires de fiesta, una feria de canciones a todo color, un abanico de historias contadas y cantadas que celebran el amor, la vida y la guasa con el público como protagonista. Deshojando margaritas y convocando al duende, la de Utrera nos adentra en curiosas aventuras y desventuras amorosas de toda índole, tomando la risa como remedio infalible ante el desencanto. Aires de rumba, bulería o alegrías impregnan este simpático repertorio que zarandea al espectador por dentro y por fuera, a modo experiencia terapéutica, logrando aumentar exponencialmente las ganas de exprimir la vida. "Quererte a medias" se estrena con una puesta en escena sorprendente en la que se rompe la cuarta pared para implicar al espectador en el misterio, la alegría y la cercanía propia de los mejores convites. Disfrutaremos de sus últimas canciones y seremos partícipes del estreno de temas inéditos que se visten de lentejuelas para la ocasión.</t>
+  </si>
+  <si>
+    <t>17 de Octubre del 2026 | A las 21:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/quererte-medias-cuarteto-2</t>
+  </si>
+  <si>
+    <t>Rota: programación verano cultural y juvenil</t>
+  </si>
+  <si>
+    <t>📍 Castillo de Luna 📍 Auditorio Municipal Alcalde Felipe Benítez 📍 Plaza Bartolomé Pérez 📍 Plaza de la Merced 📍 Costa Ballena 📍 Parroquia Ntra. Sra. de la O
 Miércoles 1 22:00 h: Ciclo Miércoles Flamenco con "Yerma" , por Laura Pirri📍 Plaza Bartolomé Pérez. Jueves 2 21:30 h: Pasacalles "La dama de trapos" , por la Cía. Alas Circo Teatro📍 Inicio en la Plaza Bartolomé Pérez. Viernes 3 21:30 h: X Festival de Títeres: "Hansel y Gretel" , de Atrapante Teatro📍 Patio del Castillo de Luna. Sábado 4 21:00 h: "Quijote Roja" , por la Cía. El 13 Artes Escénicas📍 Teatro Auditorio Municipal Alcalde Felipe Benítez 💶 Precio: 15 € . 21:30 h: X Festival de Títeres: "Alejandra y sus dragones" , de Pequeños Duendes📍 Jardín Trasero del C.C. Costa Ballena. Martes 7 21:30 h: Ciclo Martes Clásicos . Concierto de piano y chelo, por Pablo Linares y Luca Cianciotta📍 Patio del Castillo de Luna💶 Precio: 4 € . Miércoles 8 21:00 h: Proyección de la película "El vampiro de Düsseldorf" , por Cine Club Super 8📍 Auditorio Severiano Alonso. 22:00 h: Concierto Harmoni Fusion 📍 Plaza Bartolomé Pérez. Sábado 11 22:00 h: Espectáculo flamenco "La semblanza de un río" , con Rocío Sánchez📍 Jardín Trasero del C.C. Costa Ballena. Lunes 13 21:00 h: Concierto de órgano histórico📍 Parroquia Nuestra Señora de la O. Martes 14 21:30 h: Ciclo Martes Clásicos con el concierto "Sonidos del mundo" (clarinete y piano), por Vera Paulova y Antonio Quintero📍 Patio del Castillo de Luna. 💶 Precio: 4 € . Miércoles 15 19:00 h: Procesión Marítima de Nuestra Señora del Carmen. 21:00 h: Concierto "10 Locos Años Descalzos" , de Pedro Pastor📍 Teatro Auditorio Municipal Alcalde Felipe Benítez. Jueves 16 19:30 h: Procesión de Nuestra Señora del Carmen. Viernes 17 21:30 h: Teatro "Historia de una Escalera" , por la Cía. Bombastic Teatro📍 Patio del Castillo de Luna. Sábado 18 21:30 h: XXXII Encuentro de Corales: Orfeón Virgen de la Escalera de Rota y Coral de Almendralejo 📍 Patio del Castillo de Luna. 22:00 h: Ciclo de Teatro "Mientras quede voz" , por la Asoc. Pag. en Blanco y Bombastic Teatro📍 Jardín Trasero del Centro Cultural Costa Ballena. Lunes 20 20:30 h: Presentación del libro "Arturito" , de Belinda Placek📍 Salón Multiusos del Castillo de Luna. Martes 21 22:00 h: Ciclo de Jazz "De Cádiz a Nueva York" , con Antonio Lizana (Red Andaluza de Teatros Públicos) 📍 Plaza de la Merced. Del 22 al 25 de julio Feria del Libro "Almudena Grandes" 📍 Patio del Castillo de Luna y Plaza Bartolomé Pérez. Del 30 de julio al 2 de agosto Fiesta de la Urta. EXPOSICIONES EN LA SALA INTERMODAL DE COSTA BALLENA 1-15 DE JULIO: Exposición de pinturas de Ricardo Humbría 16-30 DE AGOSTO: Exposición de pinturas 'Sui generis' de Esteban Doncel EXPOSICIONES EN LA SALA DEL CASTILLO DE LUNA 1-15 DE JULIO: Exposición de pinturas de Moustafa Loulanti 16-30 DE AGOSTO: Exposición colectiva Rotarte</t>
   </si>
   <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 31 de Julio del 2026 | Diferentes horarios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Cuna, 2 - Castillo de Luna. 11520 Rota (Cádiz), Rota. Cádiz - Rota. Castillo de Luna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/rota-programacion-verano-cultural-y-juvenil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samba do raíz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Marta Santamaría DURACIÓN: 1 hora y 15 min Samba de raiz Recorre en un repertorio inigualable la tradición popular de samba de raiz , que es el samba que popularmente se ha mantenido y conservado con fuerza en panorama musical de Brasil. Es una selección de composiciones clásicas que por su ritmo y dificultad interpretativa requieren una mayor destreza que las baladas de Bossa nova que conocemos , y que son un estilo posterior al samba . La temática es la lucha por la felicidad y la reflexión universal sobre el amor . Es común encontrar estas composiciones en rodas de samba y pagodes que son las reuniones donde la comunidad de samba se reúne. Incluso fuera de Brasil existen comunidades que rinden homenaje a este estilo por su energía transformadora y su alegría.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 de Agosto del 2026 | A las 22:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Torre de la Esquina, s/n, Arcos de la Frontera. Cádiz - Plaza del Sindicato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/samba-do-raiz-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sketches of Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Pablo Egea DURACIÓN: 60 minutos Propuesta escénica de danza-teatro donde el bailaor y coreógrafo Pablo Egea junto con el trompetista utrerano de flamenco-jazz Javier Romero proponen un serie de “sketches” (bocetos) coreográficos, inspirándose en cada uno de los temas del mítico álbum de jazz “Sketches of Spain” del célebre trompetista e icono del jazz Miles Davis. Esta obra supone un viaje emocional donde la danza española y el baile flamenco son el instrumento y el jazz la inspiración.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 de Noviembre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/sketches-spain-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tagarnina Fest en Algodonales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II TAGARNINA FEST ALGODONALES. Del 20 al 22 de agosto. La localidad gaditana de Algodonales se prepara para recibir la II edición de Tagarnina Fest, que cuenta con la colaboración del Instituto Andaluz del Flamenco. Todas las actividades serán de acceso gratuito. El programa es el siguiente: 20 de agosto . A las 21:30 horas, Alejandro Rodríguez impartirá la master class familiar ‘Tor pueblo a la plaza a bailar por tangos’. A las 23:00 horas tendrá lugar la gala flamenca ‘De Tablao’, con la participación de Mari Ángeles Gabaldón, Rafael Campallo, José Anillo, Manuel Gago y J. Antonio Gómez . Ambas actividades se celebrarán en la Plaza de la Constitución. 21 de agosto . A las 22:00 horas, ‘Retrospectiva 2.0 (Danza Española Renovada)’, a cargo de Daniel Doña Compañía (DDCdanza). A las 23:00 horas será el turno de ‘Mujeres de Bandera’, protagonizado por Antonia Jiménez, Naike Ponce y Ana Almagro . Los espectáculos tendrán lugar en el Conjunto Monumental Fuente Alta. 22 de agosto . A las 22:30 horas, el Pórtico del Ayuntamiento acogerá el espectáculo ‘Recreo’, de la compañía de María Moreno .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 de Agosto del 2026 - 22 de Agosto del 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avenida de Andalucia 2, Algodonales. Cádiz - Algodonales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tagarnina-fest-en-algodonales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taller 'cambia la mirada'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taller inmersivo de creación sonoro-visual dirigido por Music Komité que propone explorar el lenguaje audiovisual mediante la experimentación con imagen, sonido y nuevas tecnologías. Una experiencia participativa donde la creatividad, la improvisación y el trabajo colectivo se convierten en herramientas para descubrir nuevas formas de percibir y crear.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 de Agosto del 2026 | 10:30h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-cambia-la-mirada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taller 'collage textil y pintura en hilo'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taller creativo dirigido por Virginia Filardi y Debaga que invita a experimentar con el collage, el bordado y otras técnicas textiles desde una mirada contemporánea. A través de la combinación de imagen, materia e hilo, los participantes crearán piezas personales que exploran la relación entre arte, identidad y paisaje.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 de Septiembre del 2026 | 10:30h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-collage-textil-y-pintura-en-hilo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taller de dibujo 'Entre pinos'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Un taller de dibujo al aire libre para descubrir los pinos de la Fundación Montenmedio Contemporánea desde una mirada atenta y creativa. Guiados por la artista Anna Bellinger, los participantes explorarán la forma, la textura y la estructura de los árboles mediante la observación, el tacto y el dibujo, utilizando materiales sencillos y sin necesidad de experiencia previa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 de Julio del 2026 | 10:15h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-de-dibujo-entre-pinos-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuyo Cid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Malaje Sólo DURACIÓN: 60 minutos La letra con humor entra
+    <t>01 de Julio del 2026 - 31 de Julio del 2026 | Diferentes horarios</t>
+  </si>
+  <si>
+    <t>Calle Cuna, 2 - Castillo de Luna. 11520 Rota (Cádiz), Rota. Cádiz - Rota. Castillo de Luna</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/rota-programacion-verano-cultural-y-juvenil</t>
+  </si>
+  <si>
+    <t>Samba do raíz</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Marta Santamaría DURACIÓN: 1 hora y 15 min Samba de raiz Recorre en un repertorio inigualable la tradición popular de samba de raiz , que es el samba que popularmente se ha mantenido y conservado con fuerza en panorama musical de Brasil. Es una selección de composiciones clásicas que por su ritmo y dificultad interpretativa requieren una mayor destreza que las baladas de Bossa nova que conocemos , y que son un estilo posterior al samba . La temática es la lucha por la felicidad y la reflexión universal sobre el amor . Es común encontrar estas composiciones en rodas de samba y pagodes que son las reuniones donde la comunidad de samba se reúne. Incluso fuera de Brasil existen comunidades que rinden homenaje a este estilo por su energía transformadora y su alegría.</t>
+  </si>
+  <si>
+    <t>15 de Agosto del 2026 | A las 22:00</t>
+  </si>
+  <si>
+    <t>Calle Torre de la Esquina, s/n, Arcos de la Frontera. Cádiz - Plaza del Sindicato</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/samba-do-raiz-1</t>
+  </si>
+  <si>
+    <t>Sketches of Spain</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Pablo Egea DURACIÓN: 60 minutos Propuesta escénica de danza-teatro donde el bailaor y coreógrafo Pablo Egea junto con el trompetista utrerano de flamenco-jazz Javier Romero proponen un serie de “sketches” (bocetos) coreográficos, inspirándose en cada uno de los temas del mítico álbum de jazz “Sketches of Spain” del célebre trompetista e icono del jazz Miles Davis. Esta obra supone un viaje emocional donde la danza española y el baile flamenco son el instrumento y el jazz la inspiración.</t>
+  </si>
+  <si>
+    <t>19 de Noviembre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/sketches-spain-3</t>
+  </si>
+  <si>
+    <t>Tagarnina Fest en Algodonales</t>
+  </si>
+  <si>
+    <t>II TAGARNINA FEST ALGODONALES. Del 20 al 22 de agosto. La localidad gaditana de Algodonales se prepara para recibir la II edición de Tagarnina Fest, que cuenta con la colaboración del Instituto Andaluz del Flamenco. Todas las actividades serán de acceso gratuito. El programa es el siguiente: 20 de agosto . A las 21:30 horas, Alejandro Rodríguez impartirá la master class familiar ‘Tor pueblo a la plaza a bailar por tangos’. A las 23:00 horas tendrá lugar la gala flamenca ‘De Tablao’, con la participación de Mari Ángeles Gabaldón, Rafael Campallo, José Anillo, Manuel Gago y J. Antonio Gómez . Ambas actividades se celebrarán en la Plaza de la Constitución. 21 de agosto . A las 22:00 horas, ‘Retrospectiva 2.0 (Danza Española Renovada)’, a cargo de Daniel Doña Compañía (DDCdanza). A las 23:00 horas será el turno de ‘Mujeres de Bandera’, protagonizado por Antonia Jiménez, Naike Ponce y Ana Almagro . Los espectáculos tendrán lugar en el Conjunto Monumental Fuente Alta. 22 de agosto . A las 22:30 horas, el Pórtico del Ayuntamiento acogerá el espectáculo ‘Recreo’, de la compañía de María Moreno .</t>
+  </si>
+  <si>
+    <t>20 de Agosto del 2026 - 22 de Agosto del 2026</t>
+  </si>
+  <si>
+    <t>Avenida de Andalucia 2, Algodonales. Cádiz - Algodonales</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tagarnina-fest-en-algodonales</t>
+  </si>
+  <si>
+    <t>Taller 'cambia la mirada'</t>
+  </si>
+  <si>
+    <t>Taller inmersivo de creación sonoro-visual dirigido por Music Komité que propone explorar el lenguaje audiovisual mediante la experimentación con imagen, sonido y nuevas tecnologías. Una experiencia participativa donde la creatividad, la improvisación y el trabajo colectivo se convierten en herramientas para descubrir nuevas formas de percibir y crear.</t>
+  </si>
+  <si>
+    <t>22 de Agosto del 2026 | 10:30h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-cambia-la-mirada</t>
+  </si>
+  <si>
+    <t>Taller 'collage textil y pintura en hilo'</t>
+  </si>
+  <si>
+    <t>Taller creativo dirigido por Virginia Filardi y Debaga que invita a experimentar con el collage, el bordado y otras técnicas textiles desde una mirada contemporánea. A través de la combinación de imagen, materia e hilo, los participantes crearán piezas personales que exploran la relación entre arte, identidad y paisaje.</t>
+  </si>
+  <si>
+    <t>05 de Septiembre del 2026 | 10:30h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-collage-textil-y-pintura-en-hilo</t>
+  </si>
+  <si>
+    <t>Taller de dibujo 'Entre pinos'</t>
+  </si>
+  <si>
+    <t>Un taller de dibujo al aire libre para descubrir los pinos de la Fundación Montenmedio Contemporánea desde una mirada atenta y creativa. Guiados por la artista Anna Bellinger, los participantes explorarán la forma, la textura y la estructura de los árboles mediante la observación, el tacto y el dibujo, utilizando materiales sencillos y sin necesidad de experiencia previa.</t>
+  </si>
+  <si>
+    <t>29 de Julio del 2026 | 10:15h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-de-dibujo-entre-pinos-1</t>
+  </si>
+  <si>
+    <t>Tuyo Cid</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Malaje Sólo DURACIÓN: 60 minutos La letra con humor entra
 TUYO CID Viaje a los orígenes de la literaltura española.
 Tuyo Cid, por un lado, es un homenaje al origen de mi oficio, los juglares, esos primeros cómicos que difundían en las plazas la tradición oral narrando gestas, hazañas, leyendas… Y, por otro, una comedia que repasa los inicios de nuestra historia de la literatura y ofrece una mirada muy desenfada del primer texto escrito en castellano conocido, el Poema de Mio Cid. Respetando el argumento original, mediante la actualización de datos, el humor, la interacción, la utilización de sencillos efectos especiales y algunos otros recursos escénicos, se busca despertar el interés por uno de nuestros clásicos más representativos…</t>
   </si>
   <si>
-    <t xml:space="preserve">09 de Octubre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 de Noviembre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 de Noviembre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tío Pepe Festival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El TÍO PEPE FESTIVAL nace en el verano de 2014 con la intención de ofrecer un espacio cultural único y un lugar de encuentro privilegiado en el entorno de Jerez (y, por extensión, la bahía de Cádiz), sobre la base de proponer una experiencia sensorial múltiple y exclusiva, íntimamente ligada a la bodega y al vino, la tradición, la cultura y la gastronomía. Programación (primeras confirmaciones) RAPHAEL, 4 de julio DEEP PURPLE, 10 de julio PASTORA SOLER, 11 de julio MANU SÁNCHEZ, 17 de julio SERGIO DALMA, 18 de julio G5, 19 de julio EL MONAGUILLO, 23 de julio ANTOÑITO MOLINA, 25 de julio ISRAEL FERNÁNDEZ, 26 de julio NOCHE DE ROCK&amp;ROLL, 31 de julio LUZ CASAL, 2 de agosto M-CLAN, 4 de agosto GOD SAVE THE QUEEN, 6 de agosto ISMAEL JORDI, SABELA PUÉRTOLAS Y ÓLIVER DÍAZ, 9 de agosto Y MUCHOS MÁS Los espectáculos pueden completarse con exclusivas cenas con Chef Estrellas Michelín.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04 de Julio del 2026 - 09 de Agosto del 2026 | 21:30 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle de Manuel María González, 12, Jerez de la Frontera. Cádiz - Bodegas González Byass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tio-pepe-festival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Un dúo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Laura Morales DURACIÓN: 00:15 Primer Premio Certamen Coreográfico Nacional CREA, dentro del Festival Mudanzas, 2024. 
+    <t>09 de Octubre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-7</t>
+  </si>
+  <si>
+    <t>06 de Noviembre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-4</t>
+  </si>
+  <si>
+    <t>07 de Noviembre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-1</t>
+  </si>
+  <si>
+    <t>Tío Pepe Festival</t>
+  </si>
+  <si>
+    <t>El TÍO PEPE FESTIVAL nace en el verano de 2014 con la intención de ofrecer un espacio cultural único y un lugar de encuentro privilegiado en el entorno de Jerez (y, por extensión, la bahía de Cádiz), sobre la base de proponer una experiencia sensorial múltiple y exclusiva, íntimamente ligada a la bodega y al vino, la tradición, la cultura y la gastronomía. Programación (primeras confirmaciones) RAPHAEL, 4 de julio DEEP PURPLE, 10 de julio PASTORA SOLER, 11 de julio MANU SÁNCHEZ, 17 de julio SERGIO DALMA, 18 de julio G5, 19 de julio EL MONAGUILLO, 23 de julio ANTOÑITO MOLINA, 25 de julio ISRAEL FERNÁNDEZ, 26 de julio NOCHE DE ROCK&amp;ROLL, 31 de julio LUZ CASAL, 2 de agosto M-CLAN, 4 de agosto GOD SAVE THE QUEEN, 6 de agosto ISMAEL JORDI, SABELA PUÉRTOLAS Y ÓLIVER DÍAZ, 9 de agosto Y MUCHOS MÁS Los espectáculos pueden completarse con exclusivas cenas con Chef Estrellas Michelín.</t>
+  </si>
+  <si>
+    <t>04 de Julio del 2026 - 09 de Agosto del 2026 | 21:30 horas</t>
+  </si>
+  <si>
+    <t>Calle de Manuel María González, 12, Jerez de la Frontera. Cádiz - Bodegas González Byass</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tio-pepe-festival</t>
+  </si>
+  <si>
+    <t>Un dúo</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Laura Morales DURACIÓN: 00:15 Primer Premio Certamen Coreográfico Nacional CREA, dentro del Festival Mudanzas, 2024. 
 Puedo escribir los versos más tristes para explicar qué es UN DÚO, pero os lo vamos a bailar.
 Un dúo es la agrupación perfecta para una pieza de danza.
 UN DÚO son dos. Como flik y flak en un reloj.
@@ -1540,204 +1545,204 @@
 Nuestro Romeo y Julieta de la danza.</t>
   </si>
   <si>
-    <t xml:space="preserve">10 de Octubre del 2026 | A las 18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avenida de la Feria, Villamartín. Cádiz - Jardines del Museo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/un-duo-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Un trocito de Luna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: A la Sombrita DURACIÓN: 45 minutos Sinopsis argumental
+    <t>10 de Octubre del 2026 | A las 18:00</t>
+  </si>
+  <si>
+    <t>Avenida de la Feria, Villamartín. Cádiz - Jardines del Museo</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/un-duo-6</t>
+  </si>
+  <si>
+    <t>Un trocito de Luna</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: A la Sombrita DURACIÓN: 45 minutos Sinopsis argumental
 ¿Quién no soñó alguna vez con darle un mordisco a la luna?
 Este fue precisamente el deseo de los animales de este cuento. Tan solo querían probar un trocito pero, por más que se estiraban, no eran capaces de tocarla.
 Esta es una historia de deseos que parecen –a primera vista- inalcanzables, como la luna, pero que consiguen hacerse realidad gracias a la colaboración. Una ayuda mutua de la que son partícipes los más variados animales.
 A medio camino entre la fábula y la leyenda, este relato le ofrece una poética moraleja que habla de generosidad, solidaridad y sueños compartidos.</t>
   </si>
   <si>
-    <t xml:space="preserve">30 de Agosto del 2026 | A las 21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/un-trocito-de-luna-39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una Historia de Mujeres en el Jazz, en Puerto Real</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Four Women Quartet DURACIÓN: 65 min. Este concierto recorre musicalmente las vidas, luchas y logros de mujeres artistas que se abrieron paso en un mundo en el que estaban predestinadas a ocupar un papel secundario,mostrando así el poder transformador del género del Jazz. “Una Historia de Mujeres En El Jazz” arranca desde sus raíces africanas con el sonido de las canciones de trabajo de las esclavas y el Blues. Continúa el recorrido recordando el Hot Jazz de Chicago y la gran era del Swing y sus Big Bands. En los años 40 aparece el Bebop como movimiento musical que contrasta con cualquier otro estilo previo. Los años 50 y 60 dan paso a las movilizaciones por los derechos civiles y estos provocan el resurgir del sonido de los orígenes, la vuelta a lo tradicional como reivindicación identitaria y cultural. El viaje finaliza en la época actual, con la música de mujeres que se encuentran en la vanguardia del Jazz Contemporáneo. A lo largo de la historia, las mujeres no han dejado de reinventarse, de explorar, proponer, crear y, muchas de sus aportaciones han sido determinantes en el salto a la modernidad artística. Programa 1.Work song &amp; Abbey Lincoln – Hoe Ema Hoe / Afro Blue 2.Alberta Hunter - Down Hearted Blues 3.Lilian Hardin - Born to Swing 4.Ann Ronell- Willow Weep For Me 5.Ivie Anderson - It Don’t Mean A Thing 6.Dorothy Fields - On The Sunny Side Of The Street 7.Irene Higginbotham- Good Morning Heartache 8.Carmen McRae - The Best Is Yet To Come 9.Sheila Jordan – Antropology 10.Anita O’ Day - Sweet Georgia Brown 11.Betty Carter - Tight 12.Maria Schneider - Walking by Flashlight 13.Nina Simone - Four Women / Ain’t Got No, I Got Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 de Noviembre del 2026 | A las 19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/una-historia-de-mujeres-en-el-jazz-en-puerto-real</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verano 2026: programación de la Red Andaluza de Teatros Públicos en Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Andaluza de Teatros Públicos El Instituto Andaluz de las Artes Escénicas y de la Música (IAAEM) gestiona la Red Andaluza de Teatros Públicos , una iniciativa de la Agencia Andaluza de Instituciones Culturales. Su objetivo es difundir el teatro, la danza, la música y el circo en decenas de municipios de Andalucía. En distintos municipios de la provincia de Almería se han organizado para la campaña veraniega actividades que puedes conocer AQUÍ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 31 de Agosto del 2026 | Diferentes horarios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">, . Cádiz - En varias localidades de la provincia de Cádiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/verano-2026-programacion-de-la-red-andaluza-de-teatros-publicos-en-cadiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verano en Baelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 30 de Agosto del 2026 | Del 21 de junio al 20 de septiembre: de martes a domingo de 09:00 a 15:00 h.  Lunes cerrado (excepto víspera de festivo que abrimos de 9:00 a 15:00 h). Última entrada permitida: 30 minutos antes del cierre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01 de Julio del 2026 - 30 de Agosto del 2026 Del 21 de junio al 20 de septiembre: de martes a domingo de 09:00 a 15:00 h.  Lunes cerrado (excepto víspera de festivo que abrimos de 9:00 a 15:00 h). Última entrada permitida: 30 minutos antes del cierre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/verano-en-baelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visita guiada a la Fundación Montenmedio Contemporánea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una visita guiada que invita a descubrir el parque de esculturas a través de un recorrido por el paisaje y el arte contemporáneo. Acompañados por el equipo de la Fundación Montenmedio Contemporánea, los visitantes conocerán la historia del proyecto, el diálogo entre las obras y el entorno natural, así como las claves para comprender una colección única integrada en el bosque.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-la-fundacion-montenmedio-contemporanea-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 de Agosto del 2026 | 10:30h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-la-fundacion-montenmedio-contemporanea-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visita guiada bajo la luna llena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una experiencia nocturna que permite descubrir el parque de esculturas bajo una atmósfera mágica. Acompañados por personal de la Fundación Montenmedio Contemporánea, los visitantes recorrerán el bosque entre luces y sombras, activando nuevas lecturas de las piezas instaladas en la naturaleza.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 de Julio del 2026 | 22:00h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-bajo-la-luna-llena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 de Agosto del 2026 | 22:00h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-bajo-la-luna-llena-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: David Cebrian DURACIÓN: 55 min Un hombre de 48 años consigue el sueño de su vida: comprarse una vivienda e independizarse. En la inmobiliaria le han dicho que es una vivienda pequeña y antigua, pero con encanto. Diáfana y con un buen cuarto de baño. En la realidad quizás sea más pequeña y más antigua. Y quizás no tenga tanto encanto. Lo mejor de la casa es el cuarto de baño. Lo peor, también es el cuarto de baño. Es que la casa es un cuarto de baño… W.C. es una comedia no escatológica de un solo acto para wáter closet y clown, donde poder fisgonear, curiosear y cotillear a un señor que encuentra su independencia y se emancipa en un lugar adecuado a sus posibilidades. Las dificultades que presenta este lugar, la resignación y las reacciones del personaje a esta desesperante situación, ofrecerán al espectador una comedia absurda e hilarante. Una obra sin palabras, con imágenes reconociblemente imposibles y elementos sorpresivos y absurdos para todos los públicos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 de Octubre del 2026 | A las 18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/wc-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XIX Festival de Chipiona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XIX Festival de Chipiona: 18 conciertos para disfrutar del verano en el claustro del Santuario y el Hotel Al Sur de Chipiona.
+    <t>30 de Agosto del 2026 | A las 21:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/un-trocito-de-luna-39</t>
+  </si>
+  <si>
+    <t>Una Historia de Mujeres en el Jazz, en Puerto Real</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Four Women Quartet DURACIÓN: 65 min. Este concierto recorre musicalmente las vidas, luchas y logros de mujeres artistas que se abrieron paso en un mundo en el que estaban predestinadas a ocupar un papel secundario,mostrando así el poder transformador del género del Jazz. “Una Historia de Mujeres En El Jazz” arranca desde sus raíces africanas con el sonido de las canciones de trabajo de las esclavas y el Blues. Continúa el recorrido recordando el Hot Jazz de Chicago y la gran era del Swing y sus Big Bands. En los años 40 aparece el Bebop como movimiento musical que contrasta con cualquier otro estilo previo. Los años 50 y 60 dan paso a las movilizaciones por los derechos civiles y estos provocan el resurgir del sonido de los orígenes, la vuelta a lo tradicional como reivindicación identitaria y cultural. El viaje finaliza en la época actual, con la música de mujeres que se encuentran en la vanguardia del Jazz Contemporáneo. A lo largo de la historia, las mujeres no han dejado de reinventarse, de explorar, proponer, crear y, muchas de sus aportaciones han sido determinantes en el salto a la modernidad artística. Programa 1.Work song &amp; Abbey Lincoln – Hoe Ema Hoe / Afro Blue 2.Alberta Hunter - Down Hearted Blues 3.Lilian Hardin - Born to Swing 4.Ann Ronell- Willow Weep For Me 5.Ivie Anderson - It Don’t Mean A Thing 6.Dorothy Fields - On The Sunny Side Of The Street 7.Irene Higginbotham- Good Morning Heartache 8.Carmen McRae - The Best Is Yet To Come 9.Sheila Jordan – Antropology 10.Anita O’ Day - Sweet Georgia Brown 11.Betty Carter - Tight 12.Maria Schneider - Walking by Flashlight 13.Nina Simone - Four Women / Ain’t Got No, I Got Life</t>
+  </si>
+  <si>
+    <t>06 de Noviembre del 2026 | A las 19:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/una-historia-de-mujeres-en-el-jazz-en-puerto-real</t>
+  </si>
+  <si>
+    <t>Verano 2026: programación de la Red Andaluza de Teatros Públicos en Cádiz</t>
+  </si>
+  <si>
+    <t>Red Andaluza de Teatros Públicos El Instituto Andaluz de las Artes Escénicas y de la Música (IAAEM) gestiona la Red Andaluza de Teatros Públicos , una iniciativa de la Agencia Andaluza de Instituciones Culturales. Su objetivo es difundir el teatro, la danza, la música y el circo en decenas de municipios de Andalucía. En distintos municipios de la provincia de Almería se han organizado para la campaña veraniega actividades que puedes conocer AQUÍ</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 31 de Agosto del 2026 | Diferentes horarios</t>
+  </si>
+  <si>
+    <t>, . Cádiz - En varias localidades de la provincia de Cádiz</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/verano-2026-programacion-de-la-red-andaluza-de-teatros-publicos-en-cadiz</t>
+  </si>
+  <si>
+    <t>Verano en Baelo</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 30 de Agosto del 2026 | Del 21 de junio al 20 de septiembre: de martes a domingo de 09:00 a 15:00 h.  Lunes cerrado (excepto víspera de festivo que abrimos de 9:00 a 15:00 h). Última entrada permitida: 30 minutos antes del cierre.</t>
+  </si>
+  <si>
+    <t>01 de Julio del 2026 - 30 de Agosto del 2026 Del 21 de junio al 20 de septiembre: de martes a domingo de 09:00 a 15:00 h.  Lunes cerrado (excepto víspera de festivo que abrimos de 9:00 a 15:00 h). Última entrada permitida: 30 minutos antes del cierre.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/verano-en-baelo</t>
+  </si>
+  <si>
+    <t>Visita guiada a la Fundación Montenmedio Contemporánea</t>
+  </si>
+  <si>
+    <t>Una visita guiada que invita a descubrir el parque de esculturas a través de un recorrido por el paisaje y el arte contemporáneo. Acompañados por el equipo de la Fundación Montenmedio Contemporánea, los visitantes conocerán la historia del proyecto, el diálogo entre las obras y el entorno natural, así como las claves para comprender una colección única integrada en el bosque.</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-la-fundacion-montenmedio-contemporanea-1</t>
+  </si>
+  <si>
+    <t>20 de Agosto del 2026 | 10:30h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-la-fundacion-montenmedio-contemporanea-2</t>
+  </si>
+  <si>
+    <t>Visita guiada bajo la luna llena</t>
+  </si>
+  <si>
+    <t>Una experiencia nocturna que permite descubrir el parque de esculturas bajo una atmósfera mágica. Acompañados por personal de la Fundación Montenmedio Contemporánea, los visitantes recorrerán el bosque entre luces y sombras, activando nuevas lecturas de las piezas instaladas en la naturaleza.</t>
+  </si>
+  <si>
+    <t>29 de Julio del 2026 | 22:00h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-bajo-la-luna-llena</t>
+  </si>
+  <si>
+    <t>28 de Agosto del 2026 | 22:00h</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-bajo-la-luna-llena-0</t>
+  </si>
+  <si>
+    <t>WC</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: David Cebrian DURACIÓN: 55 min Un hombre de 48 años consigue el sueño de su vida: comprarse una vivienda e independizarse. En la inmobiliaria le han dicho que es una vivienda pequeña y antigua, pero con encanto. Diáfana y con un buen cuarto de baño. En la realidad quizás sea más pequeña y más antigua. Y quizás no tenga tanto encanto. Lo mejor de la casa es el cuarto de baño. Lo peor, también es el cuarto de baño. Es que la casa es un cuarto de baño… W.C. es una comedia no escatológica de un solo acto para wáter closet y clown, donde poder fisgonear, curiosear y cotillear a un señor que encuentra su independencia y se emancipa en un lugar adecuado a sus posibilidades. Las dificultades que presenta este lugar, la resignación y las reacciones del personaje a esta desesperante situación, ofrecerán al espectador una comedia absurda e hilarante. Una obra sin palabras, con imágenes reconociblemente imposibles y elementos sorpresivos y absurdos para todos los públicos.</t>
+  </si>
+  <si>
+    <t>25 de Octubre del 2026 | A las 18:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/wc-22</t>
+  </si>
+  <si>
+    <t>XIX Festival de Chipiona</t>
+  </si>
+  <si>
+    <t>XIX Festival de Chipiona: 18 conciertos para disfrutar del verano en el claustro del Santuario y el Hotel Al Sur de Chipiona.
 Este es el listado oficial de los 18 conciertos programados para el XIX Festival de Música Ciudad de Chipiona organizado por Juventudes Musicales de Chipiona. PROGRAMACIÓN JUNIO 27/06 · 21:30 — Orquesta Joven Camerata de Jerez · Claustro del Santuario de Regla JULIO 03/07 · 21:30 — Joven Orquesta de Cámara de Sevilla · Claustro del Santuario de Regla 10/07 · 21:30 — Joven Orquesta Barroca de Sevilla · Claustro del Santuario de Regla 14/07 · 21:30 — Trío Benlliure · Hotel Al Sur de Chipiona 17/07 · 21:30 — Orquesta y Coro San Felipe Neri de Sevilla · Claustro del Santuario de Regla 21/07 · 21:30 — Dúo Borany · Hotel Al Sur de Chipiona 24/07 · 21:30 — Keks Quintett · Claustro del Santuario de Regla 28/07 · 21:30 — Marta Roca (mezzosoprano) y Georgina Monsalves (piano) · Hotel Al Sur de Chipiona 31/07 · 21:30 — Cuarteto de Saxofones Esencia · Claustro del Santuario de Regla AGOSTO 04/08 · 21:30 — Escuela Bolera (María Chamorro Dorantes) · Claustro del Santuario de Regla 07/08 · 21:30 — Orquesta Flamenca · Claustro del Santuario de Regla 11/08 · 21:30 — Dúo Diáleg · Hotel Al Sur de Chipiona 14/08 · 21:30 — Guitarras de Luz y Sal · Claustro del Santuario de Regla 18/08 · 21:30 — Elena Cadierno Gómez y Mercedes Medina · Hotel Al Sur de Chipiona 21/08 · 21:30 — Grupo La Porteña Tango · Claustro del Santuario de Regla 25/08 · 21:30 — Julia Heras, Laura Cruz y Vera Pavlova · Hotel Al Sur de Chipiona 28/08 · 21:30 — Ensemble de Clarinetes de Cádiz · Hotel Al Sur de Chipiona SEPTIEMBRE 08/09 · 11:00 — Coro San Pedro Nolasco · Claustro del Santuario de Regla</t>
   </si>
   <si>
-    <t xml:space="preserve">27 de Junio del 2026 - 08 de Septiembre del 2026 | Todos los conciertos comienzan a las 21:30 horas, excepto el último que es a las 11:00 horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chipiona, Chipiona. Cádiz - Chipiona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/xix-festival-de-chipiona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yesterday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Manolo Carambolas DURACIÓN: 55 minutos Yesterday es un espectáculo fresco y divertido dedicado por completo al público infantil y familiar. Manolo Carambolas mezcla las distintas técnicas gestuales creando gags, cargadas de nuevas e ingeniosas situaciones gestuales, que mediante la espontaneidad, logra arrancar la carcajada y el aplauso del público. Es capaz de bucear dentro de un bar fotografiándose en un "fotomatón"...y todo esto cantando su canción preferida. Un espectáculo de circo, teatro visual, malabares y mucho humor sin palabras, donde el disfrute por parte del público está más que garantizado. Prepárense, aquí esta el "Electromimo"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 de Diciembre del 2026 | A las 17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/yesterday-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAMBRA DE LA BUENA SALVAJE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Isabel Vázquez DURACIÓN: 55 minutos «Si yo fuera fiel a mi naturaleza, una salvaje de mirada ancestral, gritaría hasta que se me saltaran las cuerdas vocales y después me las tragaría. Porque en ese último grito todo quedaría dicho. Pero, por encima de todo, si yo fuera fiel a mi naturaleza diría: no.» Ella, de entre todas las salvajes, sueña con ser la más descalza, la más bruta, la salvaje ejemplar. Una mujer que contiene a todas las mujeres. Un cuerpo que se debate entre lo que es y lo que se proyecta sobre él. Zambra de la buena salvaje es un grito, un desgarro, un ritual de desposesión. ¿Cómo recuperar tanto espacio perdido? ¿Cómo desdomesticarse? ¿Qué le ocurre a un cuerpo cuando es en otros, cuando se permite la furia, la risa, la reventaera?
+    <t>27 de Junio del 2026 - 08 de Septiembre del 2026 | Todos los conciertos comienzan a las 21:30 horas, excepto el último que es a las 11:00 horas</t>
+  </si>
+  <si>
+    <t>Chipiona, Chipiona. Cádiz - Chipiona</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/xix-festival-de-chipiona</t>
+  </si>
+  <si>
+    <t>Yesterday</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Manolo Carambolas DURACIÓN: 55 minutos Yesterday es un espectáculo fresco y divertido dedicado por completo al público infantil y familiar. Manolo Carambolas mezcla las distintas técnicas gestuales creando gags, cargadas de nuevas e ingeniosas situaciones gestuales, que mediante la espontaneidad, logra arrancar la carcajada y el aplauso del público. Es capaz de bucear dentro de un bar fotografiándose en un "fotomatón"...y todo esto cantando su canción preferida. Un espectáculo de circo, teatro visual, malabares y mucho humor sin palabras, donde el disfrute por parte del público está más que garantizado. Prepárense, aquí esta el "Electromimo"</t>
+  </si>
+  <si>
+    <t>05 de Diciembre del 2026 | A las 17:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/yesterday-18</t>
+  </si>
+  <si>
+    <t>ZAMBRA DE LA BUENA SALVAJE</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Isabel Vázquez DURACIÓN: 55 minutos «Si yo fuera fiel a mi naturaleza, una salvaje de mirada ancestral, gritaría hasta que se me saltaran las cuerdas vocales y después me las tragaría. Porque en ese último grito todo quedaría dicho. Pero, por encima de todo, si yo fuera fiel a mi naturaleza diría: no.» Ella, de entre todas las salvajes, sueña con ser la más descalza, la más bruta, la salvaje ejemplar. Una mujer que contiene a todas las mujeres. Un cuerpo que se debate entre lo que es y lo que se proyecta sobre él. Zambra de la buena salvaje es un grito, un desgarro, un ritual de desposesión. ¿Cómo recuperar tanto espacio perdido? ¿Cómo desdomesticarse? ¿Qué le ocurre a un cuerpo cuando es en otros, cuando se permite la furia, la risa, la reventaera?
 Danza, humor e irreverencia se entrelazan en un monólogo coral
 donde lo salvaje se traduce en un acto de resistencia colectiva. Un espectáculo que baila con la bestia, que se abre paso entre los escombros de la norma y que, sobre la tierra removida, siembra un mundo nuevo.</t>
   </si>
   <si>
-    <t xml:space="preserve">26 de Noviembre del 2026 | A las 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/zambra-de-la-buena-salvaje-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cual es mi nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Da.Te Danza DURACIÓN: 45 minutos Premio FETEN 2015 (Gijón) – Mejor Espectáculo para la infancia. / Premio FITC 2016 (Hungría) – Mejor Bailarina
+    <t>26 de Noviembre del 2026 | A las 20:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/zambra-de-la-buena-salvaje-1</t>
+  </si>
+  <si>
+    <t>cual es mi nombre</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Da.Te Danza DURACIÓN: 45 minutos Premio FETEN 2015 (Gijón) – Mejor Espectáculo para la infancia. / Premio FITC 2016 (Hungría) – Mejor Bailarina
 un sofá que es un tren, una alfombra convertida en espejo, una montaña de césped que se mueve, lámparas de amapola y tu y yo! 
 ¿cuál es tu nombre..? si, tu, ¿cómo te llamas? entra en nuestro espectáculo y diviértete, acaso importa cómo te llames?
 la identidad se fortalece con los años pero tú esencia esta en ti desde que naces, amas, ríes y lloras igual que cualquiera no importa ni tu ropa, ni de donde vengas, ni cual sea tú nombre. esto sucede durante la infancia, no cuentan las etiquetas, un mundo maravilloso nace antes nuestros ojos cuando lo único que necesitamos es nuestra imaginación y un amigo con el que compartir nuestros sueños.
 el niño/a reconocerá el lenguaje ligado al movimiento y esto, unido a la luz y la música, sumergirá al pequeño espectador en un clima familiar y divertido, captando su atención, sin necesidad de recurrir a efectos superficiales. cada objeto puede tener una utilidad y forma muy distinta a la que vemos, todo y todos podemos convertirnos en lo que imaginemos, en un globo, en un sillón, en ti… en esta historia todo es un juego, la búsqueda de tu nombre será muy entretenida, juega a mirar, mira jugando.</t>
   </si>
   <si>
-    <t xml:space="preserve">18 de Octubre del 2026 | A las 18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cual-es-mi-nombre-54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">las furias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: SilencioDanza DURACIÓN: 45 aproximadamente La cólera de Las Furias se ha despertado en pleno siglo XXI. Su aliento es el calor de un infierno lleno de brujas, arpías, féminas vengativas que se levantan en armas contra una sociedad patriarcal. Marcada la piel con el sentimiento de culpa, con el estigma incluso del no saber amar, Las Furias han vuelto del Infierno para vengar la historia
+    <t>18 de Octubre del 2026 | A las 18:00</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cual-es-mi-nombre-54</t>
+  </si>
+  <si>
+    <t>las furias</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: SilencioDanza DURACIÓN: 45 aproximadamente La cólera de Las Furias se ha despertado en pleno siglo XXI. Su aliento es el calor de un infierno lleno de brujas, arpías, féminas vengativas que se levantan en armas contra una sociedad patriarcal. Marcada la piel con el sentimiento de culpa, con el estigma incluso del no saber amar, Las Furias han vuelto del Infierno para vengar la historia
 de la mujer.
 Las Furias suponen una revisión del rol que la mujer ha venido cumpliendo a lo largo de la historia. Vista siempre a través de los ojos del hombre, esta nueva propuesta pretende marcar un giro en la producción de la compañía.
 El espectáculo ha sido premiado con el premio LORCA del teatro andalúz a mejor intérprete de danza y mejor espectáculo de danza 2022, premio Ateneo mejor dirección y mejor espectáculo de danza 2022, mención especial del jurado en los premios CINTA  2022</t>
   </si>
   <si>
-    <t xml:space="preserve">27 de Noviembre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/las-furias-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">molotov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: la buena compañia DURACIÓN: 60 Carlos García es un titiritero del montón que acaba en el calabozo después de un incidente en su última función. Lo pierde todo; a su compañero, a su novia, su tiempo y su bien más preciado: la ilusión. Pero, ¿qué nos queda cuando nos lo quitan todo? ¿Tiene limites la imaginación? Carlos decide crear un nuevo espectáculo durante su detención con un guardia como único espectador. Con él descubrirá que tienen más en común de lo que creen. Y es que cualquier revolución puede empezar incluso con la llama más pequeña. ¿Alguien tiene un mechero?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 de Noviembre del 2026 | A las 20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/molotov-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">río de luna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAÑÍA: Da.Te Danza DURACIÓN: 37 minutos Mejor Espectáculo de Danza en FETEN (Gijón, 2011)
+    <t>27 de Noviembre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/las-furias-13</t>
+  </si>
+  <si>
+    <t>molotov</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: la buena compañia DURACIÓN: 60 Carlos García es un titiritero del montón que acaba en el calabozo después de un incidente en su última función. Lo pierde todo; a su compañero, a su novia, su tiempo y su bien más preciado: la ilusión. Pero, ¿qué nos queda cuando nos lo quitan todo? ¿Tiene limites la imaginación? Carlos decide crear un nuevo espectáculo durante su detención con un guardia como único espectador. Con él descubrirá que tienen más en común de lo que creen. Y es que cualquier revolución puede empezar incluso con la llama más pequeña. ¿Alguien tiene un mechero?</t>
+  </si>
+  <si>
+    <t>28 de Noviembre del 2026 | A las 20:30</t>
+  </si>
+  <si>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/molotov-0</t>
+  </si>
+  <si>
+    <t>río de luna</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA: Da.Te Danza DURACIÓN: 37 minutos Mejor Espectáculo de Danza en FETEN (Gijón, 2011)
 Un despertar, una corriente suave, un primer aliento que se transforma en danza.
 Todo empieza con una vibración. Una luz que acaricia la piel, una sombra que se mueve, un sonido que parece llamarnos desde dentro.
 “Río de Luna” es un viaje sin palabras hacia ese instante en que la vida comienza a sentirse.
@@ -1748,17 +1753,14 @@
 Río de Luna es un canto al vínculo, a la complicidad que brota entre cuerpos pequeños y grandes cuando el lenguaje es presencia.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/rio-de-luna-17</t>
+    <t>https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/rio-de-luna-17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1767,43 +1769,25 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -1826,7 +1810,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1834,62 +1818,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1948,47 +1901,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F5496"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1996,12 +1965,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2030,7 +1999,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2051,7 +2020,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2102,7 +2071,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2120,31 +2089,30 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F121"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="45"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2164,7 +2132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" ht="224.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2184,7 +2152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -2204,7 +2172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -2224,7 +2192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -2244,7 +2212,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -2264,7 +2232,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -2284,7 +2252,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -2304,7 +2272,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
@@ -2324,7 +2292,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -2344,7 +2312,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -2364,7 +2332,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="236.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:6" ht="277.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -2384,7 +2352,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
@@ -2404,7 +2372,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>59</v>
       </c>
@@ -2424,7 +2392,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>64</v>
       </c>
@@ -2444,7 +2412,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="326.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:6" ht="396" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>69</v>
       </c>
@@ -2464,7 +2432,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
@@ -2484,7 +2452,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>80</v>
       </c>
@@ -2504,7 +2472,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>85</v>
       </c>
@@ -2524,7 +2492,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>90</v>
       </c>
@@ -2544,7 +2512,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>95</v>
       </c>
@@ -2564,7 +2532,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>100</v>
       </c>
@@ -2584,7 +2552,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>104</v>
       </c>
@@ -2604,7 +2572,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>109</v>
       </c>
@@ -2624,7 +2592,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>114</v>
       </c>
@@ -2644,7 +2612,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>118</v>
       </c>
@@ -2664,7 +2632,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>123</v>
       </c>
@@ -2684,7 +2652,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>128</v>
       </c>
@@ -2704,7 +2672,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:6" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>132</v>
       </c>
@@ -2724,7 +2692,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>137</v>
       </c>
@@ -2744,7 +2712,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>142</v>
       </c>
@@ -2764,7 +2732,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="460.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>145</v>
       </c>
@@ -2784,7 +2752,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="605.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>150</v>
       </c>
@@ -2804,7 +2772,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>155</v>
       </c>
@@ -2824,7 +2792,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>159</v>
       </c>
@@ -2844,7 +2812,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:6" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>164</v>
       </c>
@@ -2864,7 +2832,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:6" ht="237.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>170</v>
       </c>
@@ -2884,7 +2852,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:6" ht="237.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>175</v>
       </c>
@@ -2904,7 +2872,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="236.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:6" ht="290.39999999999998" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>179</v>
       </c>
@@ -2924,7 +2892,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>184</v>
       </c>
@@ -2944,7 +2912,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>184</v>
       </c>
@@ -2964,7 +2932,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>184</v>
       </c>
@@ -2984,7 +2952,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>192</v>
       </c>
@@ -3004,7 +2972,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:6" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>196</v>
       </c>
@@ -3024,7 +2992,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="258.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:6" ht="303.60000000000002" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>200</v>
       </c>
@@ -3044,7 +3012,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>205</v>
       </c>
@@ -3064,7 +3032,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="236.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:6" ht="290.39999999999998" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>209</v>
       </c>
@@ -3084,7 +3052,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:6" ht="224.4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>214</v>
       </c>
@@ -3104,7 +3072,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="594.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>219</v>
       </c>
@@ -3124,7 +3092,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>223</v>
       </c>
@@ -3144,7 +3112,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="214.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:6" ht="264" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>227</v>
       </c>
@@ -3164,7 +3132,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:6" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>232</v>
       </c>
@@ -3184,7 +3152,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>237</v>
       </c>
@@ -3204,7 +3172,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>242</v>
       </c>
@@ -3224,7 +3192,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:6" ht="198" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>247</v>
       </c>
@@ -3244,7 +3212,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>252</v>
       </c>
@@ -3264,7 +3232,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:6" ht="132" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>258</v>
       </c>
@@ -3284,7 +3252,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>263</v>
       </c>
@@ -3304,7 +3272,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>268</v>
       </c>
@@ -3324,7 +3292,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="281.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:6" ht="356.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>272</v>
       </c>
@@ -3344,7 +3312,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:6" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>277</v>
       </c>
@@ -3364,7 +3332,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>282</v>
       </c>
@@ -3384,7 +3352,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>286</v>
       </c>
@@ -3404,7 +3372,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>290</v>
       </c>
@@ -3424,7 +3392,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="258.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:6" ht="330" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>294</v>
       </c>
@@ -3444,7 +3412,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>298</v>
       </c>
@@ -3464,7 +3432,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>303</v>
       </c>
@@ -3484,7 +3452,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>308</v>
       </c>
@@ -3504,7 +3472,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>313</v>
       </c>
@@ -3524,7 +3492,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>313</v>
       </c>
@@ -3544,7 +3512,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="404.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>319</v>
       </c>
@@ -3564,7 +3532,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:6" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>323</v>
       </c>
@@ -3584,7 +3552,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:6" ht="132" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>327</v>
       </c>
@@ -3604,7 +3572,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>332</v>
       </c>
@@ -3624,7 +3592,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>332</v>
       </c>
@@ -3644,7 +3612,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:6" ht="303.60000000000002" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>340</v>
       </c>
@@ -3664,7 +3632,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="236.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:6" ht="290.39999999999998" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>345</v>
       </c>
@@ -3684,7 +3652,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:6" ht="198" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>349</v>
       </c>
@@ -3704,7 +3672,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>353</v>
       </c>
@@ -3724,7 +3692,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>358</v>
       </c>
@@ -3744,7 +3712,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>363</v>
       </c>
@@ -3764,7 +3732,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>367</v>
       </c>
@@ -3784,7 +3752,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>372</v>
       </c>
@@ -3804,7 +3772,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>377</v>
       </c>
@@ -3824,7 +3792,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="303.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:6" ht="356.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>381</v>
       </c>
@@ -3844,7 +3812,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>386</v>
       </c>
@@ -3864,7 +3832,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>390</v>
       </c>
@@ -3884,7 +3852,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>395</v>
       </c>
@@ -3904,7 +3872,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="930.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>400</v>
       </c>
@@ -3924,7 +3892,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>405</v>
       </c>
@@ -3944,7 +3912,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:6" ht="330" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>410</v>
       </c>
@@ -3964,7 +3932,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>415</v>
       </c>
@@ -3984,7 +3952,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:6" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>420</v>
       </c>
@@ -4004,7 +3972,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="494" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>424</v>
       </c>
@@ -4024,7 +3992,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>429</v>
       </c>
@@ -4044,7 +4012,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>434</v>
       </c>
@@ -4064,7 +4032,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:6" ht="224.4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>438</v>
       </c>
@@ -4084,7 +4052,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>443</v>
       </c>
@@ -4104,7 +4072,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>447</v>
       </c>
@@ -4124,7 +4092,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>451</v>
       </c>
@@ -4144,7 +4112,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>455</v>
       </c>
@@ -4164,7 +4132,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>455</v>
       </c>
@@ -4184,7 +4152,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>455</v>
       </c>
@@ -4204,7 +4172,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:6" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>463</v>
       </c>
@@ -4224,7 +4192,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="236.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:6" ht="290.39999999999998" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>468</v>
       </c>
@@ -4244,7 +4212,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:6" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>473</v>
       </c>
@@ -4264,7 +4232,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:6" ht="343.2" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>477</v>
       </c>
@@ -4284,7 +4252,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>481</v>
       </c>
@@ -4304,7 +4272,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="605.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>486</v>
       </c>
@@ -4324,7 +4292,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>490</v>
       </c>
@@ -4344,7 +4312,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>490</v>
       </c>
@@ -4364,7 +4332,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>495</v>
       </c>
@@ -4384,7 +4352,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>495</v>
       </c>
@@ -4404,7 +4372,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:6" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>501</v>
       </c>
@@ -4424,7 +4392,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="303.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:6" ht="356.4" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>505</v>
       </c>
@@ -4444,7 +4412,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:6" ht="132" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>510</v>
       </c>
@@ -4464,7 +4432,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:6" ht="224.4" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>514</v>
       </c>
@@ -4484,7 +4452,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:6" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>518</v>
       </c>
@@ -4504,7 +4472,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:6" ht="224.4" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>522</v>
       </c>
@@ -4524,7 +4492,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>526</v>
       </c>
@@ -4544,7 +4512,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="270.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:6" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>530</v>
       </c>
@@ -4566,133 +4534,128 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exito-asegurado-12"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/y-tu-de-que-te-ries-alex-odogherty"/>
-    <hyperlink ref="F4" r:id="rId3" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aires-hojas-al-viento-3"/>
-    <hyperlink ref="F5" r:id="rId4" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aromas-del-sur-cuarteto-3"/>
-    <hyperlink ref="F6" r:id="rId5" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/aromas-del-sur-cuarteto-en-arcos-de-la-frontera"/>
-    <hyperlink ref="F7" r:id="rId6" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-0"/>
-    <hyperlink ref="F8" r:id="rId7" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-1"/>
-    <hyperlink ref="F9" r:id="rId8" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-2"/>
-    <hyperlink ref="F10" r:id="rId9" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-3"/>
-    <hyperlink ref="F11" r:id="rId10" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/arte-contemporaneo-y-yoga-para-ninos"/>
-    <hyperlink ref="F12" r:id="rId11" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/barquichuelo-de-papel-12"/>
-    <hyperlink ref="F13" r:id="rId12" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cabaret-festival-el-puerto-de-santa-maria"/>
-    <hyperlink ref="F14" r:id="rId13" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cabaret-festival-algeciras"/>
-    <hyperlink ref="F15" r:id="rId14" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/campo-abierto-0"/>
-    <hyperlink ref="F16" r:id="rId15" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/centro-de-interpretacion-del-mar-las-almadrabas-y-el-atun-conil-recinto-de-la-chanca"/>
-    <hyperlink ref="F17" r:id="rId16" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/ciclo-musica-del-mar"/>
-    <hyperlink ref="F18" r:id="rId17" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-de-rota"/>
-    <hyperlink ref="F19" r:id="rId18" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-chipiona"/>
-    <hyperlink ref="F20" r:id="rId19" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-el-patio-de-la-casa-del-nino-jesus"/>
-    <hyperlink ref="F21" r:id="rId20" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-la-linea-de-la-concepcion"/>
-    <hyperlink ref="F22" r:id="rId21" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-la-palma-del-condado"/>
-    <hyperlink ref="F23" r:id="rId22" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cine-de-verano-en-playas-algeciras"/>
-    <hyperlink ref="F24" r:id="rId23" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/circodeliko-5"/>
-    <hyperlink ref="F25" r:id="rId24" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/con-mucho-clown-16"/>
-    <hyperlink ref="F26" r:id="rId25" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concert-music-festival-en-sancti-petri"/>
-    <hyperlink ref="F27" r:id="rId26" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-andy-en-cadiz-solo-tour-2026"/>
-    <hyperlink ref="F28" r:id="rId27" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-andy-en-el-bosque-solo-tour-2026"/>
-    <hyperlink ref="F29" r:id="rId28" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-brothers-band-en-barco-la-pepa"/>
-    <hyperlink ref="F30" r:id="rId29" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-gipsy-kings-en-barco-la-pepa"/>
-    <hyperlink ref="F31" r:id="rId30" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/concierto-de-jose-manuel-soto-en-barco-la-pepa"/>
-    <hyperlink ref="F32" r:id="rId31" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/conjunto-arqueologico-de-baelo-claudia"/>
-    <hyperlink ref="F33" r:id="rId32" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/conjunto-arqueologico-de-baelo-claudia-en-verano-2026"/>
-    <hyperlink ref="F34" r:id="rId33" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/connectivity-5tet-2"/>
-    <hyperlink ref="F35" r:id="rId34" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cualquier-verdura-9"/>
-    <hyperlink ref="F36" r:id="rId35" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-exposicion-sobre-caballero-bonald-en-la-facultad-de-filosofia-y-letras"/>
-    <hyperlink ref="F37" r:id="rId36" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-musica-de-lobo-carmen-camacho-y-javier-prieto"/>
-    <hyperlink ref="F38" r:id="rId37" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cadiz-musica-de-lobo-david-eloy-rodriguez-y-virginia-moreno"/>
-    <hyperlink ref="F39" r:id="rId38" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/danzas-latinoamericanas"/>
-    <hyperlink ref="F40" r:id="rId39" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-0"/>
-    <hyperlink ref="F41" r:id="rId40" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-1"/>
-    <hyperlink ref="F42" r:id="rId41" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/desayunos-con-arte-2"/>
-    <hyperlink ref="F43" r:id="rId42" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/diabolo-classic-metal-1"/>
-    <hyperlink ref="F44" r:id="rId43" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/ellas-de-oro-1"/>
-    <hyperlink ref="F45" r:id="rId44" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-viento-es-salvaje-6"/>
-    <hyperlink ref="F46" r:id="rId45" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-asesino-de-la-regana-20"/>
-    <hyperlink ref="F47" r:id="rId46" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-clavecin-espanol-en-arcos-de-la-frontera"/>
-    <hyperlink ref="F48" r:id="rId47" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-crimen-del-palodu-21"/>
-    <hyperlink ref="F49" r:id="rId48" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/el-pianista-de-la-mano-izquierda-1"/>
-    <hyperlink ref="F50" r:id="rId49" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/espacios-en-conil-de-la-frontera"/>
-    <hyperlink ref="F51" r:id="rId50" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/espejo-de-las-estrellas-desiree-martin-juan-manuel-roman"/>
-    <hyperlink ref="F52" r:id="rId51" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exiliada-mujeres-en-el-arte"/>
-    <hyperlink ref="F53" r:id="rId52" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exposicion-en-rota-rotarte-2026"/>
-    <hyperlink ref="F54" r:id="rId53" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/exposicion-permanente-el-valle-de-los-caidos-1980-1987-de-costus"/>
-    <hyperlink ref="F55" r:id="rId54" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/festival-de-jazz-de-baelo-claudia"/>
-    <hyperlink ref="F56" r:id="rId55" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/fiestas-de-la-urta"/>
-    <hyperlink ref="F57" r:id="rId56" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/floridance-festival-en-rota"/>
-    <hyperlink ref="F58" r:id="rId57" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/gran-noche-de-carnaval-en-rota"/>
-    <hyperlink ref="F59" r:id="rId58" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/guitarricadelafuente"/>
-    <hyperlink ref="F60" r:id="rId59" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/historia-de-la-luz-electrica"/>
-    <hyperlink ref="F61" r:id="rId60" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/invisible-y-todas-las-demas-0"/>
-    <hyperlink ref="F62" r:id="rId61" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/joana-jimenez-en-rota"/>
-    <hyperlink ref="F63" r:id="rId62" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juan-amodeo-en-rota"/>
-    <hyperlink ref="F64" r:id="rId63" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juan-medina"/>
-    <hyperlink ref="F65" r:id="rId64" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/juanita-con-mayusculas"/>
-    <hyperlink ref="F66" r:id="rId65" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/lxv-festival-flamenco-velada-de-las-nieves-en-arcos-de-la-frontera"/>
-    <hyperlink ref="F67" r:id="rId66" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-coquette-6"/>
-    <hyperlink ref="F68" r:id="rId67" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-gallina-de-los-huevos-de-oro-6"/>
-    <hyperlink ref="F69" r:id="rId68" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-reina-brava-1"/>
-    <hyperlink ref="F70" r:id="rId69" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-reina-brava-4"/>
-    <hyperlink ref="F71" r:id="rId70" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-venganza-de-don-mendo-10"/>
-    <hyperlink ref="F72" r:id="rId71" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/la-voz-que-aun-resuena-mujeres-de-las-tres-culturas"/>
-    <hyperlink ref="F73" r:id="rId72" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/las-noches-blancas-de-medina-sidonia"/>
-    <hyperlink ref="F74" r:id="rId73" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/latente-2"/>
-    <hyperlink ref="F75" r:id="rId74" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/latente-1"/>
-    <hyperlink ref="F76" r:id="rId75" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/los-viajes-de-bowa-3"/>
-    <hyperlink ref="F77" r:id="rId76" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/machado-flamenco"/>
-    <hyperlink ref="F78" r:id="rId77" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/mama"/>
-    <hyperlink ref="F79" r:id="rId78" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/manolo-morera-en-conil"/>
-    <hyperlink ref="F80" r:id="rId79" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/melody-concierto-en-la-mina-conil-de-la-frontera"/>
-    <hyperlink ref="F81" r:id="rId80" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/miguel-campello-concierto-en-la-mina-conil-de-la-frontera"/>
-    <hyperlink ref="F82" r:id="rId81" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/molan-los-90-en-cadiz"/>
-    <hyperlink ref="F83" r:id="rId82" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/morera-president-en-rota"/>
-    <hyperlink ref="F84" r:id="rId83" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/no-sin-musica-festival"/>
-    <hyperlink ref="F85" r:id="rId84" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/noches-de-soul-y-blues-0"/>
-    <hyperlink ref="F86" r:id="rId85" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/pando-el-mago-en-rota"/>
-    <hyperlink ref="F87" r:id="rId86" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/pies-de-gallina-3"/>
-    <hyperlink ref="F88" r:id="rId87" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-de-actividades-en-la-bpe-biblioteca-provincial-de-cadiz"/>
-    <hyperlink ref="F89" r:id="rId88" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-de-verano-en-el-museo-de-cadiz"/>
-    <hyperlink ref="F90" r:id="rId89" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-del-ciclo-solera-y-compas"/>
-    <hyperlink ref="F91" r:id="rId90" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-especial-de-verano-del-centro-andaluz-de-las-letras-en-cadiz"/>
-    <hyperlink ref="F92" r:id="rId91" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/programacion-especial-de-verano-en-el-archivo-historico-provincial-de-cadiz"/>
-    <hyperlink ref="F93" r:id="rId92" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/quererte-medias-cuarteto-2"/>
-    <hyperlink ref="F94" r:id="rId93" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/rota-programacion-verano-cultural-y-juvenil"/>
-    <hyperlink ref="F95" r:id="rId94" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/samba-do-raiz-1"/>
-    <hyperlink ref="F96" r:id="rId95" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/sketches-spain-3"/>
-    <hyperlink ref="F97" r:id="rId96" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tagarnina-fest-en-algodonales"/>
-    <hyperlink ref="F98" r:id="rId97" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-cambia-la-mirada"/>
-    <hyperlink ref="F99" r:id="rId98" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-collage-textil-y-pintura-en-hilo"/>
-    <hyperlink ref="F100" r:id="rId99" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/taller-de-dibujo-entre-pinos-1"/>
-    <hyperlink ref="F101" r:id="rId100" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-7"/>
-    <hyperlink ref="F102" r:id="rId101" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-4"/>
-    <hyperlink ref="F103" r:id="rId102" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tuyo-cid-1"/>
-    <hyperlink ref="F104" r:id="rId103" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/tio-pepe-festival"/>
-    <hyperlink ref="F105" r:id="rId104" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/un-duo-6"/>
-    <hyperlink ref="F106" r:id="rId105" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/un-trocito-de-luna-39"/>
-    <hyperlink ref="F107" r:id="rId106" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/una-historia-de-mujeres-en-el-jazz-en-puerto-real"/>
-    <hyperlink ref="F108" r:id="rId107" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/verano-2026-programacion-de-la-red-andaluza-de-teatros-publicos-en-cadiz"/>
-    <hyperlink ref="F109" r:id="rId108" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/verano-en-baelo"/>
-    <hyperlink ref="F110" r:id="rId109" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-la-fundacion-montenmedio-contemporanea-1"/>
-    <hyperlink ref="F111" r:id="rId110" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-la-fundacion-montenmedio-contemporanea-2"/>
-    <hyperlink ref="F112" r:id="rId111" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-bajo-la-luna-llena"/>
-    <hyperlink ref="F113" r:id="rId112" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/visita-guiada-bajo-la-luna-llena-0"/>
-    <hyperlink ref="F114" r:id="rId113" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/wc-22"/>
-    <hyperlink ref="F115" r:id="rId114" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/xix-festival-de-chipiona"/>
-    <hyperlink ref="F116" r:id="rId115" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/yesterday-18"/>
-    <hyperlink ref="F117" r:id="rId116" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/zambra-de-la-buena-salvaje-1"/>
-    <hyperlink ref="F118" r:id="rId117" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/cual-es-mi-nombre-54"/>
-    <hyperlink ref="F119" r:id="rId118" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/las-furias-13"/>
-    <hyperlink ref="F120" r:id="rId119" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/molotov-0"/>
-    <hyperlink ref="F121" r:id="rId120" display="https://www.juntadeandalucia.es/cultura/agendaculturaldeandalucia/evento/rio-de-luna-17"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="F13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="F15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="F19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="F24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="F25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="F26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="F27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="F29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="F31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="F38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="F39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="F40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="F43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="F44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="F45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="F46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="F49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="F50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="F52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="F54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="F56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="F58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="F61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="F63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="F65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="F68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="F72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="F77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="F79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="F81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="F85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="F87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="F89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="F90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="F91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="F92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="F94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="F95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="F97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="F98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="F99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="F101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="F102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="F103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="F104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="F105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="F106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="F107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="F108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="F109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="F110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="F111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="F112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="F113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="F114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="F115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="F116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="F117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="F118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="F119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="F120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="F121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>